--- a/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9F19C9-7DDF-4A48-87C8-C2CA585D94C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A2682-F0F5-4E80-BB2D-61E2CBD86E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="296">
   <si>
     <t>*</t>
   </si>
@@ -725,10 +725,6 @@
   </si>
   <si>
     <t>itm_nm</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>RO</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2550,6 +2546,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2586,6 +2585,108 @@
     <xf numFmtId="0" fontId="23" fillId="24" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2604,15 +2705,6 @@
     <xf numFmtId="165" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2625,15 +2717,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="26" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2642,93 +2725,6 @@
     </xf>
     <xf numFmtId="165" fontId="26" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="47">
@@ -3166,7 +3162,7 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E2" s="39" t="s">
         <v>136</v>
@@ -3174,21 +3170,21 @@
       <c r="F2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="61"/>
-      <c r="I2" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="J2" s="65"/>
-      <c r="K2" s="58" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="J2" s="66"/>
+      <c r="K2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="55"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="56"/>
       <c r="P2" s="40"/>
       <c r="Q2" s="42" t="s">
         <v>49</v>
@@ -3222,23 +3218,23 @@
         <v>14</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="G3" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64" t="s">
-        <v>219</v>
-      </c>
-      <c r="J3" s="65"/>
-      <c r="K3" s="58" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="J3" s="66"/>
+      <c r="K3" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="55"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="56"/>
       <c r="P3" s="40"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="39" t="s">
@@ -3274,21 +3270,21 @@
       <c r="F4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64" t="s">
-        <v>217</v>
-      </c>
-      <c r="J4" s="65"/>
-      <c r="K4" s="59" t="s">
+      <c r="H4" s="64"/>
+      <c r="I4" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="J4" s="66"/>
+      <c r="K4" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="55"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="56"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="20" t="s">
         <v>51</v>
@@ -3322,12 +3318,12 @@
       <c r="F5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
       <c r="K5" s="46"/>
       <c r="L5" s="46"/>
       <c r="M5" s="46"/>
@@ -3360,19 +3356,19 @@
       <c r="D6" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="E6" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
       <c r="P6" s="47"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
@@ -3450,49 +3446,49 @@
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="39" t="s">
+      <c r="G8" s="46" t="s">
         <v>183</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>184</v>
       </c>
       <c r="H8" s="39"/>
       <c r="I8" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="J8" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="K8" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="L8" s="39" t="s">
         <v>187</v>
-      </c>
-      <c r="L8" s="39" t="s">
-        <v>188</v>
       </c>
       <c r="M8" s="41" t="s">
         <v>89</v>
       </c>
       <c r="N8" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="O8" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="O8" s="39" t="s">
+      <c r="P8" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="P8" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q8" s="55" t="s">
+      <c r="Q8" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="R8" s="57"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="R8" s="56"/>
-      <c r="S8" s="57"/>
-      <c r="T8" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="U8" s="20" t="s">
         <v>53</v>
@@ -3508,21 +3504,21 @@
       </c>
       <c r="Y8" s="27"/>
       <c r="Z8" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA8" s="20" t="s">
         <v>178</v>
-      </c>
-      <c r="AA8" s="20" t="s">
-        <v>179</v>
       </c>
       <c r="AB8" s="27"/>
       <c r="AC8" s="39" t="s">
         <v>143</v>
       </c>
       <c r="AD8" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE8" s="19"/>
       <c r="AF8" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="54" customFormat="1" ht="60" customHeight="1">
@@ -3532,43 +3528,43 @@
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="46" t="s">
         <v>191</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="F9" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="G9" s="52" t="s">
         <v>193</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="H9" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="I9" s="39" t="s">
         <v>195</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>196</v>
       </c>
       <c r="J9" s="53" t="s">
         <v>92</v>
       </c>
       <c r="K9" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="L9" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="M9" s="39" t="s">
         <v>198</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="N9" s="39" t="s">
         <v>199</v>
-      </c>
-      <c r="N9" s="39" t="s">
-        <v>200</v>
       </c>
       <c r="O9" s="39" t="s">
         <v>24</v>
       </c>
       <c r="P9" s="39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q9" s="39" t="s">
         <v>25</v>
@@ -3595,10 +3591,10 @@
         <v>28</v>
       </c>
       <c r="AE9" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AF9" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="1" customFormat="1" ht="27">
@@ -3631,10 +3627,10 @@
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD10" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD10" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AE10" s="4"/>
       <c r="AF10" s="28"/>
@@ -3660,7 +3656,7 @@
         <v>70</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K11" s="30" t="s">
         <v>71</v>
@@ -3869,10 +3865,10 @@
     <row r="17" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A17" s="5"/>
       <c r="AC17" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD17" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD17" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF17" s="11"/>
     </row>
@@ -3934,7 +3930,7 @@
         <v>95</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>66</v>
@@ -3979,7 +3975,7 @@
         <v>97</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F20" s="20" t="s">
         <v>68</v>
@@ -4024,7 +4020,7 @@
         <v>108</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>109</v>
@@ -4062,10 +4058,10 @@
     <row r="22" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A22" s="5"/>
       <c r="AC22" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD22" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD22" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF22" s="11"/>
     </row>
@@ -4159,10 +4155,10 @@
     <row r="25" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A25" s="5"/>
       <c r="AC25" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD25" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD25" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF25" s="11"/>
     </row>
@@ -4256,10 +4252,10 @@
     <row r="28" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A28" s="5"/>
       <c r="AC28" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD28" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD28" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF28" s="11"/>
     </row>
@@ -4353,10 +4349,10 @@
     <row r="31" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A31" s="5"/>
       <c r="AC31" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD31" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD31" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF31" s="11"/>
     </row>
@@ -4417,7 +4413,7 @@
       <c r="B33" s="37"/>
       <c r="C33" s="37"/>
       <c r="D33" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -4465,16 +4461,16 @@
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="F34" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="G34" s="20" t="s">
         <v>226</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>227</v>
       </c>
       <c r="H34" s="20"/>
       <c r="I34" s="20" t="s">
@@ -4494,7 +4490,7 @@
       </c>
       <c r="R34" s="20"/>
       <c r="S34" s="20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T34" s="20"/>
       <c r="U34" s="20"/>
@@ -4508,7 +4504,7 @@
       <c r="Z34" s="20"/>
       <c r="AA34" s="20"/>
       <c r="AC34" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AD34" s="20"/>
       <c r="AF34" s="16"/>
@@ -4520,13 +4516,13 @@
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E35" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="F35" s="20" t="s">
         <v>229</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>230</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="R35" s="20"/>
       <c r="S35" s="20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T35" s="20"/>
       <c r="U35" s="20"/>
@@ -4561,7 +4557,7 @@
       <c r="Z35" s="20"/>
       <c r="AA35" s="20"/>
       <c r="AC35" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AD35" s="20"/>
       <c r="AF35" s="16"/>
@@ -4573,13 +4569,13 @@
       <c r="B36" s="20"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="F36" s="20" t="s">
         <v>232</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>233</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
@@ -4600,7 +4596,7 @@
       </c>
       <c r="R36" s="20"/>
       <c r="S36" s="20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T36" s="20"/>
       <c r="U36" s="20"/>
@@ -4614,7 +4610,7 @@
       <c r="Z36" s="20"/>
       <c r="AA36" s="20"/>
       <c r="AC36" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AD36" s="20"/>
       <c r="AF36" s="16"/>
@@ -4626,13 +4622,13 @@
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
       <c r="D37" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="F37" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
@@ -4653,7 +4649,7 @@
       </c>
       <c r="R37" s="20"/>
       <c r="S37" s="20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T37" s="20"/>
       <c r="U37" s="20"/>
@@ -4667,7 +4663,7 @@
       <c r="Z37" s="20"/>
       <c r="AA37" s="20"/>
       <c r="AC37" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AD37" s="20"/>
       <c r="AF37" s="16"/>
@@ -4679,13 +4675,13 @@
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="F38" s="20" t="s">
         <v>238</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>239</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
@@ -4712,7 +4708,7 @@
       <c r="Z38" s="20"/>
       <c r="AA38" s="20"/>
       <c r="AC38" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AD38" s="20"/>
       <c r="AF38" s="16"/>
@@ -4724,20 +4720,20 @@
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
       <c r="D39" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E39" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>247</v>
       </c>
       <c r="G39" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J39" s="20"/>
       <c r="K39" s="20" t="s">
@@ -4756,12 +4752,8 @@
       <c r="V39" s="20"/>
       <c r="W39" s="20"/>
       <c r="X39" s="20"/>
-      <c r="Z39" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA39" s="20" t="s">
-        <v>161</v>
-      </c>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
       <c r="AC39" s="20"/>
       <c r="AD39" s="20"/>
       <c r="AF39" s="16"/>
@@ -4773,7 +4765,7 @@
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
       <c r="D40" s="37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E40" s="37"/>
       <c r="F40" s="37"/>
@@ -4821,16 +4813,16 @@
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="F41" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="G41" s="20" t="s">
         <v>251</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>252</v>
       </c>
       <c r="H41" s="20"/>
       <c r="I41" s="20" t="s">
@@ -4850,7 +4842,7 @@
       </c>
       <c r="R41" s="20"/>
       <c r="S41" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T41" s="20"/>
       <c r="U41" s="20"/>
@@ -4876,13 +4868,13 @@
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E42" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="F42" s="20" t="s">
         <v>254</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>255</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
@@ -4903,7 +4895,7 @@
       </c>
       <c r="R42" s="20"/>
       <c r="S42" s="20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T42" s="20"/>
       <c r="U42" s="20"/>
@@ -4929,13 +4921,13 @@
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E43" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="F43" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>258</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
@@ -4956,7 +4948,7 @@
       </c>
       <c r="R43" s="20"/>
       <c r="S43" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T43" s="20"/>
       <c r="U43" s="20"/>
@@ -4982,13 +4974,13 @@
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E44" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="F44" s="20" t="s">
         <v>260</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>261</v>
       </c>
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
@@ -5009,7 +5001,7 @@
       </c>
       <c r="R44" s="20"/>
       <c r="S44" s="20" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
@@ -5035,13 +5027,13 @@
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="F45" s="20" t="s">
         <v>263</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>264</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
@@ -5074,7 +5066,7 @@
       <c r="AF45" s="16"/>
     </row>
     <row r="46" spans="1:34" s="1" customFormat="1">
-      <c r="A46" s="114">
+      <c r="A46" s="55">
         <v>70</v>
       </c>
       <c r="B46" s="30"/>
@@ -5083,7 +5075,7 @@
         <v>126</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>100</v>
@@ -5093,11 +5085,11 @@
       </c>
       <c r="H46" s="30"/>
       <c r="I46" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J46" s="30"/>
       <c r="K46" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L46" s="30"/>
       <c r="M46" s="30"/>
@@ -5127,7 +5119,7 @@
       <c r="AH46" s="36"/>
     </row>
     <row r="47" spans="1:34" s="1" customFormat="1">
-      <c r="A47" s="114">
+      <c r="A47" s="55">
         <v>70</v>
       </c>
       <c r="B47" s="30"/>
@@ -5136,7 +5128,7 @@
         <v>127</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F47" s="30" t="s">
         <v>102</v>
@@ -5146,11 +5138,11 @@
       </c>
       <c r="H47" s="30"/>
       <c r="I47" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J47" s="30"/>
       <c r="K47" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L47" s="30"/>
       <c r="M47" s="30"/>
@@ -5182,10 +5174,10 @@
     <row r="48" spans="1:34" s="1" customFormat="1" ht="27">
       <c r="A48" s="5"/>
       <c r="AC48" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD48" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD48" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF48" s="11"/>
     </row>
@@ -5240,10 +5232,10 @@
     <row r="50" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A50" s="5"/>
       <c r="AC50" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD50" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD50" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF50" s="11"/>
     </row>
@@ -5298,10 +5290,10 @@
     <row r="52" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A52" s="5"/>
       <c r="AC52" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD52" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD52" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF52" s="11"/>
     </row>
@@ -5328,7 +5320,7 @@
         <v>71</v>
       </c>
       <c r="L53" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M53" s="20" t="s">
         <v>85</v>
@@ -5383,7 +5375,7 @@
       <c r="O54" s="20"/>
       <c r="P54" s="20"/>
       <c r="Q54" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R54" s="20"/>
       <c r="S54" s="20"/>
@@ -5401,10 +5393,10 @@
     <row r="55" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A55" s="5"/>
       <c r="AC55" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="AD55" s="39" t="s">
         <v>213</v>
-      </c>
-      <c r="AD55" s="39" t="s">
-        <v>214</v>
       </c>
       <c r="AF55" s="11"/>
     </row>
@@ -5468,7 +5460,7 @@
         <v>114</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F57" s="20" t="s">
         <v>115</v>
@@ -5482,7 +5474,7 @@
       </c>
       <c r="J57" s="20"/>
       <c r="K57" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L57" s="20"/>
       <c r="M57" s="20" t="s">
@@ -5495,7 +5487,7 @@
       <c r="R57" s="20"/>
       <c r="S57" s="20"/>
       <c r="T57" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U57" s="20"/>
       <c r="V57" s="20"/>
@@ -5541,7 +5533,7 @@
       </c>
       <c r="N59" s="20"/>
       <c r="O59" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P59" s="20"/>
       <c r="Q59" s="22"/>
@@ -5570,7 +5562,7 @@
       <c r="B60" s="37"/>
       <c r="C60" s="37"/>
       <c r="D60" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E60" s="37"/>
       <c r="F60" s="37"/>
@@ -5600,10 +5592,10 @@
       <c r="X60" s="37"/>
       <c r="Y60" s="37"/>
       <c r="Z60" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA60" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AB60" s="37"/>
       <c r="AC60" s="37"/>
@@ -5618,16 +5610,16 @@
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="E61" s="16" t="s">
+      <c r="F61" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="G61" s="20" t="s">
         <v>226</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>227</v>
       </c>
       <c r="H61" s="20"/>
       <c r="I61" s="20" t="s">
@@ -5654,7 +5646,7 @@
       <c r="AA61" s="20"/>
       <c r="AC61" s="20"/>
       <c r="AD61" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AF61" s="17"/>
     </row>
@@ -5665,13 +5657,13 @@
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="F62" s="20" t="s">
         <v>229</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>230</v>
       </c>
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
@@ -5699,7 +5691,7 @@
       <c r="AA62" s="20"/>
       <c r="AC62" s="20"/>
       <c r="AD62" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AF62" s="17"/>
     </row>
@@ -5710,13 +5702,13 @@
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E63" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="F63" s="20" t="s">
         <v>232</v>
-      </c>
-      <c r="F63" s="20" t="s">
-        <v>233</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
@@ -5744,7 +5736,7 @@
       <c r="AA63" s="20"/>
       <c r="AC63" s="20"/>
       <c r="AD63" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AF63" s="17"/>
     </row>
@@ -5755,13 +5747,13 @@
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E64" s="16" t="s">
+      <c r="F64" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="F64" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
@@ -5789,7 +5781,7 @@
       <c r="AA64" s="20"/>
       <c r="AC64" s="20"/>
       <c r="AD64" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AF64" s="17"/>
     </row>
@@ -5800,13 +5792,13 @@
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="F65" s="20" t="s">
         <v>238</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>239</v>
       </c>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
@@ -5834,7 +5826,7 @@
       <c r="AA65" s="20"/>
       <c r="AC65" s="20"/>
       <c r="AD65" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF65" s="17"/>
     </row>
@@ -5845,20 +5837,20 @@
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E66" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F66" s="20" t="s">
         <v>242</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>243</v>
       </c>
       <c r="G66" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H66" s="20"/>
       <c r="I66" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J66" s="20"/>
       <c r="K66" s="20" t="s">
@@ -5894,20 +5886,20 @@
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E67" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="F67" s="20" t="s">
-        <v>247</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H67" s="20"/>
       <c r="I67" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J67" s="20"/>
       <c r="K67" s="20" t="s">
@@ -5943,7 +5935,7 @@
       <c r="B68" s="37"/>
       <c r="C68" s="37"/>
       <c r="D68" s="37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E68" s="37"/>
       <c r="F68" s="37"/>
@@ -5973,10 +5965,10 @@
       <c r="X68" s="37"/>
       <c r="Y68" s="37"/>
       <c r="Z68" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA68" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AB68" s="37"/>
       <c r="AC68" s="37"/>
@@ -5991,16 +5983,16 @@
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E69" s="16" t="s">
+      <c r="F69" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="F69" s="20" t="s">
+      <c r="G69" s="20" t="s">
         <v>251</v>
-      </c>
-      <c r="G69" s="20" t="s">
-        <v>252</v>
       </c>
       <c r="H69" s="20"/>
       <c r="I69" s="20" t="s">
@@ -6038,13 +6030,13 @@
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E70" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="F70" s="20" t="s">
         <v>254</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>255</v>
       </c>
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
@@ -6083,13 +6075,13 @@
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E71" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="E71" s="16" t="s">
+      <c r="F71" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>258</v>
       </c>
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
@@ -6128,13 +6120,13 @@
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="F72" s="20" t="s">
         <v>260</v>
-      </c>
-      <c r="F72" s="20" t="s">
-        <v>261</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
@@ -6173,13 +6165,13 @@
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E73" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="E73" s="16" t="s">
+      <c r="F73" s="20" t="s">
         <v>263</v>
-      </c>
-      <c r="F73" s="20" t="s">
-        <v>264</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
@@ -6218,20 +6210,20 @@
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E74" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F74" s="20" t="s">
         <v>273</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>274</v>
       </c>
       <c r="G74" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H74" s="20"/>
       <c r="I74" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J74" s="20"/>
       <c r="K74" s="20" t="s">
@@ -6267,20 +6259,20 @@
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E75" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="F75" s="20" t="s">
         <v>275</v>
-      </c>
-      <c r="F75" s="20" t="s">
-        <v>276</v>
       </c>
       <c r="G75" s="20" t="s">
         <v>121</v>
       </c>
       <c r="H75" s="20"/>
       <c r="I75" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J75" s="20"/>
       <c r="K75" s="20" t="s">
@@ -6316,24 +6308,24 @@
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E76" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="F76" s="20" t="s">
         <v>277</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>278</v>
       </c>
       <c r="G76" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H76" s="20"/>
       <c r="I76" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J76" s="20"/>
       <c r="K76" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L76" s="20"/>
       <c r="M76" s="20"/>
@@ -6361,24 +6353,24 @@
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E77" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="F77" s="20" t="s">
         <v>279</v>
-      </c>
-      <c r="F77" s="20" t="s">
-        <v>280</v>
       </c>
       <c r="G77" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H77" s="20"/>
       <c r="I77" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J77" s="20"/>
       <c r="K77" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L77" s="20"/>
       <c r="M77" s="20"/>
@@ -6406,24 +6398,24 @@
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E78" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F78" s="20" t="s">
         <v>281</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>282</v>
       </c>
       <c r="G78" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H78" s="20"/>
       <c r="I78" s="20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J78" s="20"/>
       <c r="K78" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L78" s="20"/>
       <c r="M78" s="20"/>
@@ -6505,16 +6497,16 @@
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
       <c r="D81" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="F81" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F81" s="20" t="s">
+      <c r="G81" s="20" t="s">
         <v>176</v>
-      </c>
-      <c r="G81" s="20" t="s">
-        <v>177</v>
       </c>
       <c r="H81" s="20"/>
       <c r="I81" s="20" t="s">
@@ -6522,7 +6514,7 @@
       </c>
       <c r="J81" s="20"/>
       <c r="K81" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L81" s="20"/>
       <c r="M81" s="20"/>
@@ -6533,7 +6525,7 @@
       <c r="R81" s="20"/>
       <c r="S81" s="20"/>
       <c r="T81" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U81" s="20"/>
       <c r="V81" s="20"/>
@@ -6559,13 +6551,13 @@
         <v>123</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F82" s="20" t="s">
         <v>124</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H82" s="20"/>
       <c r="I82" s="20" t="s">
@@ -6573,7 +6565,7 @@
       </c>
       <c r="J82" s="20"/>
       <c r="K82" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L82" s="20"/>
       <c r="M82" s="20"/>
@@ -6822,65 +6814,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
-      <c r="AC1" s="91"/>
-      <c r="AD1" s="91"/>
-      <c r="AE1" s="91"/>
-      <c r="AF1" s="91"/>
-      <c r="AG1" s="91"/>
-      <c r="AH1" s="91"/>
-      <c r="AI1" s="91"/>
-      <c r="AJ1" s="91"/>
-      <c r="AK1" s="91"/>
-      <c r="AL1" s="91"/>
-      <c r="AM1" s="91"/>
-      <c r="AN1" s="91"/>
-      <c r="AO1" s="91"/>
-      <c r="AP1" s="91"/>
-      <c r="AQ1" s="91"/>
-      <c r="AR1" s="91"/>
-      <c r="AS1" s="91"/>
-      <c r="AT1" s="91"/>
-      <c r="AU1" s="91"/>
-      <c r="AV1" s="91"/>
-      <c r="AW1" s="91"/>
-      <c r="AX1" s="91"/>
-      <c r="AY1" s="91"/>
-      <c r="AZ1" s="91"/>
-      <c r="BA1" s="91"/>
-      <c r="BB1" s="91"/>
-      <c r="BC1" s="91"/>
-      <c r="BD1" s="91"/>
-      <c r="BE1" s="92"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
+      <c r="Z1" s="92"/>
+      <c r="AA1" s="92"/>
+      <c r="AB1" s="92"/>
+      <c r="AC1" s="92"/>
+      <c r="AD1" s="92"/>
+      <c r="AE1" s="92"/>
+      <c r="AF1" s="92"/>
+      <c r="AG1" s="92"/>
+      <c r="AH1" s="92"/>
+      <c r="AI1" s="92"/>
+      <c r="AJ1" s="92"/>
+      <c r="AK1" s="92"/>
+      <c r="AL1" s="92"/>
+      <c r="AM1" s="92"/>
+      <c r="AN1" s="92"/>
+      <c r="AO1" s="92"/>
+      <c r="AP1" s="92"/>
+      <c r="AQ1" s="92"/>
+      <c r="AR1" s="92"/>
+      <c r="AS1" s="92"/>
+      <c r="AT1" s="92"/>
+      <c r="AU1" s="92"/>
+      <c r="AV1" s="92"/>
+      <c r="AW1" s="92"/>
+      <c r="AX1" s="92"/>
+      <c r="AY1" s="92"/>
+      <c r="AZ1" s="92"/>
+      <c r="BA1" s="92"/>
+      <c r="BB1" s="92"/>
+      <c r="BC1" s="92"/>
+      <c r="BD1" s="92"/>
+      <c r="BE1" s="93"/>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="13"/>
@@ -6927,1972 +6919,2081 @@
       <c r="AP2" s="13"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="93" t="s">
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="93" t="s">
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="96"/>
-      <c r="AD3" s="96"/>
-      <c r="AE3" s="96"/>
-      <c r="AF3" s="96"/>
-      <c r="AG3" s="96"/>
-      <c r="AH3" s="96"/>
-      <c r="AI3" s="96"/>
-      <c r="AJ3" s="96"/>
-      <c r="AK3" s="96"/>
-      <c r="AL3" s="96"/>
-      <c r="AM3" s="96"/>
-      <c r="AN3" s="96"/>
-      <c r="AO3" s="96"/>
-      <c r="AP3" s="97"/>
-      <c r="AQ3" s="93" t="s">
+      <c r="P3" s="95"/>
+      <c r="Q3" s="95"/>
+      <c r="R3" s="95"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="95"/>
+      <c r="V3" s="95"/>
+      <c r="W3" s="95"/>
+      <c r="X3" s="95"/>
+      <c r="Y3" s="95"/>
+      <c r="Z3" s="95"/>
+      <c r="AA3" s="95"/>
+      <c r="AB3" s="95"/>
+      <c r="AC3" s="95"/>
+      <c r="AD3" s="95"/>
+      <c r="AE3" s="95"/>
+      <c r="AF3" s="95"/>
+      <c r="AG3" s="95"/>
+      <c r="AH3" s="95"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="96"/>
+      <c r="AQ3" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="AR3" s="98"/>
-      <c r="AS3" s="98"/>
-      <c r="AT3" s="98"/>
-      <c r="AU3" s="98"/>
-      <c r="AV3" s="98"/>
-      <c r="AW3" s="98"/>
-      <c r="AX3" s="98"/>
-      <c r="AY3" s="98"/>
-      <c r="AZ3" s="98"/>
-      <c r="BA3" s="98"/>
-      <c r="BB3" s="98"/>
-      <c r="BC3" s="98"/>
-      <c r="BD3" s="98"/>
-      <c r="BE3" s="99"/>
+      <c r="AR3" s="97"/>
+      <c r="AS3" s="97"/>
+      <c r="AT3" s="97"/>
+      <c r="AU3" s="97"/>
+      <c r="AV3" s="97"/>
+      <c r="AW3" s="97"/>
+      <c r="AX3" s="97"/>
+      <c r="AY3" s="97"/>
+      <c r="AZ3" s="97"/>
+      <c r="BA3" s="97"/>
+      <c r="BB3" s="97"/>
+      <c r="BC3" s="97"/>
+      <c r="BD3" s="97"/>
+      <c r="BE3" s="98"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="70">
+      <c r="A4" s="105">
         <v>1</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="109"/>
-      <c r="O4" s="107" t="s">
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
-      <c r="W4" s="110"/>
-      <c r="X4" s="110"/>
-      <c r="Y4" s="110"/>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="110"/>
-      <c r="AE4" s="110"/>
-      <c r="AF4" s="110"/>
-      <c r="AG4" s="110"/>
-      <c r="AH4" s="110"/>
-      <c r="AI4" s="110"/>
-      <c r="AJ4" s="110"/>
-      <c r="AK4" s="110"/>
-      <c r="AL4" s="110"/>
-      <c r="AM4" s="110"/>
-      <c r="AN4" s="110"/>
-      <c r="AO4" s="110"/>
-      <c r="AP4" s="111"/>
-      <c r="AQ4" s="112"/>
-      <c r="AR4" s="110"/>
-      <c r="AS4" s="110"/>
-      <c r="AT4" s="110"/>
-      <c r="AU4" s="110"/>
-      <c r="AV4" s="110"/>
-      <c r="AW4" s="110"/>
-      <c r="AX4" s="110"/>
-      <c r="AY4" s="110"/>
-      <c r="AZ4" s="110"/>
-      <c r="BA4" s="110"/>
-      <c r="BB4" s="110"/>
-      <c r="BC4" s="110"/>
-      <c r="BD4" s="110"/>
-      <c r="BE4" s="113"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="74"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="74"/>
+      <c r="X4" s="74"/>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="74"/>
+      <c r="AB4" s="74"/>
+      <c r="AC4" s="74"/>
+      <c r="AD4" s="74"/>
+      <c r="AE4" s="74"/>
+      <c r="AF4" s="74"/>
+      <c r="AG4" s="74"/>
+      <c r="AH4" s="74"/>
+      <c r="AI4" s="74"/>
+      <c r="AJ4" s="74"/>
+      <c r="AK4" s="74"/>
+      <c r="AL4" s="74"/>
+      <c r="AM4" s="74"/>
+      <c r="AN4" s="74"/>
+      <c r="AO4" s="74"/>
+      <c r="AP4" s="75"/>
+      <c r="AQ4" s="76"/>
+      <c r="AR4" s="74"/>
+      <c r="AS4" s="74"/>
+      <c r="AT4" s="74"/>
+      <c r="AU4" s="74"/>
+      <c r="AV4" s="74"/>
+      <c r="AW4" s="74"/>
+      <c r="AX4" s="74"/>
+      <c r="AY4" s="74"/>
+      <c r="AZ4" s="74"/>
+      <c r="BA4" s="74"/>
+      <c r="BB4" s="74"/>
+      <c r="BC4" s="74"/>
+      <c r="BD4" s="74"/>
+      <c r="BE4" s="77"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="73">
+      <c r="A5" s="99">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="101" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="86"/>
+      <c r="V5" s="86"/>
+      <c r="W5" s="86"/>
+      <c r="X5" s="86"/>
+      <c r="Y5" s="86"/>
+      <c r="Z5" s="86"/>
+      <c r="AA5" s="86"/>
+      <c r="AB5" s="86"/>
+      <c r="AC5" s="86"/>
+      <c r="AD5" s="86"/>
+      <c r="AE5" s="86"/>
+      <c r="AF5" s="86"/>
+      <c r="AG5" s="86"/>
+      <c r="AH5" s="86"/>
+      <c r="AI5" s="86"/>
+      <c r="AJ5" s="86"/>
+      <c r="AK5" s="86"/>
+      <c r="AL5" s="86"/>
+      <c r="AM5" s="86"/>
+      <c r="AN5" s="86"/>
+      <c r="AO5" s="86"/>
+      <c r="AP5" s="87"/>
+      <c r="AQ5" s="88" t="s">
         <v>215</v>
       </c>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
-      <c r="AI5" s="102"/>
-      <c r="AJ5" s="102"/>
-      <c r="AK5" s="102"/>
-      <c r="AL5" s="102"/>
-      <c r="AM5" s="102"/>
-      <c r="AN5" s="102"/>
-      <c r="AO5" s="102"/>
-      <c r="AP5" s="103"/>
-      <c r="AQ5" s="104" t="s">
-        <v>216</v>
-      </c>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="105"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="105"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="105"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="105"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="105"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="105"/>
-      <c r="BD5" s="105"/>
-      <c r="BE5" s="106"/>
+      <c r="AR5" s="89"/>
+      <c r="AS5" s="89"/>
+      <c r="AT5" s="89"/>
+      <c r="AU5" s="89"/>
+      <c r="AV5" s="89"/>
+      <c r="AW5" s="89"/>
+      <c r="AX5" s="89"/>
+      <c r="AY5" s="89"/>
+      <c r="AZ5" s="89"/>
+      <c r="BA5" s="89"/>
+      <c r="BB5" s="89"/>
+      <c r="BC5" s="89"/>
+      <c r="BD5" s="89"/>
+      <c r="BE5" s="90"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="73"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="89"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="81"/>
-      <c r="AA6" s="81"/>
-      <c r="AB6" s="81"/>
-      <c r="AC6" s="81"/>
-      <c r="AD6" s="81"/>
-      <c r="AE6" s="81"/>
-      <c r="AF6" s="81"/>
-      <c r="AG6" s="81"/>
-      <c r="AH6" s="81"/>
-      <c r="AI6" s="81"/>
-      <c r="AJ6" s="81"/>
-      <c r="AK6" s="81"/>
-      <c r="AL6" s="81"/>
-      <c r="AM6" s="81"/>
-      <c r="AN6" s="81"/>
-      <c r="AO6" s="81"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="86"/>
-      <c r="AR6" s="81"/>
-      <c r="AS6" s="81"/>
-      <c r="AT6" s="81"/>
-      <c r="AU6" s="81"/>
-      <c r="AV6" s="81"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="81"/>
-      <c r="AY6" s="81"/>
-      <c r="AZ6" s="81"/>
-      <c r="BA6" s="81"/>
-      <c r="BB6" s="81"/>
-      <c r="BC6" s="81"/>
-      <c r="BD6" s="81"/>
-      <c r="BE6" s="87"/>
+      <c r="A6" s="99"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="69"/>
+      <c r="Y6" s="69"/>
+      <c r="Z6" s="69"/>
+      <c r="AA6" s="69"/>
+      <c r="AB6" s="69"/>
+      <c r="AC6" s="69"/>
+      <c r="AD6" s="69"/>
+      <c r="AE6" s="69"/>
+      <c r="AF6" s="69"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="69"/>
+      <c r="AJ6" s="69"/>
+      <c r="AK6" s="69"/>
+      <c r="AL6" s="69"/>
+      <c r="AM6" s="69"/>
+      <c r="AN6" s="69"/>
+      <c r="AO6" s="69"/>
+      <c r="AP6" s="81"/>
+      <c r="AQ6" s="68"/>
+      <c r="AR6" s="69"/>
+      <c r="AS6" s="69"/>
+      <c r="AT6" s="69"/>
+      <c r="AU6" s="69"/>
+      <c r="AV6" s="69"/>
+      <c r="AW6" s="69"/>
+      <c r="AX6" s="69"/>
+      <c r="AY6" s="69"/>
+      <c r="AZ6" s="69"/>
+      <c r="BA6" s="69"/>
+      <c r="BB6" s="69"/>
+      <c r="BC6" s="69"/>
+      <c r="BD6" s="69"/>
+      <c r="BE6" s="70"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="89"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="81"/>
-      <c r="U7" s="81"/>
-      <c r="V7" s="81"/>
-      <c r="W7" s="81"/>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="81"/>
-      <c r="AB7" s="81"/>
-      <c r="AC7" s="81"/>
-      <c r="AD7" s="81"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="81"/>
-      <c r="AG7" s="81"/>
-      <c r="AH7" s="81"/>
-      <c r="AI7" s="81"/>
-      <c r="AJ7" s="81"/>
-      <c r="AK7" s="81"/>
-      <c r="AL7" s="81"/>
-      <c r="AM7" s="81"/>
-      <c r="AN7" s="81"/>
-      <c r="AO7" s="81"/>
-      <c r="AP7" s="82"/>
-      <c r="AQ7" s="86"/>
-      <c r="AR7" s="81"/>
-      <c r="AS7" s="81"/>
-      <c r="AT7" s="81"/>
-      <c r="AU7" s="81"/>
-      <c r="AV7" s="81"/>
-      <c r="AW7" s="81"/>
-      <c r="AX7" s="81"/>
-      <c r="AY7" s="81"/>
-      <c r="AZ7" s="81"/>
-      <c r="BA7" s="81"/>
-      <c r="BB7" s="81"/>
-      <c r="BC7" s="81"/>
-      <c r="BD7" s="81"/>
-      <c r="BE7" s="87"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="69"/>
+      <c r="V7" s="69"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="69"/>
+      <c r="Z7" s="69"/>
+      <c r="AA7" s="69"/>
+      <c r="AB7" s="69"/>
+      <c r="AC7" s="69"/>
+      <c r="AD7" s="69"/>
+      <c r="AE7" s="69"/>
+      <c r="AF7" s="69"/>
+      <c r="AG7" s="69"/>
+      <c r="AH7" s="69"/>
+      <c r="AI7" s="69"/>
+      <c r="AJ7" s="69"/>
+      <c r="AK7" s="69"/>
+      <c r="AL7" s="69"/>
+      <c r="AM7" s="69"/>
+      <c r="AN7" s="69"/>
+      <c r="AO7" s="69"/>
+      <c r="AP7" s="81"/>
+      <c r="AQ7" s="68"/>
+      <c r="AR7" s="69"/>
+      <c r="AS7" s="69"/>
+      <c r="AT7" s="69"/>
+      <c r="AU7" s="69"/>
+      <c r="AV7" s="69"/>
+      <c r="AW7" s="69"/>
+      <c r="AX7" s="69"/>
+      <c r="AY7" s="69"/>
+      <c r="AZ7" s="69"/>
+      <c r="BA7" s="69"/>
+      <c r="BB7" s="69"/>
+      <c r="BC7" s="69"/>
+      <c r="BD7" s="69"/>
+      <c r="BE7" s="70"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="73"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="80"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="81"/>
-      <c r="V8" s="81"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="81"/>
-      <c r="AC8" s="81"/>
-      <c r="AD8" s="81"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="81"/>
-      <c r="AJ8" s="81"/>
-      <c r="AK8" s="81"/>
-      <c r="AL8" s="81"/>
-      <c r="AM8" s="81"/>
-      <c r="AN8" s="81"/>
-      <c r="AO8" s="81"/>
-      <c r="AP8" s="82"/>
-      <c r="AQ8" s="86"/>
-      <c r="AR8" s="81"/>
-      <c r="AS8" s="81"/>
-      <c r="AT8" s="81"/>
-      <c r="AU8" s="81"/>
-      <c r="AV8" s="81"/>
-      <c r="AW8" s="81"/>
-      <c r="AX8" s="81"/>
-      <c r="AY8" s="81"/>
-      <c r="AZ8" s="81"/>
-      <c r="BA8" s="81"/>
-      <c r="BB8" s="81"/>
-      <c r="BC8" s="81"/>
-      <c r="BD8" s="81"/>
-      <c r="BE8" s="87"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="69"/>
+      <c r="Q8" s="69"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="69"/>
+      <c r="T8" s="69"/>
+      <c r="U8" s="69"/>
+      <c r="V8" s="69"/>
+      <c r="W8" s="69"/>
+      <c r="X8" s="69"/>
+      <c r="Y8" s="69"/>
+      <c r="Z8" s="69"/>
+      <c r="AA8" s="69"/>
+      <c r="AB8" s="69"/>
+      <c r="AC8" s="69"/>
+      <c r="AD8" s="69"/>
+      <c r="AE8" s="69"/>
+      <c r="AF8" s="69"/>
+      <c r="AG8" s="69"/>
+      <c r="AH8" s="69"/>
+      <c r="AI8" s="69"/>
+      <c r="AJ8" s="69"/>
+      <c r="AK8" s="69"/>
+      <c r="AL8" s="69"/>
+      <c r="AM8" s="69"/>
+      <c r="AN8" s="69"/>
+      <c r="AO8" s="69"/>
+      <c r="AP8" s="81"/>
+      <c r="AQ8" s="68"/>
+      <c r="AR8" s="69"/>
+      <c r="AS8" s="69"/>
+      <c r="AT8" s="69"/>
+      <c r="AU8" s="69"/>
+      <c r="AV8" s="69"/>
+      <c r="AW8" s="69"/>
+      <c r="AX8" s="69"/>
+      <c r="AY8" s="69"/>
+      <c r="AZ8" s="69"/>
+      <c r="BA8" s="69"/>
+      <c r="BB8" s="69"/>
+      <c r="BC8" s="69"/>
+      <c r="BD8" s="69"/>
+      <c r="BE8" s="70"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="73"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="88"/>
-      <c r="L9" s="88"/>
-      <c r="M9" s="88"/>
-      <c r="N9" s="89"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="81"/>
-      <c r="AB9" s="81"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-      <c r="AG9" s="81"/>
-      <c r="AH9" s="81"/>
-      <c r="AI9" s="81"/>
-      <c r="AJ9" s="81"/>
-      <c r="AK9" s="81"/>
-      <c r="AL9" s="81"/>
-      <c r="AM9" s="81"/>
-      <c r="AN9" s="81"/>
-      <c r="AO9" s="81"/>
-      <c r="AP9" s="82"/>
-      <c r="AQ9" s="86"/>
-      <c r="AR9" s="81"/>
-      <c r="AS9" s="81"/>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="81"/>
-      <c r="AV9" s="81"/>
-      <c r="AW9" s="81"/>
-      <c r="AX9" s="81"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="81"/>
-      <c r="BA9" s="81"/>
-      <c r="BB9" s="81"/>
-      <c r="BC9" s="81"/>
-      <c r="BD9" s="81"/>
-      <c r="BE9" s="87"/>
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="69"/>
+      <c r="Q9" s="69"/>
+      <c r="R9" s="69"/>
+      <c r="S9" s="69"/>
+      <c r="T9" s="69"/>
+      <c r="U9" s="69"/>
+      <c r="V9" s="69"/>
+      <c r="W9" s="69"/>
+      <c r="X9" s="69"/>
+      <c r="Y9" s="69"/>
+      <c r="Z9" s="69"/>
+      <c r="AA9" s="69"/>
+      <c r="AB9" s="69"/>
+      <c r="AC9" s="69"/>
+      <c r="AD9" s="69"/>
+      <c r="AE9" s="69"/>
+      <c r="AF9" s="69"/>
+      <c r="AG9" s="69"/>
+      <c r="AH9" s="69"/>
+      <c r="AI9" s="69"/>
+      <c r="AJ9" s="69"/>
+      <c r="AK9" s="69"/>
+      <c r="AL9" s="69"/>
+      <c r="AM9" s="69"/>
+      <c r="AN9" s="69"/>
+      <c r="AO9" s="69"/>
+      <c r="AP9" s="81"/>
+      <c r="AQ9" s="68"/>
+      <c r="AR9" s="69"/>
+      <c r="AS9" s="69"/>
+      <c r="AT9" s="69"/>
+      <c r="AU9" s="69"/>
+      <c r="AV9" s="69"/>
+      <c r="AW9" s="69"/>
+      <c r="AX9" s="69"/>
+      <c r="AY9" s="69"/>
+      <c r="AZ9" s="69"/>
+      <c r="BA9" s="69"/>
+      <c r="BB9" s="69"/>
+      <c r="BC9" s="69"/>
+      <c r="BD9" s="69"/>
+      <c r="BE9" s="70"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="81"/>
-      <c r="AJ10" s="81"/>
-      <c r="AK10" s="81"/>
-      <c r="AL10" s="81"/>
-      <c r="AM10" s="81"/>
-      <c r="AN10" s="81"/>
-      <c r="AO10" s="81"/>
-      <c r="AP10" s="82"/>
-      <c r="AQ10" s="86"/>
-      <c r="AR10" s="81"/>
-      <c r="AS10" s="81"/>
-      <c r="AT10" s="81"/>
-      <c r="AU10" s="81"/>
-      <c r="AV10" s="81"/>
-      <c r="AW10" s="81"/>
-      <c r="AX10" s="81"/>
-      <c r="AY10" s="81"/>
-      <c r="AZ10" s="81"/>
-      <c r="BA10" s="81"/>
-      <c r="BB10" s="81"/>
-      <c r="BC10" s="81"/>
-      <c r="BD10" s="81"/>
-      <c r="BE10" s="87"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69"/>
+      <c r="U10" s="69"/>
+      <c r="V10" s="69"/>
+      <c r="W10" s="69"/>
+      <c r="X10" s="69"/>
+      <c r="Y10" s="69"/>
+      <c r="Z10" s="69"/>
+      <c r="AA10" s="69"/>
+      <c r="AB10" s="69"/>
+      <c r="AC10" s="69"/>
+      <c r="AD10" s="69"/>
+      <c r="AE10" s="69"/>
+      <c r="AF10" s="69"/>
+      <c r="AG10" s="69"/>
+      <c r="AH10" s="69"/>
+      <c r="AI10" s="69"/>
+      <c r="AJ10" s="69"/>
+      <c r="AK10" s="69"/>
+      <c r="AL10" s="69"/>
+      <c r="AM10" s="69"/>
+      <c r="AN10" s="69"/>
+      <c r="AO10" s="69"/>
+      <c r="AP10" s="81"/>
+      <c r="AQ10" s="68"/>
+      <c r="AR10" s="69"/>
+      <c r="AS10" s="69"/>
+      <c r="AT10" s="69"/>
+      <c r="AU10" s="69"/>
+      <c r="AV10" s="69"/>
+      <c r="AW10" s="69"/>
+      <c r="AX10" s="69"/>
+      <c r="AY10" s="69"/>
+      <c r="AZ10" s="69"/>
+      <c r="BA10" s="69"/>
+      <c r="BB10" s="69"/>
+      <c r="BC10" s="69"/>
+      <c r="BD10" s="69"/>
+      <c r="BE10" s="70"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="89"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="81"/>
-      <c r="AJ11" s="81"/>
-      <c r="AK11" s="81"/>
-      <c r="AL11" s="81"/>
-      <c r="AM11" s="81"/>
-      <c r="AN11" s="81"/>
-      <c r="AO11" s="81"/>
-      <c r="AP11" s="82"/>
-      <c r="AQ11" s="86"/>
-      <c r="AR11" s="81"/>
-      <c r="AS11" s="81"/>
-      <c r="AT11" s="81"/>
-      <c r="AU11" s="81"/>
-      <c r="AV11" s="81"/>
-      <c r="AW11" s="81"/>
-      <c r="AX11" s="81"/>
-      <c r="AY11" s="81"/>
-      <c r="AZ11" s="81"/>
-      <c r="BA11" s="81"/>
-      <c r="BB11" s="81"/>
-      <c r="BC11" s="81"/>
-      <c r="BD11" s="81"/>
-      <c r="BE11" s="87"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
+      <c r="W11" s="69"/>
+      <c r="X11" s="69"/>
+      <c r="Y11" s="69"/>
+      <c r="Z11" s="69"/>
+      <c r="AA11" s="69"/>
+      <c r="AB11" s="69"/>
+      <c r="AC11" s="69"/>
+      <c r="AD11" s="69"/>
+      <c r="AE11" s="69"/>
+      <c r="AF11" s="69"/>
+      <c r="AG11" s="69"/>
+      <c r="AH11" s="69"/>
+      <c r="AI11" s="69"/>
+      <c r="AJ11" s="69"/>
+      <c r="AK11" s="69"/>
+      <c r="AL11" s="69"/>
+      <c r="AM11" s="69"/>
+      <c r="AN11" s="69"/>
+      <c r="AO11" s="69"/>
+      <c r="AP11" s="81"/>
+      <c r="AQ11" s="68"/>
+      <c r="AR11" s="69"/>
+      <c r="AS11" s="69"/>
+      <c r="AT11" s="69"/>
+      <c r="AU11" s="69"/>
+      <c r="AV11" s="69"/>
+      <c r="AW11" s="69"/>
+      <c r="AX11" s="69"/>
+      <c r="AY11" s="69"/>
+      <c r="AZ11" s="69"/>
+      <c r="BA11" s="69"/>
+      <c r="BB11" s="69"/>
+      <c r="BC11" s="69"/>
+      <c r="BD11" s="69"/>
+      <c r="BE11" s="70"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="88"/>
-      <c r="L12" s="88"/>
-      <c r="M12" s="88"/>
-      <c r="N12" s="89"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="81"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="81"/>
-      <c r="AI12" s="81"/>
-      <c r="AJ12" s="81"/>
-      <c r="AK12" s="81"/>
-      <c r="AL12" s="81"/>
-      <c r="AM12" s="81"/>
-      <c r="AN12" s="81"/>
-      <c r="AO12" s="81"/>
-      <c r="AP12" s="82"/>
-      <c r="AQ12" s="86"/>
-      <c r="AR12" s="81"/>
-      <c r="AS12" s="81"/>
-      <c r="AT12" s="81"/>
-      <c r="AU12" s="81"/>
-      <c r="AV12" s="81"/>
-      <c r="AW12" s="81"/>
-      <c r="AX12" s="81"/>
-      <c r="AY12" s="81"/>
-      <c r="AZ12" s="81"/>
-      <c r="BA12" s="81"/>
-      <c r="BB12" s="81"/>
-      <c r="BC12" s="81"/>
-      <c r="BD12" s="81"/>
-      <c r="BE12" s="87"/>
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="69"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="69"/>
+      <c r="Y12" s="69"/>
+      <c r="Z12" s="69"/>
+      <c r="AA12" s="69"/>
+      <c r="AB12" s="69"/>
+      <c r="AC12" s="69"/>
+      <c r="AD12" s="69"/>
+      <c r="AE12" s="69"/>
+      <c r="AF12" s="69"/>
+      <c r="AG12" s="69"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="69"/>
+      <c r="AJ12" s="69"/>
+      <c r="AK12" s="69"/>
+      <c r="AL12" s="69"/>
+      <c r="AM12" s="69"/>
+      <c r="AN12" s="69"/>
+      <c r="AO12" s="69"/>
+      <c r="AP12" s="81"/>
+      <c r="AQ12" s="68"/>
+      <c r="AR12" s="69"/>
+      <c r="AS12" s="69"/>
+      <c r="AT12" s="69"/>
+      <c r="AU12" s="69"/>
+      <c r="AV12" s="69"/>
+      <c r="AW12" s="69"/>
+      <c r="AX12" s="69"/>
+      <c r="AY12" s="69"/>
+      <c r="AZ12" s="69"/>
+      <c r="BA12" s="69"/>
+      <c r="BB12" s="69"/>
+      <c r="BC12" s="69"/>
+      <c r="BD12" s="69"/>
+      <c r="BE12" s="70"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="73"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="80"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="81"/>
-      <c r="AJ13" s="81"/>
-      <c r="AK13" s="81"/>
-      <c r="AL13" s="81"/>
-      <c r="AM13" s="81"/>
-      <c r="AN13" s="81"/>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="82"/>
-      <c r="AQ13" s="86"/>
-      <c r="AR13" s="81"/>
-      <c r="AS13" s="81"/>
-      <c r="AT13" s="81"/>
-      <c r="AU13" s="81"/>
-      <c r="AV13" s="81"/>
-      <c r="AW13" s="81"/>
-      <c r="AX13" s="81"/>
-      <c r="AY13" s="81"/>
-      <c r="AZ13" s="81"/>
-      <c r="BA13" s="81"/>
-      <c r="BB13" s="81"/>
-      <c r="BC13" s="81"/>
-      <c r="BD13" s="81"/>
-      <c r="BE13" s="87"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="69"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="69"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="69"/>
+      <c r="Y13" s="69"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="69"/>
+      <c r="AB13" s="69"/>
+      <c r="AC13" s="69"/>
+      <c r="AD13" s="69"/>
+      <c r="AE13" s="69"/>
+      <c r="AF13" s="69"/>
+      <c r="AG13" s="69"/>
+      <c r="AH13" s="69"/>
+      <c r="AI13" s="69"/>
+      <c r="AJ13" s="69"/>
+      <c r="AK13" s="69"/>
+      <c r="AL13" s="69"/>
+      <c r="AM13" s="69"/>
+      <c r="AN13" s="69"/>
+      <c r="AO13" s="69"/>
+      <c r="AP13" s="81"/>
+      <c r="AQ13" s="68"/>
+      <c r="AR13" s="69"/>
+      <c r="AS13" s="69"/>
+      <c r="AT13" s="69"/>
+      <c r="AU13" s="69"/>
+      <c r="AV13" s="69"/>
+      <c r="AW13" s="69"/>
+      <c r="AX13" s="69"/>
+      <c r="AY13" s="69"/>
+      <c r="AZ13" s="69"/>
+      <c r="BA13" s="69"/>
+      <c r="BB13" s="69"/>
+      <c r="BC13" s="69"/>
+      <c r="BD13" s="69"/>
+      <c r="BE13" s="70"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="73"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="81"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-      <c r="AI14" s="81"/>
-      <c r="AJ14" s="81"/>
-      <c r="AK14" s="81"/>
-      <c r="AL14" s="81"/>
-      <c r="AM14" s="81"/>
-      <c r="AN14" s="81"/>
-      <c r="AO14" s="81"/>
-      <c r="AP14" s="82"/>
-      <c r="AQ14" s="86"/>
-      <c r="AR14" s="81"/>
-      <c r="AS14" s="81"/>
-      <c r="AT14" s="81"/>
-      <c r="AU14" s="81"/>
-      <c r="AV14" s="81"/>
-      <c r="AW14" s="81"/>
-      <c r="AX14" s="81"/>
-      <c r="AY14" s="81"/>
-      <c r="AZ14" s="81"/>
-      <c r="BA14" s="81"/>
-      <c r="BB14" s="81"/>
-      <c r="BC14" s="81"/>
-      <c r="BD14" s="81"/>
-      <c r="BE14" s="87"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="69"/>
+      <c r="X14" s="69"/>
+      <c r="Y14" s="69"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="69"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="69"/>
+      <c r="AE14" s="69"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="69"/>
+      <c r="AL14" s="69"/>
+      <c r="AM14" s="69"/>
+      <c r="AN14" s="69"/>
+      <c r="AO14" s="69"/>
+      <c r="AP14" s="81"/>
+      <c r="AQ14" s="68"/>
+      <c r="AR14" s="69"/>
+      <c r="AS14" s="69"/>
+      <c r="AT14" s="69"/>
+      <c r="AU14" s="69"/>
+      <c r="AV14" s="69"/>
+      <c r="AW14" s="69"/>
+      <c r="AX14" s="69"/>
+      <c r="AY14" s="69"/>
+      <c r="AZ14" s="69"/>
+      <c r="BA14" s="69"/>
+      <c r="BB14" s="69"/>
+      <c r="BC14" s="69"/>
+      <c r="BD14" s="69"/>
+      <c r="BE14" s="70"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="73"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AA15" s="81"/>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-      <c r="AI15" s="81"/>
-      <c r="AJ15" s="81"/>
-      <c r="AK15" s="81"/>
-      <c r="AL15" s="81"/>
-      <c r="AM15" s="81"/>
-      <c r="AN15" s="81"/>
-      <c r="AO15" s="81"/>
-      <c r="AP15" s="82"/>
-      <c r="AQ15" s="86"/>
-      <c r="AR15" s="81"/>
-      <c r="AS15" s="81"/>
-      <c r="AT15" s="81"/>
-      <c r="AU15" s="81"/>
-      <c r="AV15" s="81"/>
-      <c r="AW15" s="81"/>
-      <c r="AX15" s="81"/>
-      <c r="AY15" s="81"/>
-      <c r="AZ15" s="81"/>
-      <c r="BA15" s="81"/>
-      <c r="BB15" s="81"/>
-      <c r="BC15" s="81"/>
-      <c r="BD15" s="81"/>
-      <c r="BE15" s="87"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="69"/>
+      <c r="AE15" s="69"/>
+      <c r="AF15" s="69"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="69"/>
+      <c r="AK15" s="69"/>
+      <c r="AL15" s="69"/>
+      <c r="AM15" s="69"/>
+      <c r="AN15" s="69"/>
+      <c r="AO15" s="69"/>
+      <c r="AP15" s="81"/>
+      <c r="AQ15" s="68"/>
+      <c r="AR15" s="69"/>
+      <c r="AS15" s="69"/>
+      <c r="AT15" s="69"/>
+      <c r="AU15" s="69"/>
+      <c r="AV15" s="69"/>
+      <c r="AW15" s="69"/>
+      <c r="AX15" s="69"/>
+      <c r="AY15" s="69"/>
+      <c r="AZ15" s="69"/>
+      <c r="BA15" s="69"/>
+      <c r="BB15" s="69"/>
+      <c r="BC15" s="69"/>
+      <c r="BD15" s="69"/>
+      <c r="BE15" s="70"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="73"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="88"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="89"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="81"/>
-      <c r="AJ16" s="81"/>
-      <c r="AK16" s="81"/>
-      <c r="AL16" s="81"/>
-      <c r="AM16" s="81"/>
-      <c r="AN16" s="81"/>
-      <c r="AO16" s="81"/>
-      <c r="AP16" s="82"/>
-      <c r="AQ16" s="86"/>
-      <c r="AR16" s="81"/>
-      <c r="AS16" s="81"/>
-      <c r="AT16" s="81"/>
-      <c r="AU16" s="81"/>
-      <c r="AV16" s="81"/>
-      <c r="AW16" s="81"/>
-      <c r="AX16" s="81"/>
-      <c r="AY16" s="81"/>
-      <c r="AZ16" s="81"/>
-      <c r="BA16" s="81"/>
-      <c r="BB16" s="81"/>
-      <c r="BC16" s="81"/>
-      <c r="BD16" s="81"/>
-      <c r="BE16" s="87"/>
+      <c r="A16" s="99"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="69"/>
+      <c r="Y16" s="69"/>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="69"/>
+      <c r="AB16" s="69"/>
+      <c r="AC16" s="69"/>
+      <c r="AD16" s="69"/>
+      <c r="AE16" s="69"/>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="69"/>
+      <c r="AK16" s="69"/>
+      <c r="AL16" s="69"/>
+      <c r="AM16" s="69"/>
+      <c r="AN16" s="69"/>
+      <c r="AO16" s="69"/>
+      <c r="AP16" s="81"/>
+      <c r="AQ16" s="68"/>
+      <c r="AR16" s="69"/>
+      <c r="AS16" s="69"/>
+      <c r="AT16" s="69"/>
+      <c r="AU16" s="69"/>
+      <c r="AV16" s="69"/>
+      <c r="AW16" s="69"/>
+      <c r="AX16" s="69"/>
+      <c r="AY16" s="69"/>
+      <c r="AZ16" s="69"/>
+      <c r="BA16" s="69"/>
+      <c r="BB16" s="69"/>
+      <c r="BC16" s="69"/>
+      <c r="BD16" s="69"/>
+      <c r="BE16" s="70"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="73"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="89"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="82"/>
-      <c r="AQ17" s="86"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="81"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="81"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="81"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="87"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="69"/>
+      <c r="AE17" s="69"/>
+      <c r="AF17" s="69"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="69"/>
+      <c r="AK17" s="69"/>
+      <c r="AL17" s="69"/>
+      <c r="AM17" s="69"/>
+      <c r="AN17" s="69"/>
+      <c r="AO17" s="69"/>
+      <c r="AP17" s="81"/>
+      <c r="AQ17" s="68"/>
+      <c r="AR17" s="69"/>
+      <c r="AS17" s="69"/>
+      <c r="AT17" s="69"/>
+      <c r="AU17" s="69"/>
+      <c r="AV17" s="69"/>
+      <c r="AW17" s="69"/>
+      <c r="AX17" s="69"/>
+      <c r="AY17" s="69"/>
+      <c r="AZ17" s="69"/>
+      <c r="BA17" s="69"/>
+      <c r="BB17" s="69"/>
+      <c r="BC17" s="69"/>
+      <c r="BD17" s="69"/>
+      <c r="BE17" s="70"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="73"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="89"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="81"/>
-      <c r="AJ18" s="81"/>
-      <c r="AK18" s="81"/>
-      <c r="AL18" s="81"/>
-      <c r="AM18" s="81"/>
-      <c r="AN18" s="81"/>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="82"/>
-      <c r="AQ18" s="86"/>
-      <c r="AR18" s="81"/>
-      <c r="AS18" s="81"/>
-      <c r="AT18" s="81"/>
-      <c r="AU18" s="81"/>
-      <c r="AV18" s="81"/>
-      <c r="AW18" s="81"/>
-      <c r="AX18" s="81"/>
-      <c r="AY18" s="81"/>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81"/>
-      <c r="BB18" s="81"/>
-      <c r="BC18" s="81"/>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="87"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="69"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="69"/>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="69"/>
+      <c r="AK18" s="69"/>
+      <c r="AL18" s="69"/>
+      <c r="AM18" s="69"/>
+      <c r="AN18" s="69"/>
+      <c r="AO18" s="69"/>
+      <c r="AP18" s="81"/>
+      <c r="AQ18" s="68"/>
+      <c r="AR18" s="69"/>
+      <c r="AS18" s="69"/>
+      <c r="AT18" s="69"/>
+      <c r="AU18" s="69"/>
+      <c r="AV18" s="69"/>
+      <c r="AW18" s="69"/>
+      <c r="AX18" s="69"/>
+      <c r="AY18" s="69"/>
+      <c r="AZ18" s="69"/>
+      <c r="BA18" s="69"/>
+      <c r="BB18" s="69"/>
+      <c r="BC18" s="69"/>
+      <c r="BD18" s="69"/>
+      <c r="BE18" s="70"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="73"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="89"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="81"/>
-      <c r="AJ19" s="81"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="81"/>
-      <c r="AM19" s="81"/>
-      <c r="AN19" s="81"/>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="82"/>
-      <c r="AQ19" s="86"/>
-      <c r="AR19" s="81"/>
-      <c r="AS19" s="81"/>
-      <c r="AT19" s="81"/>
-      <c r="AU19" s="81"/>
-      <c r="AV19" s="81"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="81"/>
-      <c r="AY19" s="81"/>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81"/>
-      <c r="BB19" s="81"/>
-      <c r="BC19" s="81"/>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="87"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="69"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="69"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="69"/>
+      <c r="AE19" s="69"/>
+      <c r="AF19" s="69"/>
+      <c r="AG19" s="69"/>
+      <c r="AH19" s="69"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="69"/>
+      <c r="AK19" s="69"/>
+      <c r="AL19" s="69"/>
+      <c r="AM19" s="69"/>
+      <c r="AN19" s="69"/>
+      <c r="AO19" s="69"/>
+      <c r="AP19" s="81"/>
+      <c r="AQ19" s="68"/>
+      <c r="AR19" s="69"/>
+      <c r="AS19" s="69"/>
+      <c r="AT19" s="69"/>
+      <c r="AU19" s="69"/>
+      <c r="AV19" s="69"/>
+      <c r="AW19" s="69"/>
+      <c r="AX19" s="69"/>
+      <c r="AY19" s="69"/>
+      <c r="AZ19" s="69"/>
+      <c r="BA19" s="69"/>
+      <c r="BB19" s="69"/>
+      <c r="BC19" s="69"/>
+      <c r="BD19" s="69"/>
+      <c r="BE19" s="70"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="73"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
-      <c r="T20" s="81"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
-      <c r="X20" s="81"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
-      <c r="AJ20" s="81"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="81"/>
-      <c r="AM20" s="81"/>
-      <c r="AN20" s="81"/>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="86"/>
-      <c r="AR20" s="81"/>
-      <c r="AS20" s="81"/>
-      <c r="AT20" s="81"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="81"/>
-      <c r="AW20" s="81"/>
-      <c r="AX20" s="81"/>
-      <c r="AY20" s="81"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81"/>
-      <c r="BB20" s="81"/>
-      <c r="BC20" s="81"/>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="87"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="69"/>
+      <c r="AH20" s="69"/>
+      <c r="AI20" s="69"/>
+      <c r="AJ20" s="69"/>
+      <c r="AK20" s="69"/>
+      <c r="AL20" s="69"/>
+      <c r="AM20" s="69"/>
+      <c r="AN20" s="69"/>
+      <c r="AO20" s="69"/>
+      <c r="AP20" s="81"/>
+      <c r="AQ20" s="68"/>
+      <c r="AR20" s="69"/>
+      <c r="AS20" s="69"/>
+      <c r="AT20" s="69"/>
+      <c r="AU20" s="69"/>
+      <c r="AV20" s="69"/>
+      <c r="AW20" s="69"/>
+      <c r="AX20" s="69"/>
+      <c r="AY20" s="69"/>
+      <c r="AZ20" s="69"/>
+      <c r="BA20" s="69"/>
+      <c r="BB20" s="69"/>
+      <c r="BC20" s="69"/>
+      <c r="BD20" s="69"/>
+      <c r="BE20" s="70"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="73"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="88"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="89"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-      <c r="T21" s="81"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="81"/>
-      <c r="Y21" s="81"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="81"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="81"/>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="81"/>
-      <c r="AJ21" s="81"/>
-      <c r="AK21" s="81"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="81"/>
-      <c r="AN21" s="81"/>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="82"/>
-      <c r="AQ21" s="86"/>
-      <c r="AR21" s="81"/>
-      <c r="AS21" s="81"/>
-      <c r="AT21" s="81"/>
-      <c r="AU21" s="81"/>
-      <c r="AV21" s="81"/>
-      <c r="AW21" s="81"/>
-      <c r="AX21" s="81"/>
-      <c r="AY21" s="81"/>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81"/>
-      <c r="BB21" s="81"/>
-      <c r="BC21" s="81"/>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="87"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="69"/>
+      <c r="V21" s="69"/>
+      <c r="W21" s="69"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="69"/>
+      <c r="AC21" s="69"/>
+      <c r="AD21" s="69"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="69"/>
+      <c r="AG21" s="69"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="69"/>
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="69"/>
+      <c r="AL21" s="69"/>
+      <c r="AM21" s="69"/>
+      <c r="AN21" s="69"/>
+      <c r="AO21" s="69"/>
+      <c r="AP21" s="81"/>
+      <c r="AQ21" s="68"/>
+      <c r="AR21" s="69"/>
+      <c r="AS21" s="69"/>
+      <c r="AT21" s="69"/>
+      <c r="AU21" s="69"/>
+      <c r="AV21" s="69"/>
+      <c r="AW21" s="69"/>
+      <c r="AX21" s="69"/>
+      <c r="AY21" s="69"/>
+      <c r="AZ21" s="69"/>
+      <c r="BA21" s="69"/>
+      <c r="BB21" s="69"/>
+      <c r="BC21" s="69"/>
+      <c r="BD21" s="69"/>
+      <c r="BE21" s="70"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="73"/>
-      <c r="B22" s="74"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="88"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
-      <c r="T22" s="81"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="81"/>
-      <c r="AJ22" s="81"/>
-      <c r="AK22" s="81"/>
-      <c r="AL22" s="81"/>
-      <c r="AM22" s="81"/>
-      <c r="AN22" s="81"/>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="82"/>
-      <c r="AQ22" s="86"/>
-      <c r="AR22" s="81"/>
-      <c r="AS22" s="81"/>
-      <c r="AT22" s="81"/>
-      <c r="AU22" s="81"/>
-      <c r="AV22" s="81"/>
-      <c r="AW22" s="81"/>
-      <c r="AX22" s="81"/>
-      <c r="AY22" s="81"/>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81"/>
-      <c r="BB22" s="81"/>
-      <c r="BC22" s="81"/>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="87"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="101"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="69"/>
+      <c r="V22" s="69"/>
+      <c r="W22" s="69"/>
+      <c r="X22" s="69"/>
+      <c r="Y22" s="69"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="69"/>
+      <c r="AD22" s="69"/>
+      <c r="AE22" s="69"/>
+      <c r="AF22" s="69"/>
+      <c r="AG22" s="69"/>
+      <c r="AH22" s="69"/>
+      <c r="AI22" s="69"/>
+      <c r="AJ22" s="69"/>
+      <c r="AK22" s="69"/>
+      <c r="AL22" s="69"/>
+      <c r="AM22" s="69"/>
+      <c r="AN22" s="69"/>
+      <c r="AO22" s="69"/>
+      <c r="AP22" s="81"/>
+      <c r="AQ22" s="68"/>
+      <c r="AR22" s="69"/>
+      <c r="AS22" s="69"/>
+      <c r="AT22" s="69"/>
+      <c r="AU22" s="69"/>
+      <c r="AV22" s="69"/>
+      <c r="AW22" s="69"/>
+      <c r="AX22" s="69"/>
+      <c r="AY22" s="69"/>
+      <c r="AZ22" s="69"/>
+      <c r="BA22" s="69"/>
+      <c r="BB22" s="69"/>
+      <c r="BC22" s="69"/>
+      <c r="BD22" s="69"/>
+      <c r="BE22" s="70"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="73"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="81"/>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="81"/>
-      <c r="AJ23" s="81"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="81"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="82"/>
-      <c r="AQ23" s="86"/>
-      <c r="AR23" s="81"/>
-      <c r="AS23" s="81"/>
-      <c r="AT23" s="81"/>
-      <c r="AU23" s="81"/>
-      <c r="AV23" s="81"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="81"/>
-      <c r="AY23" s="81"/>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81"/>
-      <c r="BB23" s="81"/>
-      <c r="BC23" s="81"/>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="87"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="69"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="69"/>
+      <c r="AC23" s="69"/>
+      <c r="AD23" s="69"/>
+      <c r="AE23" s="69"/>
+      <c r="AF23" s="69"/>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="69"/>
+      <c r="AK23" s="69"/>
+      <c r="AL23" s="69"/>
+      <c r="AM23" s="69"/>
+      <c r="AN23" s="69"/>
+      <c r="AO23" s="69"/>
+      <c r="AP23" s="81"/>
+      <c r="AQ23" s="68"/>
+      <c r="AR23" s="69"/>
+      <c r="AS23" s="69"/>
+      <c r="AT23" s="69"/>
+      <c r="AU23" s="69"/>
+      <c r="AV23" s="69"/>
+      <c r="AW23" s="69"/>
+      <c r="AX23" s="69"/>
+      <c r="AY23" s="69"/>
+      <c r="AZ23" s="69"/>
+      <c r="BA23" s="69"/>
+      <c r="BB23" s="69"/>
+      <c r="BC23" s="69"/>
+      <c r="BD23" s="69"/>
+      <c r="BE23" s="70"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="73"/>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="80"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
-      <c r="T24" s="81"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="81"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="81"/>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="81"/>
-      <c r="AJ24" s="81"/>
-      <c r="AK24" s="81"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="81"/>
-      <c r="AN24" s="81"/>
-      <c r="AO24" s="81"/>
-      <c r="AP24" s="82"/>
-      <c r="AQ24" s="86"/>
-      <c r="AR24" s="81"/>
-      <c r="AS24" s="81"/>
-      <c r="AT24" s="81"/>
-      <c r="AU24" s="81"/>
-      <c r="AV24" s="81"/>
-      <c r="AW24" s="81"/>
-      <c r="AX24" s="81"/>
-      <c r="AY24" s="81"/>
-      <c r="AZ24" s="81"/>
-      <c r="BA24" s="81"/>
-      <c r="BB24" s="81"/>
-      <c r="BC24" s="81"/>
-      <c r="BD24" s="81"/>
-      <c r="BE24" s="87"/>
+      <c r="A24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="69"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="69"/>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="69"/>
+      <c r="AI24" s="69"/>
+      <c r="AJ24" s="69"/>
+      <c r="AK24" s="69"/>
+      <c r="AL24" s="69"/>
+      <c r="AM24" s="69"/>
+      <c r="AN24" s="69"/>
+      <c r="AO24" s="69"/>
+      <c r="AP24" s="81"/>
+      <c r="AQ24" s="68"/>
+      <c r="AR24" s="69"/>
+      <c r="AS24" s="69"/>
+      <c r="AT24" s="69"/>
+      <c r="AU24" s="69"/>
+      <c r="AV24" s="69"/>
+      <c r="AW24" s="69"/>
+      <c r="AX24" s="69"/>
+      <c r="AY24" s="69"/>
+      <c r="AZ24" s="69"/>
+      <c r="BA24" s="69"/>
+      <c r="BB24" s="69"/>
+      <c r="BC24" s="69"/>
+      <c r="BD24" s="69"/>
+      <c r="BE24" s="70"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="73"/>
-      <c r="B25" s="74"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="88"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="88"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="81"/>
-      <c r="X25" s="81"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="81"/>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="81"/>
-      <c r="AN25" s="81"/>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="82"/>
-      <c r="AQ25" s="86"/>
-      <c r="AR25" s="81"/>
-      <c r="AS25" s="81"/>
-      <c r="AT25" s="81"/>
-      <c r="AU25" s="81"/>
-      <c r="AV25" s="81"/>
-      <c r="AW25" s="81"/>
-      <c r="AX25" s="81"/>
-      <c r="AY25" s="81"/>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="87"/>
+      <c r="A25" s="99"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="101"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="78"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="69"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="69"/>
+      <c r="AE25" s="69"/>
+      <c r="AF25" s="69"/>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="69"/>
+      <c r="AI25" s="69"/>
+      <c r="AJ25" s="69"/>
+      <c r="AK25" s="69"/>
+      <c r="AL25" s="69"/>
+      <c r="AM25" s="69"/>
+      <c r="AN25" s="69"/>
+      <c r="AO25" s="69"/>
+      <c r="AP25" s="81"/>
+      <c r="AQ25" s="68"/>
+      <c r="AR25" s="69"/>
+      <c r="AS25" s="69"/>
+      <c r="AT25" s="69"/>
+      <c r="AU25" s="69"/>
+      <c r="AV25" s="69"/>
+      <c r="AW25" s="69"/>
+      <c r="AX25" s="69"/>
+      <c r="AY25" s="69"/>
+      <c r="AZ25" s="69"/>
+      <c r="BA25" s="69"/>
+      <c r="BB25" s="69"/>
+      <c r="BC25" s="69"/>
+      <c r="BD25" s="69"/>
+      <c r="BE25" s="70"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="73"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="81"/>
-      <c r="T26" s="81"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="81"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="81"/>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="81"/>
-      <c r="AJ26" s="81"/>
-      <c r="AK26" s="81"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="81"/>
-      <c r="AN26" s="81"/>
-      <c r="AO26" s="81"/>
-      <c r="AP26" s="82"/>
-      <c r="AQ26" s="86"/>
-      <c r="AR26" s="81"/>
-      <c r="AS26" s="81"/>
-      <c r="AT26" s="81"/>
-      <c r="AU26" s="81"/>
-      <c r="AV26" s="81"/>
-      <c r="AW26" s="81"/>
-      <c r="AX26" s="81"/>
-      <c r="AY26" s="81"/>
-      <c r="AZ26" s="81"/>
-      <c r="BA26" s="81"/>
-      <c r="BB26" s="81"/>
-      <c r="BC26" s="81"/>
-      <c r="BD26" s="81"/>
-      <c r="BE26" s="87"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="100"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="69"/>
+      <c r="U26" s="69"/>
+      <c r="V26" s="69"/>
+      <c r="W26" s="69"/>
+      <c r="X26" s="69"/>
+      <c r="Y26" s="69"/>
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="69"/>
+      <c r="AB26" s="69"/>
+      <c r="AC26" s="69"/>
+      <c r="AD26" s="69"/>
+      <c r="AE26" s="69"/>
+      <c r="AF26" s="69"/>
+      <c r="AG26" s="69"/>
+      <c r="AH26" s="69"/>
+      <c r="AI26" s="69"/>
+      <c r="AJ26" s="69"/>
+      <c r="AK26" s="69"/>
+      <c r="AL26" s="69"/>
+      <c r="AM26" s="69"/>
+      <c r="AN26" s="69"/>
+      <c r="AO26" s="69"/>
+      <c r="AP26" s="81"/>
+      <c r="AQ26" s="68"/>
+      <c r="AR26" s="69"/>
+      <c r="AS26" s="69"/>
+      <c r="AT26" s="69"/>
+      <c r="AU26" s="69"/>
+      <c r="AV26" s="69"/>
+      <c r="AW26" s="69"/>
+      <c r="AX26" s="69"/>
+      <c r="AY26" s="69"/>
+      <c r="AZ26" s="69"/>
+      <c r="BA26" s="69"/>
+      <c r="BB26" s="69"/>
+      <c r="BC26" s="69"/>
+      <c r="BD26" s="69"/>
+      <c r="BE26" s="70"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="73"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="80"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="81"/>
-      <c r="T27" s="81"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="81"/>
-      <c r="W27" s="81"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="81"/>
-      <c r="AJ27" s="81"/>
-      <c r="AK27" s="81"/>
-      <c r="AL27" s="81"/>
-      <c r="AM27" s="81"/>
-      <c r="AN27" s="81"/>
-      <c r="AO27" s="81"/>
-      <c r="AP27" s="82"/>
-      <c r="AQ27" s="86"/>
-      <c r="AR27" s="81"/>
-      <c r="AS27" s="81"/>
-      <c r="AT27" s="81"/>
-      <c r="AU27" s="81"/>
-      <c r="AV27" s="81"/>
-      <c r="AW27" s="81"/>
-      <c r="AX27" s="81"/>
-      <c r="AY27" s="81"/>
-      <c r="AZ27" s="81"/>
-      <c r="BA27" s="81"/>
-      <c r="BB27" s="81"/>
-      <c r="BC27" s="81"/>
-      <c r="BD27" s="81"/>
-      <c r="BE27" s="87"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="69"/>
+      <c r="R27" s="69"/>
+      <c r="S27" s="69"/>
+      <c r="T27" s="69"/>
+      <c r="U27" s="69"/>
+      <c r="V27" s="69"/>
+      <c r="W27" s="69"/>
+      <c r="X27" s="69"/>
+      <c r="Y27" s="69"/>
+      <c r="Z27" s="69"/>
+      <c r="AA27" s="69"/>
+      <c r="AB27" s="69"/>
+      <c r="AC27" s="69"/>
+      <c r="AD27" s="69"/>
+      <c r="AE27" s="69"/>
+      <c r="AF27" s="69"/>
+      <c r="AG27" s="69"/>
+      <c r="AH27" s="69"/>
+      <c r="AI27" s="69"/>
+      <c r="AJ27" s="69"/>
+      <c r="AK27" s="69"/>
+      <c r="AL27" s="69"/>
+      <c r="AM27" s="69"/>
+      <c r="AN27" s="69"/>
+      <c r="AO27" s="69"/>
+      <c r="AP27" s="81"/>
+      <c r="AQ27" s="68"/>
+      <c r="AR27" s="69"/>
+      <c r="AS27" s="69"/>
+      <c r="AT27" s="69"/>
+      <c r="AU27" s="69"/>
+      <c r="AV27" s="69"/>
+      <c r="AW27" s="69"/>
+      <c r="AX27" s="69"/>
+      <c r="AY27" s="69"/>
+      <c r="AZ27" s="69"/>
+      <c r="BA27" s="69"/>
+      <c r="BB27" s="69"/>
+      <c r="BC27" s="69"/>
+      <c r="BD27" s="69"/>
+      <c r="BE27" s="70"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="73"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="75"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="81"/>
-      <c r="T28" s="81"/>
-      <c r="U28" s="81"/>
-      <c r="V28" s="81"/>
-      <c r="W28" s="81"/>
-      <c r="X28" s="81"/>
-      <c r="Y28" s="81"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="81"/>
-      <c r="AJ28" s="81"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="81"/>
-      <c r="AN28" s="81"/>
-      <c r="AO28" s="81"/>
-      <c r="AP28" s="82"/>
-      <c r="AQ28" s="86"/>
-      <c r="AR28" s="81"/>
-      <c r="AS28" s="81"/>
-      <c r="AT28" s="81"/>
-      <c r="AU28" s="81"/>
-      <c r="AV28" s="81"/>
-      <c r="AW28" s="81"/>
-      <c r="AX28" s="81"/>
-      <c r="AY28" s="81"/>
-      <c r="AZ28" s="81"/>
-      <c r="BA28" s="81"/>
-      <c r="BB28" s="81"/>
-      <c r="BC28" s="81"/>
-      <c r="BD28" s="81"/>
-      <c r="BE28" s="87"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="100"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="80"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="69"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="69"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="69"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="69"/>
+      <c r="Y28" s="69"/>
+      <c r="Z28" s="69"/>
+      <c r="AA28" s="69"/>
+      <c r="AB28" s="69"/>
+      <c r="AC28" s="69"/>
+      <c r="AD28" s="69"/>
+      <c r="AE28" s="69"/>
+      <c r="AF28" s="69"/>
+      <c r="AG28" s="69"/>
+      <c r="AH28" s="69"/>
+      <c r="AI28" s="69"/>
+      <c r="AJ28" s="69"/>
+      <c r="AK28" s="69"/>
+      <c r="AL28" s="69"/>
+      <c r="AM28" s="69"/>
+      <c r="AN28" s="69"/>
+      <c r="AO28" s="69"/>
+      <c r="AP28" s="81"/>
+      <c r="AQ28" s="68"/>
+      <c r="AR28" s="69"/>
+      <c r="AS28" s="69"/>
+      <c r="AT28" s="69"/>
+      <c r="AU28" s="69"/>
+      <c r="AV28" s="69"/>
+      <c r="AW28" s="69"/>
+      <c r="AX28" s="69"/>
+      <c r="AY28" s="69"/>
+      <c r="AZ28" s="69"/>
+      <c r="BA28" s="69"/>
+      <c r="BB28" s="69"/>
+      <c r="BC28" s="69"/>
+      <c r="BD28" s="69"/>
+      <c r="BE28" s="70"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="73"/>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="81"/>
-      <c r="S29" s="81"/>
-      <c r="T29" s="81"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="81"/>
-      <c r="W29" s="81"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="81"/>
-      <c r="AA29" s="81"/>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="81"/>
-      <c r="AJ29" s="81"/>
-      <c r="AK29" s="81"/>
-      <c r="AL29" s="81"/>
-      <c r="AM29" s="81"/>
-      <c r="AN29" s="81"/>
-      <c r="AO29" s="81"/>
-      <c r="AP29" s="82"/>
-      <c r="AQ29" s="86"/>
-      <c r="AR29" s="81"/>
-      <c r="AS29" s="81"/>
-      <c r="AT29" s="81"/>
-      <c r="AU29" s="81"/>
-      <c r="AV29" s="81"/>
-      <c r="AW29" s="81"/>
-      <c r="AX29" s="81"/>
-      <c r="AY29" s="81"/>
-      <c r="AZ29" s="81"/>
-      <c r="BA29" s="81"/>
-      <c r="BB29" s="81"/>
-      <c r="BC29" s="81"/>
-      <c r="BD29" s="81"/>
-      <c r="BE29" s="87"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+      <c r="F29" s="100"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="78"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="T29" s="69"/>
+      <c r="U29" s="69"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="69"/>
+      <c r="X29" s="69"/>
+      <c r="Y29" s="69"/>
+      <c r="Z29" s="69"/>
+      <c r="AA29" s="69"/>
+      <c r="AB29" s="69"/>
+      <c r="AC29" s="69"/>
+      <c r="AD29" s="69"/>
+      <c r="AE29" s="69"/>
+      <c r="AF29" s="69"/>
+      <c r="AG29" s="69"/>
+      <c r="AH29" s="69"/>
+      <c r="AI29" s="69"/>
+      <c r="AJ29" s="69"/>
+      <c r="AK29" s="69"/>
+      <c r="AL29" s="69"/>
+      <c r="AM29" s="69"/>
+      <c r="AN29" s="69"/>
+      <c r="AO29" s="69"/>
+      <c r="AP29" s="81"/>
+      <c r="AQ29" s="68"/>
+      <c r="AR29" s="69"/>
+      <c r="AS29" s="69"/>
+      <c r="AT29" s="69"/>
+      <c r="AU29" s="69"/>
+      <c r="AV29" s="69"/>
+      <c r="AW29" s="69"/>
+      <c r="AX29" s="69"/>
+      <c r="AY29" s="69"/>
+      <c r="AZ29" s="69"/>
+      <c r="BA29" s="69"/>
+      <c r="BB29" s="69"/>
+      <c r="BC29" s="69"/>
+      <c r="BD29" s="69"/>
+      <c r="BE29" s="70"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="73"/>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="80"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="81"/>
-      <c r="S30" s="81"/>
-      <c r="T30" s="81"/>
-      <c r="U30" s="81"/>
-      <c r="V30" s="81"/>
-      <c r="W30" s="81"/>
-      <c r="X30" s="81"/>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="81"/>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="81"/>
-      <c r="AJ30" s="81"/>
-      <c r="AK30" s="81"/>
-      <c r="AL30" s="81"/>
-      <c r="AM30" s="81"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="81"/>
-      <c r="AP30" s="82"/>
-      <c r="AQ30" s="86"/>
-      <c r="AR30" s="81"/>
-      <c r="AS30" s="81"/>
-      <c r="AT30" s="81"/>
-      <c r="AU30" s="81"/>
-      <c r="AV30" s="81"/>
-      <c r="AW30" s="81"/>
-      <c r="AX30" s="81"/>
-      <c r="AY30" s="81"/>
-      <c r="AZ30" s="81"/>
-      <c r="BA30" s="81"/>
-      <c r="BB30" s="81"/>
-      <c r="BC30" s="81"/>
-      <c r="BD30" s="81"/>
-      <c r="BE30" s="87"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="100"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="78"/>
+      <c r="P30" s="69"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="69"/>
+      <c r="S30" s="69"/>
+      <c r="T30" s="69"/>
+      <c r="U30" s="69"/>
+      <c r="V30" s="69"/>
+      <c r="W30" s="69"/>
+      <c r="X30" s="69"/>
+      <c r="Y30" s="69"/>
+      <c r="Z30" s="69"/>
+      <c r="AA30" s="69"/>
+      <c r="AB30" s="69"/>
+      <c r="AC30" s="69"/>
+      <c r="AD30" s="69"/>
+      <c r="AE30" s="69"/>
+      <c r="AF30" s="69"/>
+      <c r="AG30" s="69"/>
+      <c r="AH30" s="69"/>
+      <c r="AI30" s="69"/>
+      <c r="AJ30" s="69"/>
+      <c r="AK30" s="69"/>
+      <c r="AL30" s="69"/>
+      <c r="AM30" s="69"/>
+      <c r="AN30" s="69"/>
+      <c r="AO30" s="69"/>
+      <c r="AP30" s="81"/>
+      <c r="AQ30" s="68"/>
+      <c r="AR30" s="69"/>
+      <c r="AS30" s="69"/>
+      <c r="AT30" s="69"/>
+      <c r="AU30" s="69"/>
+      <c r="AV30" s="69"/>
+      <c r="AW30" s="69"/>
+      <c r="AX30" s="69"/>
+      <c r="AY30" s="69"/>
+      <c r="AZ30" s="69"/>
+      <c r="BA30" s="69"/>
+      <c r="BB30" s="69"/>
+      <c r="BC30" s="69"/>
+      <c r="BD30" s="69"/>
+      <c r="BE30" s="70"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="73"/>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
-      <c r="T31" s="81"/>
-      <c r="U31" s="81"/>
-      <c r="V31" s="81"/>
-      <c r="W31" s="81"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="81"/>
-      <c r="AJ31" s="81"/>
-      <c r="AK31" s="81"/>
-      <c r="AL31" s="81"/>
-      <c r="AM31" s="81"/>
-      <c r="AN31" s="81"/>
-      <c r="AO31" s="81"/>
-      <c r="AP31" s="82"/>
-      <c r="AQ31" s="86"/>
-      <c r="AR31" s="81"/>
-      <c r="AS31" s="81"/>
-      <c r="AT31" s="81"/>
-      <c r="AU31" s="81"/>
-      <c r="AV31" s="81"/>
-      <c r="AW31" s="81"/>
-      <c r="AX31" s="81"/>
-      <c r="AY31" s="81"/>
-      <c r="AZ31" s="81"/>
-      <c r="BA31" s="81"/>
-      <c r="BB31" s="81"/>
-      <c r="BC31" s="81"/>
-      <c r="BD31" s="81"/>
-      <c r="BE31" s="87"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="78"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="69"/>
+      <c r="S31" s="69"/>
+      <c r="T31" s="69"/>
+      <c r="U31" s="69"/>
+      <c r="V31" s="69"/>
+      <c r="W31" s="69"/>
+      <c r="X31" s="69"/>
+      <c r="Y31" s="69"/>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="69"/>
+      <c r="AB31" s="69"/>
+      <c r="AC31" s="69"/>
+      <c r="AD31" s="69"/>
+      <c r="AE31" s="69"/>
+      <c r="AF31" s="69"/>
+      <c r="AG31" s="69"/>
+      <c r="AH31" s="69"/>
+      <c r="AI31" s="69"/>
+      <c r="AJ31" s="69"/>
+      <c r="AK31" s="69"/>
+      <c r="AL31" s="69"/>
+      <c r="AM31" s="69"/>
+      <c r="AN31" s="69"/>
+      <c r="AO31" s="69"/>
+      <c r="AP31" s="81"/>
+      <c r="AQ31" s="68"/>
+      <c r="AR31" s="69"/>
+      <c r="AS31" s="69"/>
+      <c r="AT31" s="69"/>
+      <c r="AU31" s="69"/>
+      <c r="AV31" s="69"/>
+      <c r="AW31" s="69"/>
+      <c r="AX31" s="69"/>
+      <c r="AY31" s="69"/>
+      <c r="AZ31" s="69"/>
+      <c r="BA31" s="69"/>
+      <c r="BB31" s="69"/>
+      <c r="BC31" s="69"/>
+      <c r="BD31" s="69"/>
+      <c r="BE31" s="70"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="73"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="80"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="81"/>
-      <c r="T32" s="81"/>
-      <c r="U32" s="81"/>
-      <c r="V32" s="81"/>
-      <c r="W32" s="81"/>
-      <c r="X32" s="81"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="81"/>
-      <c r="AB32" s="81"/>
-      <c r="AC32" s="81"/>
-      <c r="AD32" s="81"/>
-      <c r="AE32" s="81"/>
-      <c r="AF32" s="81"/>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="81"/>
-      <c r="AJ32" s="81"/>
-      <c r="AK32" s="81"/>
-      <c r="AL32" s="81"/>
-      <c r="AM32" s="81"/>
-      <c r="AN32" s="81"/>
-      <c r="AO32" s="81"/>
-      <c r="AP32" s="82"/>
-      <c r="AQ32" s="86"/>
-      <c r="AR32" s="81"/>
-      <c r="AS32" s="81"/>
-      <c r="AT32" s="81"/>
-      <c r="AU32" s="81"/>
-      <c r="AV32" s="81"/>
-      <c r="AW32" s="81"/>
-      <c r="AX32" s="81"/>
-      <c r="AY32" s="81"/>
-      <c r="AZ32" s="81"/>
-      <c r="BA32" s="81"/>
-      <c r="BB32" s="81"/>
-      <c r="BC32" s="81"/>
-      <c r="BD32" s="81"/>
-      <c r="BE32" s="87"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="80"/>
+      <c r="O32" s="78"/>
+      <c r="P32" s="69"/>
+      <c r="Q32" s="69"/>
+      <c r="R32" s="69"/>
+      <c r="S32" s="69"/>
+      <c r="T32" s="69"/>
+      <c r="U32" s="69"/>
+      <c r="V32" s="69"/>
+      <c r="W32" s="69"/>
+      <c r="X32" s="69"/>
+      <c r="Y32" s="69"/>
+      <c r="Z32" s="69"/>
+      <c r="AA32" s="69"/>
+      <c r="AB32" s="69"/>
+      <c r="AC32" s="69"/>
+      <c r="AD32" s="69"/>
+      <c r="AE32" s="69"/>
+      <c r="AF32" s="69"/>
+      <c r="AG32" s="69"/>
+      <c r="AH32" s="69"/>
+      <c r="AI32" s="69"/>
+      <c r="AJ32" s="69"/>
+      <c r="AK32" s="69"/>
+      <c r="AL32" s="69"/>
+      <c r="AM32" s="69"/>
+      <c r="AN32" s="69"/>
+      <c r="AO32" s="69"/>
+      <c r="AP32" s="81"/>
+      <c r="AQ32" s="68"/>
+      <c r="AR32" s="69"/>
+      <c r="AS32" s="69"/>
+      <c r="AT32" s="69"/>
+      <c r="AU32" s="69"/>
+      <c r="AV32" s="69"/>
+      <c r="AW32" s="69"/>
+      <c r="AX32" s="69"/>
+      <c r="AY32" s="69"/>
+      <c r="AZ32" s="69"/>
+      <c r="BA32" s="69"/>
+      <c r="BB32" s="69"/>
+      <c r="BC32" s="69"/>
+      <c r="BD32" s="69"/>
+      <c r="BE32" s="70"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="73"/>
-      <c r="B33" s="74"/>
-      <c r="C33" s="74"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="89"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
-      <c r="T33" s="81"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="81"/>
-      <c r="W33" s="81"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="81"/>
-      <c r="AA33" s="81"/>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="81"/>
-      <c r="AJ33" s="81"/>
-      <c r="AK33" s="81"/>
-      <c r="AL33" s="81"/>
-      <c r="AM33" s="81"/>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="82"/>
-      <c r="AQ33" s="86"/>
-      <c r="AR33" s="81"/>
-      <c r="AS33" s="81"/>
-      <c r="AT33" s="81"/>
-      <c r="AU33" s="81"/>
-      <c r="AV33" s="81"/>
-      <c r="AW33" s="81"/>
-      <c r="AX33" s="81"/>
-      <c r="AY33" s="81"/>
-      <c r="AZ33" s="81"/>
-      <c r="BA33" s="81"/>
-      <c r="BB33" s="81"/>
-      <c r="BC33" s="81"/>
-      <c r="BD33" s="81"/>
-      <c r="BE33" s="87"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="100"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="78"/>
+      <c r="P33" s="69"/>
+      <c r="Q33" s="69"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="69"/>
+      <c r="T33" s="69"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="69"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="69"/>
+      <c r="AB33" s="69"/>
+      <c r="AC33" s="69"/>
+      <c r="AD33" s="69"/>
+      <c r="AE33" s="69"/>
+      <c r="AF33" s="69"/>
+      <c r="AG33" s="69"/>
+      <c r="AH33" s="69"/>
+      <c r="AI33" s="69"/>
+      <c r="AJ33" s="69"/>
+      <c r="AK33" s="69"/>
+      <c r="AL33" s="69"/>
+      <c r="AM33" s="69"/>
+      <c r="AN33" s="69"/>
+      <c r="AO33" s="69"/>
+      <c r="AP33" s="81"/>
+      <c r="AQ33" s="68"/>
+      <c r="AR33" s="69"/>
+      <c r="AS33" s="69"/>
+      <c r="AT33" s="69"/>
+      <c r="AU33" s="69"/>
+      <c r="AV33" s="69"/>
+      <c r="AW33" s="69"/>
+      <c r="AX33" s="69"/>
+      <c r="AY33" s="69"/>
+      <c r="AZ33" s="69"/>
+      <c r="BA33" s="69"/>
+      <c r="BB33" s="69"/>
+      <c r="BC33" s="69"/>
+      <c r="BD33" s="69"/>
+      <c r="BE33" s="70"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="73"/>
-      <c r="B34" s="74"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="89"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="81"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="81"/>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="81"/>
-      <c r="AK34" s="81"/>
-      <c r="AL34" s="81"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="82"/>
-      <c r="AQ34" s="86"/>
-      <c r="AR34" s="81"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="81"/>
-      <c r="AU34" s="81"/>
-      <c r="AV34" s="81"/>
-      <c r="AW34" s="81"/>
-      <c r="AX34" s="81"/>
-      <c r="AY34" s="81"/>
-      <c r="AZ34" s="81"/>
-      <c r="BA34" s="81"/>
-      <c r="BB34" s="81"/>
-      <c r="BC34" s="81"/>
-      <c r="BD34" s="81"/>
-      <c r="BE34" s="87"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="101"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="69"/>
+      <c r="Q34" s="69"/>
+      <c r="R34" s="69"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="69"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="69"/>
+      <c r="AH34" s="69"/>
+      <c r="AI34" s="69"/>
+      <c r="AJ34" s="69"/>
+      <c r="AK34" s="69"/>
+      <c r="AL34" s="69"/>
+      <c r="AM34" s="69"/>
+      <c r="AN34" s="69"/>
+      <c r="AO34" s="69"/>
+      <c r="AP34" s="81"/>
+      <c r="AQ34" s="68"/>
+      <c r="AR34" s="69"/>
+      <c r="AS34" s="69"/>
+      <c r="AT34" s="69"/>
+      <c r="AU34" s="69"/>
+      <c r="AV34" s="69"/>
+      <c r="AW34" s="69"/>
+      <c r="AX34" s="69"/>
+      <c r="AY34" s="69"/>
+      <c r="AZ34" s="69"/>
+      <c r="BA34" s="69"/>
+      <c r="BB34" s="69"/>
+      <c r="BC34" s="69"/>
+      <c r="BD34" s="69"/>
+      <c r="BE34" s="70"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="83"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="77"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="77"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="78"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="68"/>
-      <c r="T35" s="68"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="68"/>
-      <c r="W35" s="68"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="68"/>
-      <c r="AA35" s="68"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="68"/>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
-      <c r="AL35" s="68"/>
-      <c r="AM35" s="68"/>
-      <c r="AN35" s="68"/>
-      <c r="AO35" s="68"/>
-      <c r="AP35" s="79"/>
-      <c r="AQ35" s="67"/>
-      <c r="AR35" s="68"/>
-      <c r="AS35" s="68"/>
-      <c r="AT35" s="68"/>
-      <c r="AU35" s="68"/>
-      <c r="AV35" s="68"/>
-      <c r="AW35" s="68"/>
-      <c r="AX35" s="68"/>
-      <c r="AY35" s="68"/>
-      <c r="AZ35" s="68"/>
-      <c r="BA35" s="68"/>
-      <c r="BB35" s="68"/>
-      <c r="BC35" s="68"/>
-      <c r="BD35" s="68"/>
-      <c r="BE35" s="69"/>
+      <c r="A35" s="112"/>
+      <c r="B35" s="113"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="114"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="110"/>
+      <c r="O35" s="108"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="103"/>
+      <c r="U35" s="103"/>
+      <c r="V35" s="103"/>
+      <c r="W35" s="103"/>
+      <c r="X35" s="103"/>
+      <c r="Y35" s="103"/>
+      <c r="Z35" s="103"/>
+      <c r="AA35" s="103"/>
+      <c r="AB35" s="103"/>
+      <c r="AC35" s="103"/>
+      <c r="AD35" s="103"/>
+      <c r="AE35" s="103"/>
+      <c r="AF35" s="103"/>
+      <c r="AG35" s="103"/>
+      <c r="AH35" s="103"/>
+      <c r="AI35" s="103"/>
+      <c r="AJ35" s="103"/>
+      <c r="AK35" s="103"/>
+      <c r="AL35" s="103"/>
+      <c r="AM35" s="103"/>
+      <c r="AN35" s="103"/>
+      <c r="AO35" s="103"/>
+      <c r="AP35" s="111"/>
+      <c r="AQ35" s="102"/>
+      <c r="AR35" s="103"/>
+      <c r="AS35" s="103"/>
+      <c r="AT35" s="103"/>
+      <c r="AU35" s="103"/>
+      <c r="AV35" s="103"/>
+      <c r="AW35" s="103"/>
+      <c r="AX35" s="103"/>
+      <c r="AY35" s="103"/>
+      <c r="AZ35" s="103"/>
+      <c r="BA35" s="103"/>
+      <c r="BB35" s="103"/>
+      <c r="BC35" s="103"/>
+      <c r="BD35" s="103"/>
+      <c r="BE35" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
     <mergeCell ref="AQ6:BE6"/>
     <mergeCell ref="H4:N4"/>
     <mergeCell ref="O4:AP4"/>
@@ -8917,115 +9018,6 @@
     <mergeCell ref="AQ19:BE19"/>
     <mergeCell ref="H17:N17"/>
     <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\PJ\TK\dev\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1A2682-F0F5-4E80-BB2D-61E2CBD86E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCE2FD3-4382-44DD-81B6-BAC4AFE3FD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="303">
   <si>
     <t>*</t>
   </si>
@@ -1277,6 +1277,36 @@
   </si>
   <si>
     <t>chd_itm_nm</t>
+  </si>
+  <si>
+    <t>check</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Select</t>
+  </si>
+  <si>
+    <t>選択</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>@</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>#MA.FLG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>RO</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1619,7 +1649,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -2258,6 +2288,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2394,7 +2437,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2585,15 +2628,126 @@
     <xf numFmtId="0" fontId="23" fillId="24" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2615,116 +2769,18 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="47">
@@ -3077,7 +3133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AH101"/>
+  <dimension ref="A1:BM102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" style="10" customWidth="1"/>
@@ -5181,7 +5237,7 @@
       </c>
       <c r="AF48" s="11"/>
     </row>
-    <row r="49" spans="1:32" s="1" customFormat="1">
+    <row r="49" spans="1:65" s="1" customFormat="1">
       <c r="A49" s="30">
         <v>80</v>
       </c>
@@ -5229,7 +5285,7 @@
       <c r="AE49" s="51"/>
       <c r="AF49" s="36"/>
     </row>
-    <row r="50" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="50" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A50" s="5"/>
       <c r="AC50" s="39" t="s">
         <v>212</v>
@@ -5239,7 +5295,7 @@
       </c>
       <c r="AF50" s="11"/>
     </row>
-    <row r="51" spans="1:32" s="1" customFormat="1">
+    <row r="51" spans="1:65" s="1" customFormat="1">
       <c r="A51" s="30">
         <v>90</v>
       </c>
@@ -5287,7 +5343,7 @@
       <c r="AE51" s="51"/>
       <c r="AF51" s="36"/>
     </row>
-    <row r="52" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="52" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A52" s="5"/>
       <c r="AC52" s="39" t="s">
         <v>212</v>
@@ -5297,7 +5353,7 @@
       </c>
       <c r="AF52" s="11"/>
     </row>
-    <row r="53" spans="1:32" s="1" customFormat="1">
+    <row r="53" spans="1:65" s="1" customFormat="1">
       <c r="A53" s="20">
         <v>100</v>
       </c>
@@ -5347,7 +5403,7 @@
       <c r="AE53" s="23"/>
       <c r="AF53" s="16"/>
     </row>
-    <row r="54" spans="1:32" s="1" customFormat="1">
+    <row r="54" spans="1:65" s="1" customFormat="1">
       <c r="A54" s="20">
         <v>100</v>
       </c>
@@ -5390,7 +5446,7 @@
       <c r="AD54" s="20"/>
       <c r="AF54" s="16"/>
     </row>
-    <row r="55" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="55" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A55" s="5"/>
       <c r="AC55" s="39" t="s">
         <v>212</v>
@@ -5400,7 +5456,7 @@
       </c>
       <c r="AF55" s="11"/>
     </row>
-    <row r="56" spans="1:32" s="1" customFormat="1">
+    <row r="56" spans="1:65" s="1" customFormat="1">
       <c r="A56" s="20">
         <v>110</v>
       </c>
@@ -5450,7 +5506,7 @@
       <c r="AE56" s="23"/>
       <c r="AF56" s="16"/>
     </row>
-    <row r="57" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="57" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A57" s="20">
         <v>110</v>
       </c>
@@ -5499,13 +5555,13 @@
       <c r="AD57" s="20"/>
       <c r="AF57" s="16"/>
     </row>
-    <row r="58" spans="1:32" s="1" customFormat="1">
+    <row r="58" spans="1:65" s="1" customFormat="1">
       <c r="A58" s="5"/>
       <c r="AC58" s="39"/>
       <c r="AD58" s="39"/>
       <c r="AF58" s="11"/>
     </row>
-    <row r="59" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="59" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A59" s="20">
         <v>120</v>
       </c>
@@ -5547,125 +5603,164 @@
       <c r="Y59" s="23"/>
       <c r="Z59" s="22"/>
       <c r="AA59" s="22"/>
-      <c r="AB59" s="23"/>
-      <c r="AC59" s="20"/>
-      <c r="AD59" s="20" t="s">
+      <c r="AB59" s="115"/>
+      <c r="AC59" s="116"/>
+      <c r="AD59" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="AE59" s="23"/>
-      <c r="AF59" s="17"/>
-    </row>
-    <row r="60" spans="1:32" s="1" customFormat="1">
-      <c r="A60" s="37">
+      <c r="AE59" s="115"/>
+      <c r="AF59" s="117"/>
+    </row>
+    <row r="60" spans="1:65" s="7" customFormat="1">
+      <c r="A60" s="30">
         <v>120</v>
       </c>
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J60" s="37"/>
-      <c r="K60" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L60" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="M60" s="37"/>
-      <c r="N60" s="37"/>
-      <c r="O60" s="37"/>
-      <c r="P60" s="37"/>
-      <c r="Q60" s="37"/>
-      <c r="R60" s="37"/>
-      <c r="S60" s="37"/>
-      <c r="T60" s="37"/>
-      <c r="U60" s="37"/>
-      <c r="V60" s="37"/>
-      <c r="W60" s="37"/>
-      <c r="X60" s="37"/>
-      <c r="Y60" s="37"/>
-      <c r="Z60" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA60" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB60" s="37"/>
-      <c r="AC60" s="37"/>
-      <c r="AD60" s="37"/>
-      <c r="AE60" s="37"/>
-      <c r="AF60" s="37"/>
-    </row>
-    <row r="61" spans="1:32" s="1" customFormat="1" ht="27">
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="G60" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30"/>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
+      <c r="X60" s="30"/>
+      <c r="Z60" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA60" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="AB60" s="119"/>
+      <c r="AC60" s="116"/>
+      <c r="AD60" s="116"/>
+      <c r="AE60" s="115"/>
+      <c r="AF60" s="117"/>
+      <c r="AG60" s="119"/>
+      <c r="AH60" s="119"/>
+      <c r="AI60" s="119"/>
+      <c r="AJ60" s="119"/>
+      <c r="AK60" s="119"/>
+      <c r="AL60" s="119"/>
+      <c r="AM60" s="119"/>
+      <c r="AN60" s="119"/>
+      <c r="AO60" s="119"/>
+      <c r="AP60" s="119"/>
+      <c r="AQ60" s="119"/>
+      <c r="AR60" s="119"/>
+      <c r="AS60" s="119"/>
+      <c r="AT60" s="119"/>
+      <c r="AU60" s="119"/>
+      <c r="AV60" s="119"/>
+      <c r="AW60" s="119"/>
+      <c r="AX60" s="119"/>
+      <c r="AY60" s="119"/>
+      <c r="AZ60" s="119"/>
+      <c r="BA60" s="119"/>
+      <c r="BB60" s="119"/>
+      <c r="BC60" s="119"/>
+      <c r="BD60" s="119"/>
+      <c r="BE60" s="119"/>
+      <c r="BF60" s="119"/>
+      <c r="BG60" s="119"/>
+      <c r="BH60" s="119"/>
+      <c r="BI60" s="119"/>
+      <c r="BJ60" s="119"/>
+      <c r="BK60" s="119"/>
+      <c r="BL60" s="119"/>
+      <c r="BM60" s="119"/>
+    </row>
+    <row r="61" spans="1:65" s="1" customFormat="1">
       <c r="A61" s="37">
         <v>120</v>
       </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
-      <c r="P61" s="20"/>
-      <c r="Q61" s="20"/>
-      <c r="R61" s="20"/>
-      <c r="S61" s="20"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="20"/>
-      <c r="V61" s="20"/>
-      <c r="W61" s="20"/>
-      <c r="X61" s="20"/>
-      <c r="Z61" s="20"/>
-      <c r="AA61" s="20"/>
-      <c r="AC61" s="20"/>
-      <c r="AD61" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF61" s="17"/>
-    </row>
-    <row r="62" spans="1:32" s="1" customFormat="1" ht="27">
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L61" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="M61" s="37"/>
+      <c r="N61" s="37"/>
+      <c r="O61" s="37"/>
+      <c r="P61" s="37"/>
+      <c r="Q61" s="37"/>
+      <c r="R61" s="37"/>
+      <c r="S61" s="37"/>
+      <c r="T61" s="37"/>
+      <c r="U61" s="37"/>
+      <c r="V61" s="37"/>
+      <c r="W61" s="37"/>
+      <c r="X61" s="37"/>
+      <c r="Y61" s="37"/>
+      <c r="Z61" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA61" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB61" s="118"/>
+      <c r="AC61" s="118"/>
+      <c r="AD61" s="118"/>
+      <c r="AE61" s="118"/>
+      <c r="AF61" s="118"/>
+    </row>
+    <row r="62" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A62" s="37">
         <v>120</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="G62" s="20"/>
+        <v>225</v>
+      </c>
+      <c r="G62" s="20" t="s">
+        <v>226</v>
+      </c>
       <c r="H62" s="20"/>
       <c r="I62" s="20" t="s">
         <v>35</v>
@@ -5691,24 +5786,24 @@
       <c r="AA62" s="20"/>
       <c r="AC62" s="20"/>
       <c r="AD62" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AF62" s="17"/>
     </row>
-    <row r="63" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="63" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A63" s="37">
         <v>120</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
@@ -5736,24 +5831,24 @@
       <c r="AA63" s="20"/>
       <c r="AC63" s="20"/>
       <c r="AD63" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AF63" s="17"/>
     </row>
-    <row r="64" spans="1:32" s="1" customFormat="1" ht="27">
+    <row r="64" spans="1:65" s="1" customFormat="1" ht="27">
       <c r="A64" s="37">
         <v>120</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
@@ -5781,7 +5876,7 @@
       <c r="AA64" s="20"/>
       <c r="AC64" s="20"/>
       <c r="AD64" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AF64" s="17"/>
     </row>
@@ -5792,13 +5887,13 @@
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
@@ -5826,35 +5921,33 @@
       <c r="AA65" s="20"/>
       <c r="AC65" s="20"/>
       <c r="AD65" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AF65" s="17"/>
     </row>
-    <row r="66" spans="1:32" s="1" customFormat="1">
-      <c r="A66" s="20">
+    <row r="66" spans="1:32" s="1" customFormat="1" ht="27">
+      <c r="A66" s="37">
         <v>120</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>1</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G66" s="20"/>
       <c r="H66" s="20"/>
       <c r="I66" s="20" t="s">
-        <v>240</v>
+        <v>35</v>
       </c>
       <c r="J66" s="20"/>
       <c r="K66" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L66" s="20"/>
       <c r="M66" s="20"/>
@@ -5869,15 +5962,13 @@
       <c r="V66" s="20"/>
       <c r="W66" s="20"/>
       <c r="X66" s="20"/>
-      <c r="Z66" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA66" s="20" t="s">
-        <v>75</v>
-      </c>
+      <c r="Z66" s="20"/>
+      <c r="AA66" s="20"/>
       <c r="AC66" s="20"/>
-      <c r="AD66" s="20"/>
-      <c r="AF66" s="16"/>
+      <c r="AD66" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="AF66" s="17"/>
     </row>
     <row r="67" spans="1:32" s="1" customFormat="1">
       <c r="A67" s="20">
@@ -5886,20 +5977,20 @@
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H67" s="20"/>
       <c r="I67" s="20" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J67" s="20"/>
       <c r="K67" s="20" t="s">
@@ -5929,99 +6020,101 @@
       <c r="AF67" s="16"/>
     </row>
     <row r="68" spans="1:32" s="1" customFormat="1">
-      <c r="A68" s="37">
+      <c r="A68" s="20">
         <v>120</v>
       </c>
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J68" s="37"/>
-      <c r="K68" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L68" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="M68" s="37"/>
-      <c r="N68" s="37"/>
-      <c r="O68" s="37"/>
-      <c r="P68" s="37"/>
-      <c r="Q68" s="37"/>
-      <c r="R68" s="37"/>
-      <c r="S68" s="37"/>
-      <c r="T68" s="37"/>
-      <c r="U68" s="37"/>
-      <c r="V68" s="37"/>
-      <c r="W68" s="37"/>
-      <c r="X68" s="37"/>
-      <c r="Y68" s="37"/>
-      <c r="Z68" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA68" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB68" s="37"/>
-      <c r="AC68" s="37"/>
-      <c r="AD68" s="37"/>
-      <c r="AE68" s="37"/>
-      <c r="AF68" s="37"/>
-    </row>
-    <row r="69" spans="1:32" s="1" customFormat="1" ht="27">
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F68" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="G68" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="J68" s="20"/>
+      <c r="K68" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="L68" s="20"/>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="20"/>
+      <c r="V68" s="20"/>
+      <c r="W68" s="20"/>
+      <c r="X68" s="20"/>
+      <c r="Z68" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA68" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC68" s="20"/>
+      <c r="AD68" s="20"/>
+      <c r="AF68" s="16"/>
+    </row>
+    <row r="69" spans="1:32" s="1" customFormat="1">
       <c r="A69" s="37">
         <v>120</v>
       </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="G69" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20"/>
-      <c r="N69" s="20"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="20"/>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="20"/>
-      <c r="S69" s="20"/>
-      <c r="T69" s="20"/>
-      <c r="U69" s="20"/>
-      <c r="V69" s="20"/>
-      <c r="W69" s="20"/>
-      <c r="X69" s="20"/>
-      <c r="Z69" s="20"/>
-      <c r="AA69" s="20"/>
-      <c r="AC69" s="20"/>
-      <c r="AD69" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="AF69" s="17"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37"/>
+      <c r="I69" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="37"/>
+      <c r="K69" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L69" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69" s="37"/>
+      <c r="N69" s="37"/>
+      <c r="O69" s="37"/>
+      <c r="P69" s="37"/>
+      <c r="Q69" s="37"/>
+      <c r="R69" s="37"/>
+      <c r="S69" s="37"/>
+      <c r="T69" s="37"/>
+      <c r="U69" s="37"/>
+      <c r="V69" s="37"/>
+      <c r="W69" s="37"/>
+      <c r="X69" s="37"/>
+      <c r="Y69" s="37"/>
+      <c r="Z69" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA69" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB69" s="37"/>
+      <c r="AC69" s="37"/>
+      <c r="AD69" s="37"/>
+      <c r="AE69" s="37"/>
+      <c r="AF69" s="37"/>
     </row>
     <row r="70" spans="1:32" s="1" customFormat="1" ht="27">
       <c r="A70" s="37">
@@ -6030,15 +6123,17 @@
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="G70" s="20"/>
+        <v>250</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>251</v>
+      </c>
       <c r="H70" s="20"/>
       <c r="I70" s="20" t="s">
         <v>35</v>
@@ -6064,7 +6159,7 @@
       <c r="AA70" s="20"/>
       <c r="AC70" s="20"/>
       <c r="AD70" s="20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AF70" s="17"/>
     </row>
@@ -6075,13 +6170,13 @@
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
@@ -6109,7 +6204,7 @@
       <c r="AA71" s="20"/>
       <c r="AC71" s="20"/>
       <c r="AD71" s="20" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="AF71" s="17"/>
     </row>
@@ -6120,13 +6215,13 @@
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
@@ -6154,7 +6249,7 @@
       <c r="AA72" s="20"/>
       <c r="AC72" s="20"/>
       <c r="AD72" s="20" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AF72" s="17"/>
     </row>
@@ -6165,13 +6260,13 @@
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
@@ -6199,35 +6294,33 @@
       <c r="AA73" s="20"/>
       <c r="AC73" s="20"/>
       <c r="AD73" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AF73" s="17"/>
     </row>
-    <row r="74" spans="1:32" s="1" customFormat="1">
-      <c r="A74" s="20">
+    <row r="74" spans="1:32" s="1" customFormat="1" ht="27">
+      <c r="A74" s="37">
         <v>120</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G74" s="20" t="s">
-        <v>1</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="G74" s="20"/>
       <c r="H74" s="20"/>
       <c r="I74" s="20" t="s">
-        <v>269</v>
+        <v>35</v>
       </c>
       <c r="J74" s="20"/>
       <c r="K74" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L74" s="20"/>
       <c r="M74" s="20"/>
@@ -6242,14 +6335,12 @@
       <c r="V74" s="20"/>
       <c r="W74" s="20"/>
       <c r="X74" s="20"/>
-      <c r="Z74" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA74" s="20" t="s">
-        <v>75</v>
-      </c>
+      <c r="Z74" s="20"/>
+      <c r="AA74" s="20"/>
       <c r="AC74" s="20"/>
-      <c r="AD74" s="20"/>
+      <c r="AD74" s="20" t="s">
+        <v>160</v>
+      </c>
       <c r="AF74" s="17"/>
     </row>
     <row r="75" spans="1:32" s="1" customFormat="1">
@@ -6259,20 +6350,20 @@
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="H75" s="20"/>
       <c r="I75" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J75" s="20"/>
       <c r="K75" s="20" t="s">
@@ -6302,30 +6393,30 @@
       <c r="AF75" s="17"/>
     </row>
     <row r="76" spans="1:32" s="1" customFormat="1">
-      <c r="A76" s="37">
+      <c r="A76" s="20">
         <v>120</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>1</v>
+        <v>121</v>
       </c>
       <c r="H76" s="20"/>
       <c r="I76" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J76" s="20"/>
       <c r="K76" s="20" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="L76" s="20"/>
       <c r="M76" s="20"/>
@@ -6340,8 +6431,12 @@
       <c r="V76" s="20"/>
       <c r="W76" s="20"/>
       <c r="X76" s="20"/>
-      <c r="Z76" s="20"/>
-      <c r="AA76" s="20"/>
+      <c r="Z76" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA76" s="20" t="s">
+        <v>75</v>
+      </c>
       <c r="AC76" s="20"/>
       <c r="AD76" s="20"/>
       <c r="AF76" s="17"/>
@@ -6353,13 +6448,13 @@
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G77" s="20" t="s">
         <v>1</v>
@@ -6398,13 +6493,13 @@
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F78" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G78" s="20" t="s">
         <v>1</v>
@@ -6437,109 +6532,103 @@
       <c r="AF78" s="17"/>
     </row>
     <row r="79" spans="1:32" s="1" customFormat="1">
-      <c r="A79" s="5"/>
-      <c r="AC79" s="39"/>
-      <c r="AD79" s="39"/>
-      <c r="AF79" s="11"/>
+      <c r="A79" s="37">
+        <v>120</v>
+      </c>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F79" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G79" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="J79" s="20"/>
+      <c r="K79" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="L79" s="20"/>
+      <c r="M79" s="20"/>
+      <c r="N79" s="20"/>
+      <c r="O79" s="20"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="20"/>
+      <c r="U79" s="20"/>
+      <c r="V79" s="20"/>
+      <c r="W79" s="20"/>
+      <c r="X79" s="20"/>
+      <c r="Z79" s="20"/>
+      <c r="AA79" s="20"/>
+      <c r="AC79" s="20"/>
+      <c r="AD79" s="20"/>
+      <c r="AF79" s="17"/>
     </row>
     <row r="80" spans="1:32" s="1" customFormat="1">
-      <c r="A80" s="20">
-        <v>150</v>
-      </c>
-      <c r="B80" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E80" s="21"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="J80" s="20"/>
-      <c r="K80" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="L80" s="20"/>
-      <c r="M80" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="N80" s="20">
-        <v>700</v>
-      </c>
-      <c r="O80" s="20"/>
-      <c r="P80" s="20"/>
-      <c r="Q80" s="22"/>
-      <c r="R80" s="22"/>
-      <c r="S80" s="22"/>
-      <c r="T80" s="22"/>
-      <c r="U80" s="22"/>
-      <c r="V80" s="22"/>
-      <c r="W80" s="22"/>
-      <c r="X80" s="22"/>
-      <c r="Y80" s="23"/>
-      <c r="Z80" s="22"/>
-      <c r="AA80" s="22"/>
-      <c r="AB80" s="23"/>
-      <c r="AC80" s="20"/>
-      <c r="AD80" s="20"/>
-      <c r="AE80" s="23"/>
-      <c r="AF80" s="17"/>
+      <c r="A80" s="5"/>
+      <c r="AC80" s="39"/>
+      <c r="AD80" s="39"/>
+      <c r="AF80" s="11"/>
     </row>
     <row r="81" spans="1:32" s="1" customFormat="1">
       <c r="A81" s="20">
         <v>150</v>
       </c>
-      <c r="B81" s="20"/>
+      <c r="B81" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="C81" s="20"/>
       <c r="D81" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="E81" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="G81" s="20" t="s">
-        <v>176</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="E81" s="21"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
       <c r="H81" s="20"/>
       <c r="I81" s="20" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="J81" s="20"/>
       <c r="K81" s="20" t="s">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="L81" s="20"/>
-      <c r="M81" s="20"/>
-      <c r="N81" s="20"/>
+      <c r="M81" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="N81" s="20">
+        <v>700</v>
+      </c>
       <c r="O81" s="20"/>
       <c r="P81" s="20"/>
-      <c r="Q81" s="20"/>
-      <c r="R81" s="20"/>
-      <c r="S81" s="20"/>
-      <c r="T81" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="U81" s="20"/>
-      <c r="V81" s="20"/>
-      <c r="W81" s="20"/>
-      <c r="X81" s="20"/>
-      <c r="Z81" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA81" s="20" t="s">
-        <v>56</v>
-      </c>
+      <c r="Q81" s="22"/>
+      <c r="R81" s="22"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
+      <c r="U81" s="22"/>
+      <c r="V81" s="22"/>
+      <c r="W81" s="22"/>
+      <c r="X81" s="22"/>
+      <c r="Y81" s="23"/>
+      <c r="Z81" s="22"/>
+      <c r="AA81" s="22"/>
+      <c r="AB81" s="23"/>
       <c r="AC81" s="20"/>
       <c r="AD81" s="20"/>
-      <c r="AF81" s="16"/>
+      <c r="AE81" s="23"/>
+      <c r="AF81" s="17"/>
     </row>
     <row r="82" spans="1:32" s="1" customFormat="1">
       <c r="A82" s="20">
@@ -6548,16 +6637,16 @@
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
       <c r="D82" s="20" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F82" s="20" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H82" s="20"/>
       <c r="I82" s="20" t="s">
@@ -6576,7 +6665,7 @@
       <c r="R82" s="20"/>
       <c r="S82" s="20"/>
       <c r="T82" s="20" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="U82" s="20"/>
       <c r="V82" s="20"/>
@@ -6593,98 +6682,145 @@
       <c r="AF82" s="16"/>
     </row>
     <row r="83" spans="1:32" s="1" customFormat="1">
-      <c r="A83" s="5"/>
-      <c r="AC83" s="39"/>
-      <c r="AD83" s="39"/>
-      <c r="AF83" s="11"/>
+      <c r="A83" s="20">
+        <v>150</v>
+      </c>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E83" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="L83" s="20"/>
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="U83" s="20"/>
+      <c r="V83" s="20"/>
+      <c r="W83" s="20"/>
+      <c r="X83" s="20"/>
+      <c r="Z83" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA83" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC83" s="20"/>
+      <c r="AD83" s="20"/>
+      <c r="AF83" s="16"/>
     </row>
     <row r="84" spans="1:32" s="1" customFormat="1">
-      <c r="A84" s="20">
+      <c r="A84" s="5"/>
+      <c r="AC84" s="39"/>
+      <c r="AD84" s="39"/>
+      <c r="AF84" s="11"/>
+    </row>
+    <row r="85" spans="1:32" s="1" customFormat="1">
+      <c r="A85" s="20">
         <v>160</v>
       </c>
-      <c r="B84" s="20" t="s">
+      <c r="B85" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20" t="s">
+      <c r="C85" s="20"/>
+      <c r="D85" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20" t="s">
+      <c r="E85" s="21"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20" t="s">
+      <c r="J85" s="20"/>
+      <c r="K85" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20" t="s">
+      <c r="L85" s="20"/>
+      <c r="M85" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="N84" s="20" t="s">
+      <c r="N85" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="O84" s="20"/>
-      <c r="P84" s="20"/>
-      <c r="Q84" s="22"/>
-      <c r="R84" s="22"/>
-      <c r="S84" s="22"/>
-      <c r="T84" s="22"/>
-      <c r="U84" s="22"/>
-      <c r="V84" s="22"/>
-      <c r="W84" s="22"/>
-      <c r="X84" s="22"/>
-      <c r="Y84" s="23"/>
-      <c r="Z84" s="22"/>
-      <c r="AA84" s="22"/>
-      <c r="AB84" s="23"/>
-      <c r="AC84" s="20"/>
-      <c r="AD84" s="20"/>
-      <c r="AE84" s="23"/>
-      <c r="AF84" s="17"/>
-    </row>
-    <row r="85" spans="1:32" s="1" customFormat="1">
-      <c r="A85" s="2"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="9" t="s">
+      <c r="O85" s="20"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="22"/>
+      <c r="R85" s="22"/>
+      <c r="S85" s="22"/>
+      <c r="T85" s="22"/>
+      <c r="U85" s="22"/>
+      <c r="V85" s="22"/>
+      <c r="W85" s="22"/>
+      <c r="X85" s="22"/>
+      <c r="Y85" s="23"/>
+      <c r="Z85" s="22"/>
+      <c r="AA85" s="22"/>
+      <c r="AB85" s="23"/>
+      <c r="AC85" s="20"/>
+      <c r="AD85" s="20"/>
+      <c r="AE85" s="23"/>
+      <c r="AF85" s="17"/>
+    </row>
+    <row r="86" spans="1:32" s="1" customFormat="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9"/>
-      <c r="L85" s="9"/>
-      <c r="M85" s="9"/>
-      <c r="N85" s="9"/>
-      <c r="O85" s="9"/>
-      <c r="P85" s="9"/>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
-      <c r="V85" s="9"/>
-      <c r="W85" s="9"/>
-      <c r="X85" s="9"/>
-      <c r="Y85" s="9"/>
-      <c r="Z85" s="9"/>
-      <c r="AA85" s="9"/>
-      <c r="AB85" s="9"/>
-      <c r="AC85" s="9"/>
-      <c r="AD85" s="9"/>
-      <c r="AE85" s="9"/>
-      <c r="AF85" s="24"/>
-    </row>
-    <row r="86" spans="1:32" s="1" customFormat="1">
-      <c r="A86" s="5"/>
-      <c r="AF86" s="11"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9"/>
+      <c r="N86" s="9"/>
+      <c r="O86" s="9"/>
+      <c r="P86" s="9"/>
+      <c r="Q86" s="9"/>
+      <c r="R86" s="9"/>
+      <c r="S86" s="9"/>
+      <c r="T86" s="9"/>
+      <c r="U86" s="9"/>
+      <c r="V86" s="9"/>
+      <c r="W86" s="9"/>
+      <c r="X86" s="9"/>
+      <c r="Y86" s="9"/>
+      <c r="Z86" s="9"/>
+      <c r="AA86" s="9"/>
+      <c r="AB86" s="9"/>
+      <c r="AC86" s="9"/>
+      <c r="AD86" s="9"/>
+      <c r="AE86" s="9"/>
+      <c r="AF86" s="24"/>
     </row>
     <row r="87" spans="1:32" s="1" customFormat="1">
       <c r="A87" s="5"/>
@@ -6743,38 +6879,42 @@
       <c r="AF100" s="11"/>
     </row>
     <row r="101" spans="1:32" s="1" customFormat="1">
-      <c r="A101" s="8"/>
-      <c r="B101" s="23"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="23"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="23"/>
-      <c r="H101" s="23"/>
-      <c r="I101" s="23"/>
-      <c r="J101" s="23"/>
-      <c r="K101" s="23"/>
-      <c r="L101" s="23"/>
-      <c r="M101" s="23"/>
-      <c r="N101" s="23"/>
-      <c r="O101" s="23"/>
-      <c r="P101" s="23"/>
-      <c r="Q101" s="23"/>
-      <c r="R101" s="23"/>
-      <c r="S101" s="23"/>
-      <c r="T101" s="23"/>
-      <c r="U101" s="23"/>
-      <c r="V101" s="23"/>
-      <c r="W101" s="23"/>
-      <c r="X101" s="23"/>
-      <c r="Y101" s="23"/>
-      <c r="Z101" s="23"/>
-      <c r="AA101" s="23"/>
-      <c r="AB101" s="23"/>
-      <c r="AC101" s="23"/>
-      <c r="AD101" s="23"/>
-      <c r="AE101" s="23"/>
-      <c r="AF101" s="25"/>
+      <c r="A101" s="5"/>
+      <c r="AF101" s="11"/>
+    </row>
+    <row r="102" spans="1:32" s="1" customFormat="1">
+      <c r="A102" s="8"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23"/>
+      <c r="M102" s="23"/>
+      <c r="N102" s="23"/>
+      <c r="O102" s="23"/>
+      <c r="P102" s="23"/>
+      <c r="Q102" s="23"/>
+      <c r="R102" s="23"/>
+      <c r="S102" s="23"/>
+      <c r="T102" s="23"/>
+      <c r="U102" s="23"/>
+      <c r="V102" s="23"/>
+      <c r="W102" s="23"/>
+      <c r="X102" s="23"/>
+      <c r="Y102" s="23"/>
+      <c r="Z102" s="23"/>
+      <c r="AA102" s="23"/>
+      <c r="AB102" s="23"/>
+      <c r="AC102" s="23"/>
+      <c r="AD102" s="23"/>
+      <c r="AE102" s="23"/>
+      <c r="AF102" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -6919,1972 +7059,2081 @@
       <c r="AP2" s="13"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="84"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="96"/>
       <c r="H3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="84"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="96"/>
       <c r="O3" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="95"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="95"/>
-      <c r="V3" s="95"/>
-      <c r="W3" s="95"/>
-      <c r="X3" s="95"/>
-      <c r="Y3" s="95"/>
-      <c r="Z3" s="95"/>
-      <c r="AA3" s="95"/>
-      <c r="AB3" s="95"/>
-      <c r="AC3" s="95"/>
-      <c r="AD3" s="95"/>
-      <c r="AE3" s="95"/>
-      <c r="AF3" s="95"/>
-      <c r="AG3" s="95"/>
-      <c r="AH3" s="95"/>
-      <c r="AI3" s="95"/>
-      <c r="AJ3" s="95"/>
-      <c r="AK3" s="95"/>
-      <c r="AL3" s="95"/>
-      <c r="AM3" s="95"/>
-      <c r="AN3" s="95"/>
-      <c r="AO3" s="95"/>
-      <c r="AP3" s="96"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
+      <c r="AB3" s="97"/>
+      <c r="AC3" s="97"/>
+      <c r="AD3" s="97"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="97"/>
+      <c r="AI3" s="97"/>
+      <c r="AJ3" s="97"/>
+      <c r="AK3" s="97"/>
+      <c r="AL3" s="97"/>
+      <c r="AM3" s="97"/>
+      <c r="AN3" s="97"/>
+      <c r="AO3" s="97"/>
+      <c r="AP3" s="98"/>
       <c r="AQ3" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="AR3" s="97"/>
-      <c r="AS3" s="97"/>
-      <c r="AT3" s="97"/>
-      <c r="AU3" s="97"/>
-      <c r="AV3" s="97"/>
-      <c r="AW3" s="97"/>
-      <c r="AX3" s="97"/>
-      <c r="AY3" s="97"/>
-      <c r="AZ3" s="97"/>
-      <c r="BA3" s="97"/>
-      <c r="BB3" s="97"/>
-      <c r="BC3" s="97"/>
-      <c r="BD3" s="97"/>
-      <c r="BE3" s="98"/>
+      <c r="AR3" s="99"/>
+      <c r="AS3" s="99"/>
+      <c r="AT3" s="99"/>
+      <c r="AU3" s="99"/>
+      <c r="AV3" s="99"/>
+      <c r="AW3" s="99"/>
+      <c r="AX3" s="99"/>
+      <c r="AY3" s="99"/>
+      <c r="AZ3" s="99"/>
+      <c r="BA3" s="99"/>
+      <c r="BB3" s="99"/>
+      <c r="BC3" s="99"/>
+      <c r="BD3" s="99"/>
+      <c r="BE3" s="100"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="105">
+      <c r="A4" s="71">
         <v>1</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="71" t="s">
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="74"/>
-      <c r="AM4" s="74"/>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="74"/>
-      <c r="AP4" s="75"/>
-      <c r="AQ4" s="76"/>
-      <c r="AR4" s="74"/>
-      <c r="AS4" s="74"/>
-      <c r="AT4" s="74"/>
-      <c r="AU4" s="74"/>
-      <c r="AV4" s="74"/>
-      <c r="AW4" s="74"/>
-      <c r="AX4" s="74"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="74"/>
-      <c r="BA4" s="74"/>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="74"/>
-      <c r="BD4" s="74"/>
-      <c r="BE4" s="77"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111"/>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="111"/>
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112"/>
+      <c r="AQ4" s="113"/>
+      <c r="AR4" s="111"/>
+      <c r="AS4" s="111"/>
+      <c r="AT4" s="111"/>
+      <c r="AU4" s="111"/>
+      <c r="AV4" s="111"/>
+      <c r="AW4" s="111"/>
+      <c r="AX4" s="111"/>
+      <c r="AY4" s="111"/>
+      <c r="AZ4" s="111"/>
+      <c r="BA4" s="111"/>
+      <c r="BB4" s="111"/>
+      <c r="BC4" s="111"/>
+      <c r="BD4" s="111"/>
+      <c r="BE4" s="114"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="99">
+      <c r="A5" s="74">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="85" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="89"/>
+      <c r="L5" s="89"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="102" t="s">
         <v>214</v>
       </c>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="86"/>
-      <c r="V5" s="86"/>
-      <c r="W5" s="86"/>
-      <c r="X5" s="86"/>
-      <c r="Y5" s="86"/>
-      <c r="Z5" s="86"/>
-      <c r="AA5" s="86"/>
-      <c r="AB5" s="86"/>
-      <c r="AC5" s="86"/>
-      <c r="AD5" s="86"/>
-      <c r="AE5" s="86"/>
-      <c r="AF5" s="86"/>
-      <c r="AG5" s="86"/>
-      <c r="AH5" s="86"/>
-      <c r="AI5" s="86"/>
-      <c r="AJ5" s="86"/>
-      <c r="AK5" s="86"/>
-      <c r="AL5" s="86"/>
-      <c r="AM5" s="86"/>
-      <c r="AN5" s="86"/>
-      <c r="AO5" s="86"/>
-      <c r="AP5" s="87"/>
-      <c r="AQ5" s="88" t="s">
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103"/>
+      <c r="AA5" s="103"/>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103"/>
+      <c r="AD5" s="103"/>
+      <c r="AE5" s="103"/>
+      <c r="AF5" s="103"/>
+      <c r="AG5" s="103"/>
+      <c r="AH5" s="103"/>
+      <c r="AI5" s="103"/>
+      <c r="AJ5" s="103"/>
+      <c r="AK5" s="103"/>
+      <c r="AL5" s="103"/>
+      <c r="AM5" s="103"/>
+      <c r="AN5" s="103"/>
+      <c r="AO5" s="103"/>
+      <c r="AP5" s="104"/>
+      <c r="AQ5" s="105" t="s">
         <v>215</v>
       </c>
-      <c r="AR5" s="89"/>
-      <c r="AS5" s="89"/>
-      <c r="AT5" s="89"/>
-      <c r="AU5" s="89"/>
-      <c r="AV5" s="89"/>
-      <c r="AW5" s="89"/>
-      <c r="AX5" s="89"/>
-      <c r="AY5" s="89"/>
-      <c r="AZ5" s="89"/>
-      <c r="BA5" s="89"/>
-      <c r="BB5" s="89"/>
-      <c r="BC5" s="89"/>
-      <c r="BD5" s="89"/>
-      <c r="BE5" s="90"/>
+      <c r="AR5" s="106"/>
+      <c r="AS5" s="106"/>
+      <c r="AT5" s="106"/>
+      <c r="AU5" s="106"/>
+      <c r="AV5" s="106"/>
+      <c r="AW5" s="106"/>
+      <c r="AX5" s="106"/>
+      <c r="AY5" s="106"/>
+      <c r="AZ5" s="106"/>
+      <c r="BA5" s="106"/>
+      <c r="BB5" s="106"/>
+      <c r="BC5" s="106"/>
+      <c r="BD5" s="106"/>
+      <c r="BE5" s="107"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="99"/>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="69"/>
-      <c r="Z6" s="69"/>
-      <c r="AA6" s="69"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="69"/>
-      <c r="AD6" s="69"/>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="69"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="69"/>
-      <c r="AM6" s="69"/>
-      <c r="AN6" s="69"/>
-      <c r="AO6" s="69"/>
-      <c r="AP6" s="81"/>
-      <c r="AQ6" s="68"/>
-      <c r="AR6" s="69"/>
-      <c r="AS6" s="69"/>
-      <c r="AT6" s="69"/>
-      <c r="AU6" s="69"/>
-      <c r="AV6" s="69"/>
-      <c r="AW6" s="69"/>
-      <c r="AX6" s="69"/>
-      <c r="AY6" s="69"/>
-      <c r="AZ6" s="69"/>
-      <c r="BA6" s="69"/>
-      <c r="BB6" s="69"/>
-      <c r="BC6" s="69"/>
-      <c r="BD6" s="69"/>
-      <c r="BE6" s="70"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82"/>
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82"/>
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="82"/>
+      <c r="AH6" s="82"/>
+      <c r="AI6" s="82"/>
+      <c r="AJ6" s="82"/>
+      <c r="AK6" s="82"/>
+      <c r="AL6" s="82"/>
+      <c r="AM6" s="82"/>
+      <c r="AN6" s="82"/>
+      <c r="AO6" s="82"/>
+      <c r="AP6" s="83"/>
+      <c r="AQ6" s="87"/>
+      <c r="AR6" s="82"/>
+      <c r="AS6" s="82"/>
+      <c r="AT6" s="82"/>
+      <c r="AU6" s="82"/>
+      <c r="AV6" s="82"/>
+      <c r="AW6" s="82"/>
+      <c r="AX6" s="82"/>
+      <c r="AY6" s="82"/>
+      <c r="AZ6" s="82"/>
+      <c r="BA6" s="82"/>
+      <c r="BB6" s="82"/>
+      <c r="BC6" s="82"/>
+      <c r="BD6" s="82"/>
+      <c r="BE6" s="88"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="69"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="69"/>
-      <c r="X7" s="69"/>
-      <c r="Y7" s="69"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="69"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="69"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="69"/>
-      <c r="AF7" s="69"/>
-      <c r="AG7" s="69"/>
-      <c r="AH7" s="69"/>
-      <c r="AI7" s="69"/>
-      <c r="AJ7" s="69"/>
-      <c r="AK7" s="69"/>
-      <c r="AL7" s="69"/>
-      <c r="AM7" s="69"/>
-      <c r="AN7" s="69"/>
-      <c r="AO7" s="69"/>
-      <c r="AP7" s="81"/>
-      <c r="AQ7" s="68"/>
-      <c r="AR7" s="69"/>
-      <c r="AS7" s="69"/>
-      <c r="AT7" s="69"/>
-      <c r="AU7" s="69"/>
-      <c r="AV7" s="69"/>
-      <c r="AW7" s="69"/>
-      <c r="AX7" s="69"/>
-      <c r="AY7" s="69"/>
-      <c r="AZ7" s="69"/>
-      <c r="BA7" s="69"/>
-      <c r="BB7" s="69"/>
-      <c r="BC7" s="69"/>
-      <c r="BD7" s="69"/>
-      <c r="BE7" s="70"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="89"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
+      <c r="X7" s="82"/>
+      <c r="Y7" s="82"/>
+      <c r="Z7" s="82"/>
+      <c r="AA7" s="82"/>
+      <c r="AB7" s="82"/>
+      <c r="AC7" s="82"/>
+      <c r="AD7" s="82"/>
+      <c r="AE7" s="82"/>
+      <c r="AF7" s="82"/>
+      <c r="AG7" s="82"/>
+      <c r="AH7" s="82"/>
+      <c r="AI7" s="82"/>
+      <c r="AJ7" s="82"/>
+      <c r="AK7" s="82"/>
+      <c r="AL7" s="82"/>
+      <c r="AM7" s="82"/>
+      <c r="AN7" s="82"/>
+      <c r="AO7" s="82"/>
+      <c r="AP7" s="83"/>
+      <c r="AQ7" s="87"/>
+      <c r="AR7" s="82"/>
+      <c r="AS7" s="82"/>
+      <c r="AT7" s="82"/>
+      <c r="AU7" s="82"/>
+      <c r="AV7" s="82"/>
+      <c r="AW7" s="82"/>
+      <c r="AX7" s="82"/>
+      <c r="AY7" s="82"/>
+      <c r="AZ7" s="82"/>
+      <c r="BA7" s="82"/>
+      <c r="BB7" s="82"/>
+      <c r="BC7" s="82"/>
+      <c r="BD7" s="82"/>
+      <c r="BE7" s="88"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="69"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69"/>
-      <c r="AF8" s="69"/>
-      <c r="AG8" s="69"/>
-      <c r="AH8" s="69"/>
-      <c r="AI8" s="69"/>
-      <c r="AJ8" s="69"/>
-      <c r="AK8" s="69"/>
-      <c r="AL8" s="69"/>
-      <c r="AM8" s="69"/>
-      <c r="AN8" s="69"/>
-      <c r="AO8" s="69"/>
-      <c r="AP8" s="81"/>
-      <c r="AQ8" s="68"/>
-      <c r="AR8" s="69"/>
-      <c r="AS8" s="69"/>
-      <c r="AT8" s="69"/>
-      <c r="AU8" s="69"/>
-      <c r="AV8" s="69"/>
-      <c r="AW8" s="69"/>
-      <c r="AX8" s="69"/>
-      <c r="AY8" s="69"/>
-      <c r="AZ8" s="69"/>
-      <c r="BA8" s="69"/>
-      <c r="BB8" s="69"/>
-      <c r="BC8" s="69"/>
-      <c r="BD8" s="69"/>
-      <c r="BE8" s="70"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="89"/>
+      <c r="N8" s="90"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="82"/>
+      <c r="AJ8" s="82"/>
+      <c r="AK8" s="82"/>
+      <c r="AL8" s="82"/>
+      <c r="AM8" s="82"/>
+      <c r="AN8" s="82"/>
+      <c r="AO8" s="82"/>
+      <c r="AP8" s="83"/>
+      <c r="AQ8" s="87"/>
+      <c r="AR8" s="82"/>
+      <c r="AS8" s="82"/>
+      <c r="AT8" s="82"/>
+      <c r="AU8" s="82"/>
+      <c r="AV8" s="82"/>
+      <c r="AW8" s="82"/>
+      <c r="AX8" s="82"/>
+      <c r="AY8" s="82"/>
+      <c r="AZ8" s="82"/>
+      <c r="BA8" s="82"/>
+      <c r="BB8" s="82"/>
+      <c r="BC8" s="82"/>
+      <c r="BD8" s="82"/>
+      <c r="BE8" s="88"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="69"/>
-      <c r="V9" s="69"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69"/>
-      <c r="AF9" s="69"/>
-      <c r="AG9" s="69"/>
-      <c r="AH9" s="69"/>
-      <c r="AI9" s="69"/>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="69"/>
-      <c r="AM9" s="69"/>
-      <c r="AN9" s="69"/>
-      <c r="AO9" s="69"/>
-      <c r="AP9" s="81"/>
-      <c r="AQ9" s="68"/>
-      <c r="AR9" s="69"/>
-      <c r="AS9" s="69"/>
-      <c r="AT9" s="69"/>
-      <c r="AU9" s="69"/>
-      <c r="AV9" s="69"/>
-      <c r="AW9" s="69"/>
-      <c r="AX9" s="69"/>
-      <c r="AY9" s="69"/>
-      <c r="AZ9" s="69"/>
-      <c r="BA9" s="69"/>
-      <c r="BB9" s="69"/>
-      <c r="BC9" s="69"/>
-      <c r="BD9" s="69"/>
-      <c r="BE9" s="70"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="90"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="82"/>
+      <c r="AJ9" s="82"/>
+      <c r="AK9" s="82"/>
+      <c r="AL9" s="82"/>
+      <c r="AM9" s="82"/>
+      <c r="AN9" s="82"/>
+      <c r="AO9" s="82"/>
+      <c r="AP9" s="83"/>
+      <c r="AQ9" s="87"/>
+      <c r="AR9" s="82"/>
+      <c r="AS9" s="82"/>
+      <c r="AT9" s="82"/>
+      <c r="AU9" s="82"/>
+      <c r="AV9" s="82"/>
+      <c r="AW9" s="82"/>
+      <c r="AX9" s="82"/>
+      <c r="AY9" s="82"/>
+      <c r="AZ9" s="82"/>
+      <c r="BA9" s="82"/>
+      <c r="BB9" s="82"/>
+      <c r="BC9" s="82"/>
+      <c r="BD9" s="82"/>
+      <c r="BE9" s="88"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="80"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69"/>
-      <c r="AF10" s="69"/>
-      <c r="AG10" s="69"/>
-      <c r="AH10" s="69"/>
-      <c r="AI10" s="69"/>
-      <c r="AJ10" s="69"/>
-      <c r="AK10" s="69"/>
-      <c r="AL10" s="69"/>
-      <c r="AM10" s="69"/>
-      <c r="AN10" s="69"/>
-      <c r="AO10" s="69"/>
-      <c r="AP10" s="81"/>
-      <c r="AQ10" s="68"/>
-      <c r="AR10" s="69"/>
-      <c r="AS10" s="69"/>
-      <c r="AT10" s="69"/>
-      <c r="AU10" s="69"/>
-      <c r="AV10" s="69"/>
-      <c r="AW10" s="69"/>
-      <c r="AX10" s="69"/>
-      <c r="AY10" s="69"/>
-      <c r="AZ10" s="69"/>
-      <c r="BA10" s="69"/>
-      <c r="BB10" s="69"/>
-      <c r="BC10" s="69"/>
-      <c r="BD10" s="69"/>
-      <c r="BE10" s="70"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+      <c r="AI10" s="82"/>
+      <c r="AJ10" s="82"/>
+      <c r="AK10" s="82"/>
+      <c r="AL10" s="82"/>
+      <c r="AM10" s="82"/>
+      <c r="AN10" s="82"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="83"/>
+      <c r="AQ10" s="87"/>
+      <c r="AR10" s="82"/>
+      <c r="AS10" s="82"/>
+      <c r="AT10" s="82"/>
+      <c r="AU10" s="82"/>
+      <c r="AV10" s="82"/>
+      <c r="AW10" s="82"/>
+      <c r="AX10" s="82"/>
+      <c r="AY10" s="82"/>
+      <c r="AZ10" s="82"/>
+      <c r="BA10" s="82"/>
+      <c r="BB10" s="82"/>
+      <c r="BC10" s="82"/>
+      <c r="BD10" s="82"/>
+      <c r="BE10" s="88"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="80"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="69"/>
-      <c r="U11" s="69"/>
-      <c r="V11" s="69"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="69"/>
-      <c r="Y11" s="69"/>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="69"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="69"/>
-      <c r="AD11" s="69"/>
-      <c r="AE11" s="69"/>
-      <c r="AF11" s="69"/>
-      <c r="AG11" s="69"/>
-      <c r="AH11" s="69"/>
-      <c r="AI11" s="69"/>
-      <c r="AJ11" s="69"/>
-      <c r="AK11" s="69"/>
-      <c r="AL11" s="69"/>
-      <c r="AM11" s="69"/>
-      <c r="AN11" s="69"/>
-      <c r="AO11" s="69"/>
-      <c r="AP11" s="81"/>
-      <c r="AQ11" s="68"/>
-      <c r="AR11" s="69"/>
-      <c r="AS11" s="69"/>
-      <c r="AT11" s="69"/>
-      <c r="AU11" s="69"/>
-      <c r="AV11" s="69"/>
-      <c r="AW11" s="69"/>
-      <c r="AX11" s="69"/>
-      <c r="AY11" s="69"/>
-      <c r="AZ11" s="69"/>
-      <c r="BA11" s="69"/>
-      <c r="BB11" s="69"/>
-      <c r="BC11" s="69"/>
-      <c r="BD11" s="69"/>
-      <c r="BE11" s="70"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="89"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="89"/>
+      <c r="L11" s="89"/>
+      <c r="M11" s="89"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="81"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+      <c r="AI11" s="82"/>
+      <c r="AJ11" s="82"/>
+      <c r="AK11" s="82"/>
+      <c r="AL11" s="82"/>
+      <c r="AM11" s="82"/>
+      <c r="AN11" s="82"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="83"/>
+      <c r="AQ11" s="87"/>
+      <c r="AR11" s="82"/>
+      <c r="AS11" s="82"/>
+      <c r="AT11" s="82"/>
+      <c r="AU11" s="82"/>
+      <c r="AV11" s="82"/>
+      <c r="AW11" s="82"/>
+      <c r="AX11" s="82"/>
+      <c r="AY11" s="82"/>
+      <c r="AZ11" s="82"/>
+      <c r="BA11" s="82"/>
+      <c r="BB11" s="82"/>
+      <c r="BC11" s="82"/>
+      <c r="BD11" s="82"/>
+      <c r="BE11" s="88"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="80"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="69"/>
-      <c r="X12" s="69"/>
-      <c r="Y12" s="69"/>
-      <c r="Z12" s="69"/>
-      <c r="AA12" s="69"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="69"/>
-      <c r="AD12" s="69"/>
-      <c r="AE12" s="69"/>
-      <c r="AF12" s="69"/>
-      <c r="AG12" s="69"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="69"/>
-      <c r="AJ12" s="69"/>
-      <c r="AK12" s="69"/>
-      <c r="AL12" s="69"/>
-      <c r="AM12" s="69"/>
-      <c r="AN12" s="69"/>
-      <c r="AO12" s="69"/>
-      <c r="AP12" s="81"/>
-      <c r="AQ12" s="68"/>
-      <c r="AR12" s="69"/>
-      <c r="AS12" s="69"/>
-      <c r="AT12" s="69"/>
-      <c r="AU12" s="69"/>
-      <c r="AV12" s="69"/>
-      <c r="AW12" s="69"/>
-      <c r="AX12" s="69"/>
-      <c r="AY12" s="69"/>
-      <c r="AZ12" s="69"/>
-      <c r="BA12" s="69"/>
-      <c r="BB12" s="69"/>
-      <c r="BC12" s="69"/>
-      <c r="BD12" s="69"/>
-      <c r="BE12" s="70"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="89"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="90"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="83"/>
+      <c r="AQ12" s="87"/>
+      <c r="AR12" s="82"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="82"/>
+      <c r="AX12" s="82"/>
+      <c r="AY12" s="82"/>
+      <c r="AZ12" s="82"/>
+      <c r="BA12" s="82"/>
+      <c r="BB12" s="82"/>
+      <c r="BC12" s="82"/>
+      <c r="BD12" s="82"/>
+      <c r="BE12" s="88"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="80"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69"/>
-      <c r="T13" s="69"/>
-      <c r="U13" s="69"/>
-      <c r="V13" s="69"/>
-      <c r="W13" s="69"/>
-      <c r="X13" s="69"/>
-      <c r="Y13" s="69"/>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="69"/>
-      <c r="AB13" s="69"/>
-      <c r="AC13" s="69"/>
-      <c r="AD13" s="69"/>
-      <c r="AE13" s="69"/>
-      <c r="AF13" s="69"/>
-      <c r="AG13" s="69"/>
-      <c r="AH13" s="69"/>
-      <c r="AI13" s="69"/>
-      <c r="AJ13" s="69"/>
-      <c r="AK13" s="69"/>
-      <c r="AL13" s="69"/>
-      <c r="AM13" s="69"/>
-      <c r="AN13" s="69"/>
-      <c r="AO13" s="69"/>
-      <c r="AP13" s="81"/>
-      <c r="AQ13" s="68"/>
-      <c r="AR13" s="69"/>
-      <c r="AS13" s="69"/>
-      <c r="AT13" s="69"/>
-      <c r="AU13" s="69"/>
-      <c r="AV13" s="69"/>
-      <c r="AW13" s="69"/>
-      <c r="AX13" s="69"/>
-      <c r="AY13" s="69"/>
-      <c r="AZ13" s="69"/>
-      <c r="BA13" s="69"/>
-      <c r="BB13" s="69"/>
-      <c r="BC13" s="69"/>
-      <c r="BD13" s="69"/>
-      <c r="BE13" s="70"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="89"/>
+      <c r="K13" s="89"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="82"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="83"/>
+      <c r="AQ13" s="87"/>
+      <c r="AR13" s="82"/>
+      <c r="AS13" s="82"/>
+      <c r="AT13" s="82"/>
+      <c r="AU13" s="82"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="82"/>
+      <c r="AX13" s="82"/>
+      <c r="AY13" s="82"/>
+      <c r="AZ13" s="82"/>
+      <c r="BA13" s="82"/>
+      <c r="BB13" s="82"/>
+      <c r="BC13" s="82"/>
+      <c r="BD13" s="82"/>
+      <c r="BE13" s="88"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="69"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="69"/>
-      <c r="X14" s="69"/>
-      <c r="Y14" s="69"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="69"/>
-      <c r="AB14" s="69"/>
-      <c r="AC14" s="69"/>
-      <c r="AD14" s="69"/>
-      <c r="AE14" s="69"/>
-      <c r="AF14" s="69"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="69"/>
-      <c r="AJ14" s="69"/>
-      <c r="AK14" s="69"/>
-      <c r="AL14" s="69"/>
-      <c r="AM14" s="69"/>
-      <c r="AN14" s="69"/>
-      <c r="AO14" s="69"/>
-      <c r="AP14" s="81"/>
-      <c r="AQ14" s="68"/>
-      <c r="AR14" s="69"/>
-      <c r="AS14" s="69"/>
-      <c r="AT14" s="69"/>
-      <c r="AU14" s="69"/>
-      <c r="AV14" s="69"/>
-      <c r="AW14" s="69"/>
-      <c r="AX14" s="69"/>
-      <c r="AY14" s="69"/>
-      <c r="AZ14" s="69"/>
-      <c r="BA14" s="69"/>
-      <c r="BB14" s="69"/>
-      <c r="BC14" s="69"/>
-      <c r="BD14" s="69"/>
-      <c r="BE14" s="70"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82"/>
+      <c r="AI14" s="82"/>
+      <c r="AJ14" s="82"/>
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="82"/>
+      <c r="AN14" s="82"/>
+      <c r="AO14" s="82"/>
+      <c r="AP14" s="83"/>
+      <c r="AQ14" s="87"/>
+      <c r="AR14" s="82"/>
+      <c r="AS14" s="82"/>
+      <c r="AT14" s="82"/>
+      <c r="AU14" s="82"/>
+      <c r="AV14" s="82"/>
+      <c r="AW14" s="82"/>
+      <c r="AX14" s="82"/>
+      <c r="AY14" s="82"/>
+      <c r="AZ14" s="82"/>
+      <c r="BA14" s="82"/>
+      <c r="BB14" s="82"/>
+      <c r="BC14" s="82"/>
+      <c r="BD14" s="82"/>
+      <c r="BE14" s="88"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="69"/>
-      <c r="U15" s="69"/>
-      <c r="V15" s="69"/>
-      <c r="W15" s="69"/>
-      <c r="X15" s="69"/>
-      <c r="Y15" s="69"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="69"/>
-      <c r="AB15" s="69"/>
-      <c r="AC15" s="69"/>
-      <c r="AD15" s="69"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="69"/>
-      <c r="AG15" s="69"/>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="69"/>
-      <c r="AK15" s="69"/>
-      <c r="AL15" s="69"/>
-      <c r="AM15" s="69"/>
-      <c r="AN15" s="69"/>
-      <c r="AO15" s="69"/>
-      <c r="AP15" s="81"/>
-      <c r="AQ15" s="68"/>
-      <c r="AR15" s="69"/>
-      <c r="AS15" s="69"/>
-      <c r="AT15" s="69"/>
-      <c r="AU15" s="69"/>
-      <c r="AV15" s="69"/>
-      <c r="AW15" s="69"/>
-      <c r="AX15" s="69"/>
-      <c r="AY15" s="69"/>
-      <c r="AZ15" s="69"/>
-      <c r="BA15" s="69"/>
-      <c r="BB15" s="69"/>
-      <c r="BC15" s="69"/>
-      <c r="BD15" s="69"/>
-      <c r="BE15" s="70"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="90"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="82"/>
+      <c r="AC15" s="82"/>
+      <c r="AD15" s="82"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="82"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+      <c r="AI15" s="82"/>
+      <c r="AJ15" s="82"/>
+      <c r="AK15" s="82"/>
+      <c r="AL15" s="82"/>
+      <c r="AM15" s="82"/>
+      <c r="AN15" s="82"/>
+      <c r="AO15" s="82"/>
+      <c r="AP15" s="83"/>
+      <c r="AQ15" s="87"/>
+      <c r="AR15" s="82"/>
+      <c r="AS15" s="82"/>
+      <c r="AT15" s="82"/>
+      <c r="AU15" s="82"/>
+      <c r="AV15" s="82"/>
+      <c r="AW15" s="82"/>
+      <c r="AX15" s="82"/>
+      <c r="AY15" s="82"/>
+      <c r="AZ15" s="82"/>
+      <c r="BA15" s="82"/>
+      <c r="BB15" s="82"/>
+      <c r="BC15" s="82"/>
+      <c r="BD15" s="82"/>
+      <c r="BE15" s="88"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="99"/>
-      <c r="B16" s="100"/>
-      <c r="C16" s="100"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="100"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="69"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="69"/>
-      <c r="X16" s="69"/>
-      <c r="Y16" s="69"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="69"/>
-      <c r="AB16" s="69"/>
-      <c r="AC16" s="69"/>
-      <c r="AD16" s="69"/>
-      <c r="AE16" s="69"/>
-      <c r="AF16" s="69"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="69"/>
-      <c r="AI16" s="69"/>
-      <c r="AJ16" s="69"/>
-      <c r="AK16" s="69"/>
-      <c r="AL16" s="69"/>
-      <c r="AM16" s="69"/>
-      <c r="AN16" s="69"/>
-      <c r="AO16" s="69"/>
-      <c r="AP16" s="81"/>
-      <c r="AQ16" s="68"/>
-      <c r="AR16" s="69"/>
-      <c r="AS16" s="69"/>
-      <c r="AT16" s="69"/>
-      <c r="AU16" s="69"/>
-      <c r="AV16" s="69"/>
-      <c r="AW16" s="69"/>
-      <c r="AX16" s="69"/>
-      <c r="AY16" s="69"/>
-      <c r="AZ16" s="69"/>
-      <c r="BA16" s="69"/>
-      <c r="BB16" s="69"/>
-      <c r="BC16" s="69"/>
-      <c r="BD16" s="69"/>
-      <c r="BE16" s="70"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="89"/>
+      <c r="K16" s="89"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="82"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="82"/>
+      <c r="V16" s="82"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="82"/>
+      <c r="Y16" s="82"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="82"/>
+      <c r="AC16" s="82"/>
+      <c r="AD16" s="82"/>
+      <c r="AE16" s="82"/>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="82"/>
+      <c r="AI16" s="82"/>
+      <c r="AJ16" s="82"/>
+      <c r="AK16" s="82"/>
+      <c r="AL16" s="82"/>
+      <c r="AM16" s="82"/>
+      <c r="AN16" s="82"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="83"/>
+      <c r="AQ16" s="87"/>
+      <c r="AR16" s="82"/>
+      <c r="AS16" s="82"/>
+      <c r="AT16" s="82"/>
+      <c r="AU16" s="82"/>
+      <c r="AV16" s="82"/>
+      <c r="AW16" s="82"/>
+      <c r="AX16" s="82"/>
+      <c r="AY16" s="82"/>
+      <c r="AZ16" s="82"/>
+      <c r="BA16" s="82"/>
+      <c r="BB16" s="82"/>
+      <c r="BC16" s="82"/>
+      <c r="BD16" s="82"/>
+      <c r="BE16" s="88"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="99"/>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="69"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="69"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="69"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="69"/>
-      <c r="AB17" s="69"/>
-      <c r="AC17" s="69"/>
-      <c r="AD17" s="69"/>
-      <c r="AE17" s="69"/>
-      <c r="AF17" s="69"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="69"/>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="69"/>
-      <c r="AK17" s="69"/>
-      <c r="AL17" s="69"/>
-      <c r="AM17" s="69"/>
-      <c r="AN17" s="69"/>
-      <c r="AO17" s="69"/>
-      <c r="AP17" s="81"/>
-      <c r="AQ17" s="68"/>
-      <c r="AR17" s="69"/>
-      <c r="AS17" s="69"/>
-      <c r="AT17" s="69"/>
-      <c r="AU17" s="69"/>
-      <c r="AV17" s="69"/>
-      <c r="AW17" s="69"/>
-      <c r="AX17" s="69"/>
-      <c r="AY17" s="69"/>
-      <c r="AZ17" s="69"/>
-      <c r="BA17" s="69"/>
-      <c r="BB17" s="69"/>
-      <c r="BC17" s="69"/>
-      <c r="BD17" s="69"/>
-      <c r="BE17" s="70"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="82"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+      <c r="AI17" s="82"/>
+      <c r="AJ17" s="82"/>
+      <c r="AK17" s="82"/>
+      <c r="AL17" s="82"/>
+      <c r="AM17" s="82"/>
+      <c r="AN17" s="82"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="83"/>
+      <c r="AQ17" s="87"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="82"/>
+      <c r="AT17" s="82"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="82"/>
+      <c r="AW17" s="82"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="82"/>
+      <c r="AZ17" s="82"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="82"/>
+      <c r="BC17" s="82"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="88"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="99"/>
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="69"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="69"/>
-      <c r="X18" s="69"/>
-      <c r="Y18" s="69"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="69"/>
-      <c r="AB18" s="69"/>
-      <c r="AC18" s="69"/>
-      <c r="AD18" s="69"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="69"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="69"/>
-      <c r="AK18" s="69"/>
-      <c r="AL18" s="69"/>
-      <c r="AM18" s="69"/>
-      <c r="AN18" s="69"/>
-      <c r="AO18" s="69"/>
-      <c r="AP18" s="81"/>
-      <c r="AQ18" s="68"/>
-      <c r="AR18" s="69"/>
-      <c r="AS18" s="69"/>
-      <c r="AT18" s="69"/>
-      <c r="AU18" s="69"/>
-      <c r="AV18" s="69"/>
-      <c r="AW18" s="69"/>
-      <c r="AX18" s="69"/>
-      <c r="AY18" s="69"/>
-      <c r="AZ18" s="69"/>
-      <c r="BA18" s="69"/>
-      <c r="BB18" s="69"/>
-      <c r="BC18" s="69"/>
-      <c r="BD18" s="69"/>
-      <c r="BE18" s="70"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="89"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="82"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+      <c r="AI18" s="82"/>
+      <c r="AJ18" s="82"/>
+      <c r="AK18" s="82"/>
+      <c r="AL18" s="82"/>
+      <c r="AM18" s="82"/>
+      <c r="AN18" s="82"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="83"/>
+      <c r="AQ18" s="87"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="82"/>
+      <c r="AT18" s="82"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="82"/>
+      <c r="AW18" s="82"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="82"/>
+      <c r="AZ18" s="82"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="82"/>
+      <c r="BC18" s="82"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="88"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="69"/>
-      <c r="V19" s="69"/>
-      <c r="W19" s="69"/>
-      <c r="X19" s="69"/>
-      <c r="Y19" s="69"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="69"/>
-      <c r="AB19" s="69"/>
-      <c r="AC19" s="69"/>
-      <c r="AD19" s="69"/>
-      <c r="AE19" s="69"/>
-      <c r="AF19" s="69"/>
-      <c r="AG19" s="69"/>
-      <c r="AH19" s="69"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="69"/>
-      <c r="AK19" s="69"/>
-      <c r="AL19" s="69"/>
-      <c r="AM19" s="69"/>
-      <c r="AN19" s="69"/>
-      <c r="AO19" s="69"/>
-      <c r="AP19" s="81"/>
-      <c r="AQ19" s="68"/>
-      <c r="AR19" s="69"/>
-      <c r="AS19" s="69"/>
-      <c r="AT19" s="69"/>
-      <c r="AU19" s="69"/>
-      <c r="AV19" s="69"/>
-      <c r="AW19" s="69"/>
-      <c r="AX19" s="69"/>
-      <c r="AY19" s="69"/>
-      <c r="AZ19" s="69"/>
-      <c r="BA19" s="69"/>
-      <c r="BB19" s="69"/>
-      <c r="BC19" s="69"/>
-      <c r="BD19" s="69"/>
-      <c r="BE19" s="70"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
+      <c r="AI19" s="82"/>
+      <c r="AJ19" s="82"/>
+      <c r="AK19" s="82"/>
+      <c r="AL19" s="82"/>
+      <c r="AM19" s="82"/>
+      <c r="AN19" s="82"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="83"/>
+      <c r="AQ19" s="87"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="82"/>
+      <c r="AT19" s="82"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="82"/>
+      <c r="AW19" s="82"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="82"/>
+      <c r="AZ19" s="82"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="82"/>
+      <c r="BC19" s="82"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="88"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="101"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
-      <c r="U20" s="69"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="69"/>
-      <c r="X20" s="69"/>
-      <c r="Y20" s="69"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="69"/>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="69"/>
-      <c r="AD20" s="69"/>
-      <c r="AE20" s="69"/>
-      <c r="AF20" s="69"/>
-      <c r="AG20" s="69"/>
-      <c r="AH20" s="69"/>
-      <c r="AI20" s="69"/>
-      <c r="AJ20" s="69"/>
-      <c r="AK20" s="69"/>
-      <c r="AL20" s="69"/>
-      <c r="AM20" s="69"/>
-      <c r="AN20" s="69"/>
-      <c r="AO20" s="69"/>
-      <c r="AP20" s="81"/>
-      <c r="AQ20" s="68"/>
-      <c r="AR20" s="69"/>
-      <c r="AS20" s="69"/>
-      <c r="AT20" s="69"/>
-      <c r="AU20" s="69"/>
-      <c r="AV20" s="69"/>
-      <c r="AW20" s="69"/>
-      <c r="AX20" s="69"/>
-      <c r="AY20" s="69"/>
-      <c r="AZ20" s="69"/>
-      <c r="BA20" s="69"/>
-      <c r="BB20" s="69"/>
-      <c r="BC20" s="69"/>
-      <c r="BD20" s="69"/>
-      <c r="BE20" s="70"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="87"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="88"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="100"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="101"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
-      <c r="U21" s="69"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="69"/>
-      <c r="X21" s="69"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="69"/>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="69"/>
-      <c r="AD21" s="69"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="69"/>
-      <c r="AG21" s="69"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="69"/>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="69"/>
-      <c r="AL21" s="69"/>
-      <c r="AM21" s="69"/>
-      <c r="AN21" s="69"/>
-      <c r="AO21" s="69"/>
-      <c r="AP21" s="81"/>
-      <c r="AQ21" s="68"/>
-      <c r="AR21" s="69"/>
-      <c r="AS21" s="69"/>
-      <c r="AT21" s="69"/>
-      <c r="AU21" s="69"/>
-      <c r="AV21" s="69"/>
-      <c r="AW21" s="69"/>
-      <c r="AX21" s="69"/>
-      <c r="AY21" s="69"/>
-      <c r="AZ21" s="69"/>
-      <c r="BA21" s="69"/>
-      <c r="BB21" s="69"/>
-      <c r="BC21" s="69"/>
-      <c r="BD21" s="69"/>
-      <c r="BE21" s="70"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="89"/>
+      <c r="L21" s="89"/>
+      <c r="M21" s="89"/>
+      <c r="N21" s="90"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82"/>
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="82"/>
+      <c r="Y21" s="82"/>
+      <c r="Z21" s="82"/>
+      <c r="AA21" s="82"/>
+      <c r="AB21" s="82"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
+      <c r="AE21" s="82"/>
+      <c r="AF21" s="82"/>
+      <c r="AG21" s="82"/>
+      <c r="AH21" s="82"/>
+      <c r="AI21" s="82"/>
+      <c r="AJ21" s="82"/>
+      <c r="AK21" s="82"/>
+      <c r="AL21" s="82"/>
+      <c r="AM21" s="82"/>
+      <c r="AN21" s="82"/>
+      <c r="AO21" s="82"/>
+      <c r="AP21" s="83"/>
+      <c r="AQ21" s="87"/>
+      <c r="AR21" s="82"/>
+      <c r="AS21" s="82"/>
+      <c r="AT21" s="82"/>
+      <c r="AU21" s="82"/>
+      <c r="AV21" s="82"/>
+      <c r="AW21" s="82"/>
+      <c r="AX21" s="82"/>
+      <c r="AY21" s="82"/>
+      <c r="AZ21" s="82"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="82"/>
+      <c r="BC21" s="82"/>
+      <c r="BD21" s="82"/>
+      <c r="BE21" s="88"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="101"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="79"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="69"/>
-      <c r="X22" s="69"/>
-      <c r="Y22" s="69"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="69"/>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="69"/>
-      <c r="AD22" s="69"/>
-      <c r="AE22" s="69"/>
-      <c r="AF22" s="69"/>
-      <c r="AG22" s="69"/>
-      <c r="AH22" s="69"/>
-      <c r="AI22" s="69"/>
-      <c r="AJ22" s="69"/>
-      <c r="AK22" s="69"/>
-      <c r="AL22" s="69"/>
-      <c r="AM22" s="69"/>
-      <c r="AN22" s="69"/>
-      <c r="AO22" s="69"/>
-      <c r="AP22" s="81"/>
-      <c r="AQ22" s="68"/>
-      <c r="AR22" s="69"/>
-      <c r="AS22" s="69"/>
-      <c r="AT22" s="69"/>
-      <c r="AU22" s="69"/>
-      <c r="AV22" s="69"/>
-      <c r="AW22" s="69"/>
-      <c r="AX22" s="69"/>
-      <c r="AY22" s="69"/>
-      <c r="AZ22" s="69"/>
-      <c r="BA22" s="69"/>
-      <c r="BB22" s="69"/>
-      <c r="BC22" s="69"/>
-      <c r="BD22" s="69"/>
-      <c r="BE22" s="70"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="82"/>
+      <c r="Y22" s="82"/>
+      <c r="Z22" s="82"/>
+      <c r="AA22" s="82"/>
+      <c r="AB22" s="82"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
+      <c r="AE22" s="82"/>
+      <c r="AF22" s="82"/>
+      <c r="AG22" s="82"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="82"/>
+      <c r="AJ22" s="82"/>
+      <c r="AK22" s="82"/>
+      <c r="AL22" s="82"/>
+      <c r="AM22" s="82"/>
+      <c r="AN22" s="82"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="83"/>
+      <c r="AQ22" s="87"/>
+      <c r="AR22" s="82"/>
+      <c r="AS22" s="82"/>
+      <c r="AT22" s="82"/>
+      <c r="AU22" s="82"/>
+      <c r="AV22" s="82"/>
+      <c r="AW22" s="82"/>
+      <c r="AX22" s="82"/>
+      <c r="AY22" s="82"/>
+      <c r="AZ22" s="82"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="82"/>
+      <c r="BC22" s="82"/>
+      <c r="BD22" s="82"/>
+      <c r="BE22" s="88"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="79"/>
-      <c r="N23" s="80"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="69"/>
-      <c r="T23" s="69"/>
-      <c r="U23" s="69"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="69"/>
-      <c r="X23" s="69"/>
-      <c r="Y23" s="69"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="69"/>
-      <c r="AB23" s="69"/>
-      <c r="AC23" s="69"/>
-      <c r="AD23" s="69"/>
-      <c r="AE23" s="69"/>
-      <c r="AF23" s="69"/>
-      <c r="AG23" s="69"/>
-      <c r="AH23" s="69"/>
-      <c r="AI23" s="69"/>
-      <c r="AJ23" s="69"/>
-      <c r="AK23" s="69"/>
-      <c r="AL23" s="69"/>
-      <c r="AM23" s="69"/>
-      <c r="AN23" s="69"/>
-      <c r="AO23" s="69"/>
-      <c r="AP23" s="81"/>
-      <c r="AQ23" s="68"/>
-      <c r="AR23" s="69"/>
-      <c r="AS23" s="69"/>
-      <c r="AT23" s="69"/>
-      <c r="AU23" s="69"/>
-      <c r="AV23" s="69"/>
-      <c r="AW23" s="69"/>
-      <c r="AX23" s="69"/>
-      <c r="AY23" s="69"/>
-      <c r="AZ23" s="69"/>
-      <c r="BA23" s="69"/>
-      <c r="BB23" s="69"/>
-      <c r="BC23" s="69"/>
-      <c r="BD23" s="69"/>
-      <c r="BE23" s="70"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="82"/>
+      <c r="Y23" s="82"/>
+      <c r="Z23" s="82"/>
+      <c r="AA23" s="82"/>
+      <c r="AB23" s="82"/>
+      <c r="AC23" s="82"/>
+      <c r="AD23" s="82"/>
+      <c r="AE23" s="82"/>
+      <c r="AF23" s="82"/>
+      <c r="AG23" s="82"/>
+      <c r="AH23" s="82"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="82"/>
+      <c r="AK23" s="82"/>
+      <c r="AL23" s="82"/>
+      <c r="AM23" s="82"/>
+      <c r="AN23" s="82"/>
+      <c r="AO23" s="82"/>
+      <c r="AP23" s="83"/>
+      <c r="AQ23" s="87"/>
+      <c r="AR23" s="82"/>
+      <c r="AS23" s="82"/>
+      <c r="AT23" s="82"/>
+      <c r="AU23" s="82"/>
+      <c r="AV23" s="82"/>
+      <c r="AW23" s="82"/>
+      <c r="AX23" s="82"/>
+      <c r="AY23" s="82"/>
+      <c r="AZ23" s="82"/>
+      <c r="BA23" s="82"/>
+      <c r="BB23" s="82"/>
+      <c r="BC23" s="82"/>
+      <c r="BD23" s="82"/>
+      <c r="BE23" s="88"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="99"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="69"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="69"/>
-      <c r="AD24" s="69"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="69"/>
-      <c r="AG24" s="69"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="69"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
-      <c r="AL24" s="69"/>
-      <c r="AM24" s="69"/>
-      <c r="AN24" s="69"/>
-      <c r="AO24" s="69"/>
-      <c r="AP24" s="81"/>
-      <c r="AQ24" s="68"/>
-      <c r="AR24" s="69"/>
-      <c r="AS24" s="69"/>
-      <c r="AT24" s="69"/>
-      <c r="AU24" s="69"/>
-      <c r="AV24" s="69"/>
-      <c r="AW24" s="69"/>
-      <c r="AX24" s="69"/>
-      <c r="AY24" s="69"/>
-      <c r="AZ24" s="69"/>
-      <c r="BA24" s="69"/>
-      <c r="BB24" s="69"/>
-      <c r="BC24" s="69"/>
-      <c r="BD24" s="69"/>
-      <c r="BE24" s="70"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82"/>
+      <c r="R24" s="82"/>
+      <c r="S24" s="82"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
+      <c r="Y24" s="82"/>
+      <c r="Z24" s="82"/>
+      <c r="AA24" s="82"/>
+      <c r="AB24" s="82"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
+      <c r="AE24" s="82"/>
+      <c r="AF24" s="82"/>
+      <c r="AG24" s="82"/>
+      <c r="AH24" s="82"/>
+      <c r="AI24" s="82"/>
+      <c r="AJ24" s="82"/>
+      <c r="AK24" s="82"/>
+      <c r="AL24" s="82"/>
+      <c r="AM24" s="82"/>
+      <c r="AN24" s="82"/>
+      <c r="AO24" s="82"/>
+      <c r="AP24" s="83"/>
+      <c r="AQ24" s="87"/>
+      <c r="AR24" s="82"/>
+      <c r="AS24" s="82"/>
+      <c r="AT24" s="82"/>
+      <c r="AU24" s="82"/>
+      <c r="AV24" s="82"/>
+      <c r="AW24" s="82"/>
+      <c r="AX24" s="82"/>
+      <c r="AY24" s="82"/>
+      <c r="AZ24" s="82"/>
+      <c r="BA24" s="82"/>
+      <c r="BB24" s="82"/>
+      <c r="BC24" s="82"/>
+      <c r="BD24" s="82"/>
+      <c r="BE24" s="88"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="99"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="101"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="69"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="69"/>
-      <c r="AD25" s="69"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="69"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
-      <c r="AL25" s="69"/>
-      <c r="AM25" s="69"/>
-      <c r="AN25" s="69"/>
-      <c r="AO25" s="69"/>
-      <c r="AP25" s="81"/>
-      <c r="AQ25" s="68"/>
-      <c r="AR25" s="69"/>
-      <c r="AS25" s="69"/>
-      <c r="AT25" s="69"/>
-      <c r="AU25" s="69"/>
-      <c r="AV25" s="69"/>
-      <c r="AW25" s="69"/>
-      <c r="AX25" s="69"/>
-      <c r="AY25" s="69"/>
-      <c r="AZ25" s="69"/>
-      <c r="BA25" s="69"/>
-      <c r="BB25" s="69"/>
-      <c r="BC25" s="69"/>
-      <c r="BD25" s="69"/>
-      <c r="BE25" s="70"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="82"/>
+      <c r="AD25" s="82"/>
+      <c r="AE25" s="82"/>
+      <c r="AF25" s="82"/>
+      <c r="AG25" s="82"/>
+      <c r="AH25" s="82"/>
+      <c r="AI25" s="82"/>
+      <c r="AJ25" s="82"/>
+      <c r="AK25" s="82"/>
+      <c r="AL25" s="82"/>
+      <c r="AM25" s="82"/>
+      <c r="AN25" s="82"/>
+      <c r="AO25" s="82"/>
+      <c r="AP25" s="83"/>
+      <c r="AQ25" s="87"/>
+      <c r="AR25" s="82"/>
+      <c r="AS25" s="82"/>
+      <c r="AT25" s="82"/>
+      <c r="AU25" s="82"/>
+      <c r="AV25" s="82"/>
+      <c r="AW25" s="82"/>
+      <c r="AX25" s="82"/>
+      <c r="AY25" s="82"/>
+      <c r="AZ25" s="82"/>
+      <c r="BA25" s="82"/>
+      <c r="BB25" s="82"/>
+      <c r="BC25" s="82"/>
+      <c r="BD25" s="82"/>
+      <c r="BE25" s="88"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="79"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="69"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="69"/>
-      <c r="U26" s="69"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="69"/>
-      <c r="X26" s="69"/>
-      <c r="Y26" s="69"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="69"/>
-      <c r="AB26" s="69"/>
-      <c r="AC26" s="69"/>
-      <c r="AD26" s="69"/>
-      <c r="AE26" s="69"/>
-      <c r="AF26" s="69"/>
-      <c r="AG26" s="69"/>
-      <c r="AH26" s="69"/>
-      <c r="AI26" s="69"/>
-      <c r="AJ26" s="69"/>
-      <c r="AK26" s="69"/>
-      <c r="AL26" s="69"/>
-      <c r="AM26" s="69"/>
-      <c r="AN26" s="69"/>
-      <c r="AO26" s="69"/>
-      <c r="AP26" s="81"/>
-      <c r="AQ26" s="68"/>
-      <c r="AR26" s="69"/>
-      <c r="AS26" s="69"/>
-      <c r="AT26" s="69"/>
-      <c r="AU26" s="69"/>
-      <c r="AV26" s="69"/>
-      <c r="AW26" s="69"/>
-      <c r="AX26" s="69"/>
-      <c r="AY26" s="69"/>
-      <c r="AZ26" s="69"/>
-      <c r="BA26" s="69"/>
-      <c r="BB26" s="69"/>
-      <c r="BC26" s="69"/>
-      <c r="BD26" s="69"/>
-      <c r="BE26" s="70"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="89"/>
+      <c r="N26" s="90"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="82"/>
+      <c r="S26" s="82"/>
+      <c r="T26" s="82"/>
+      <c r="U26" s="82"/>
+      <c r="V26" s="82"/>
+      <c r="W26" s="82"/>
+      <c r="X26" s="82"/>
+      <c r="Y26" s="82"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="82"/>
+      <c r="AF26" s="82"/>
+      <c r="AG26" s="82"/>
+      <c r="AH26" s="82"/>
+      <c r="AI26" s="82"/>
+      <c r="AJ26" s="82"/>
+      <c r="AK26" s="82"/>
+      <c r="AL26" s="82"/>
+      <c r="AM26" s="82"/>
+      <c r="AN26" s="82"/>
+      <c r="AO26" s="82"/>
+      <c r="AP26" s="83"/>
+      <c r="AQ26" s="87"/>
+      <c r="AR26" s="82"/>
+      <c r="AS26" s="82"/>
+      <c r="AT26" s="82"/>
+      <c r="AU26" s="82"/>
+      <c r="AV26" s="82"/>
+      <c r="AW26" s="82"/>
+      <c r="AX26" s="82"/>
+      <c r="AY26" s="82"/>
+      <c r="AZ26" s="82"/>
+      <c r="BA26" s="82"/>
+      <c r="BB26" s="82"/>
+      <c r="BC26" s="82"/>
+      <c r="BD26" s="82"/>
+      <c r="BE26" s="88"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="79"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="69"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="69"/>
-      <c r="T27" s="69"/>
-      <c r="U27" s="69"/>
-      <c r="V27" s="69"/>
-      <c r="W27" s="69"/>
-      <c r="X27" s="69"/>
-      <c r="Y27" s="69"/>
-      <c r="Z27" s="69"/>
-      <c r="AA27" s="69"/>
-      <c r="AB27" s="69"/>
-      <c r="AC27" s="69"/>
-      <c r="AD27" s="69"/>
-      <c r="AE27" s="69"/>
-      <c r="AF27" s="69"/>
-      <c r="AG27" s="69"/>
-      <c r="AH27" s="69"/>
-      <c r="AI27" s="69"/>
-      <c r="AJ27" s="69"/>
-      <c r="AK27" s="69"/>
-      <c r="AL27" s="69"/>
-      <c r="AM27" s="69"/>
-      <c r="AN27" s="69"/>
-      <c r="AO27" s="69"/>
-      <c r="AP27" s="81"/>
-      <c r="AQ27" s="68"/>
-      <c r="AR27" s="69"/>
-      <c r="AS27" s="69"/>
-      <c r="AT27" s="69"/>
-      <c r="AU27" s="69"/>
-      <c r="AV27" s="69"/>
-      <c r="AW27" s="69"/>
-      <c r="AX27" s="69"/>
-      <c r="AY27" s="69"/>
-      <c r="AZ27" s="69"/>
-      <c r="BA27" s="69"/>
-      <c r="BB27" s="69"/>
-      <c r="BC27" s="69"/>
-      <c r="BD27" s="69"/>
-      <c r="BE27" s="70"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="82"/>
+      <c r="S27" s="82"/>
+      <c r="T27" s="82"/>
+      <c r="U27" s="82"/>
+      <c r="V27" s="82"/>
+      <c r="W27" s="82"/>
+      <c r="X27" s="82"/>
+      <c r="Y27" s="82"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="82"/>
+      <c r="AF27" s="82"/>
+      <c r="AG27" s="82"/>
+      <c r="AH27" s="82"/>
+      <c r="AI27" s="82"/>
+      <c r="AJ27" s="82"/>
+      <c r="AK27" s="82"/>
+      <c r="AL27" s="82"/>
+      <c r="AM27" s="82"/>
+      <c r="AN27" s="82"/>
+      <c r="AO27" s="82"/>
+      <c r="AP27" s="83"/>
+      <c r="AQ27" s="87"/>
+      <c r="AR27" s="82"/>
+      <c r="AS27" s="82"/>
+      <c r="AT27" s="82"/>
+      <c r="AU27" s="82"/>
+      <c r="AV27" s="82"/>
+      <c r="AW27" s="82"/>
+      <c r="AX27" s="82"/>
+      <c r="AY27" s="82"/>
+      <c r="AZ27" s="82"/>
+      <c r="BA27" s="82"/>
+      <c r="BB27" s="82"/>
+      <c r="BC27" s="82"/>
+      <c r="BD27" s="82"/>
+      <c r="BE27" s="88"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="99"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="100"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="69"/>
-      <c r="R28" s="69"/>
-      <c r="S28" s="69"/>
-      <c r="T28" s="69"/>
-      <c r="U28" s="69"/>
-      <c r="V28" s="69"/>
-      <c r="W28" s="69"/>
-      <c r="X28" s="69"/>
-      <c r="Y28" s="69"/>
-      <c r="Z28" s="69"/>
-      <c r="AA28" s="69"/>
-      <c r="AB28" s="69"/>
-      <c r="AC28" s="69"/>
-      <c r="AD28" s="69"/>
-      <c r="AE28" s="69"/>
-      <c r="AF28" s="69"/>
-      <c r="AG28" s="69"/>
-      <c r="AH28" s="69"/>
-      <c r="AI28" s="69"/>
-      <c r="AJ28" s="69"/>
-      <c r="AK28" s="69"/>
-      <c r="AL28" s="69"/>
-      <c r="AM28" s="69"/>
-      <c r="AN28" s="69"/>
-      <c r="AO28" s="69"/>
-      <c r="AP28" s="81"/>
-      <c r="AQ28" s="68"/>
-      <c r="AR28" s="69"/>
-      <c r="AS28" s="69"/>
-      <c r="AT28" s="69"/>
-      <c r="AU28" s="69"/>
-      <c r="AV28" s="69"/>
-      <c r="AW28" s="69"/>
-      <c r="AX28" s="69"/>
-      <c r="AY28" s="69"/>
-      <c r="AZ28" s="69"/>
-      <c r="BA28" s="69"/>
-      <c r="BB28" s="69"/>
-      <c r="BC28" s="69"/>
-      <c r="BD28" s="69"/>
-      <c r="BE28" s="70"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="82"/>
+      <c r="S28" s="82"/>
+      <c r="T28" s="82"/>
+      <c r="U28" s="82"/>
+      <c r="V28" s="82"/>
+      <c r="W28" s="82"/>
+      <c r="X28" s="82"/>
+      <c r="Y28" s="82"/>
+      <c r="Z28" s="82"/>
+      <c r="AA28" s="82"/>
+      <c r="AB28" s="82"/>
+      <c r="AC28" s="82"/>
+      <c r="AD28" s="82"/>
+      <c r="AE28" s="82"/>
+      <c r="AF28" s="82"/>
+      <c r="AG28" s="82"/>
+      <c r="AH28" s="82"/>
+      <c r="AI28" s="82"/>
+      <c r="AJ28" s="82"/>
+      <c r="AK28" s="82"/>
+      <c r="AL28" s="82"/>
+      <c r="AM28" s="82"/>
+      <c r="AN28" s="82"/>
+      <c r="AO28" s="82"/>
+      <c r="AP28" s="83"/>
+      <c r="AQ28" s="87"/>
+      <c r="AR28" s="82"/>
+      <c r="AS28" s="82"/>
+      <c r="AT28" s="82"/>
+      <c r="AU28" s="82"/>
+      <c r="AV28" s="82"/>
+      <c r="AW28" s="82"/>
+      <c r="AX28" s="82"/>
+      <c r="AY28" s="82"/>
+      <c r="AZ28" s="82"/>
+      <c r="BA28" s="82"/>
+      <c r="BB28" s="82"/>
+      <c r="BC28" s="82"/>
+      <c r="BD28" s="82"/>
+      <c r="BE28" s="88"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="99"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="100"/>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="100"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="80"/>
-      <c r="O29" s="78"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="69"/>
-      <c r="R29" s="69"/>
-      <c r="S29" s="69"/>
-      <c r="T29" s="69"/>
-      <c r="U29" s="69"/>
-      <c r="V29" s="69"/>
-      <c r="W29" s="69"/>
-      <c r="X29" s="69"/>
-      <c r="Y29" s="69"/>
-      <c r="Z29" s="69"/>
-      <c r="AA29" s="69"/>
-      <c r="AB29" s="69"/>
-      <c r="AC29" s="69"/>
-      <c r="AD29" s="69"/>
-      <c r="AE29" s="69"/>
-      <c r="AF29" s="69"/>
-      <c r="AG29" s="69"/>
-      <c r="AH29" s="69"/>
-      <c r="AI29" s="69"/>
-      <c r="AJ29" s="69"/>
-      <c r="AK29" s="69"/>
-      <c r="AL29" s="69"/>
-      <c r="AM29" s="69"/>
-      <c r="AN29" s="69"/>
-      <c r="AO29" s="69"/>
-      <c r="AP29" s="81"/>
-      <c r="AQ29" s="68"/>
-      <c r="AR29" s="69"/>
-      <c r="AS29" s="69"/>
-      <c r="AT29" s="69"/>
-      <c r="AU29" s="69"/>
-      <c r="AV29" s="69"/>
-      <c r="AW29" s="69"/>
-      <c r="AX29" s="69"/>
-      <c r="AY29" s="69"/>
-      <c r="AZ29" s="69"/>
-      <c r="BA29" s="69"/>
-      <c r="BB29" s="69"/>
-      <c r="BC29" s="69"/>
-      <c r="BD29" s="69"/>
-      <c r="BE29" s="70"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="82"/>
+      <c r="T29" s="82"/>
+      <c r="U29" s="82"/>
+      <c r="V29" s="82"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="82"/>
+      <c r="Y29" s="82"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="82"/>
+      <c r="AF29" s="82"/>
+      <c r="AG29" s="82"/>
+      <c r="AH29" s="82"/>
+      <c r="AI29" s="82"/>
+      <c r="AJ29" s="82"/>
+      <c r="AK29" s="82"/>
+      <c r="AL29" s="82"/>
+      <c r="AM29" s="82"/>
+      <c r="AN29" s="82"/>
+      <c r="AO29" s="82"/>
+      <c r="AP29" s="83"/>
+      <c r="AQ29" s="87"/>
+      <c r="AR29" s="82"/>
+      <c r="AS29" s="82"/>
+      <c r="AT29" s="82"/>
+      <c r="AU29" s="82"/>
+      <c r="AV29" s="82"/>
+      <c r="AW29" s="82"/>
+      <c r="AX29" s="82"/>
+      <c r="AY29" s="82"/>
+      <c r="AZ29" s="82"/>
+      <c r="BA29" s="82"/>
+      <c r="BB29" s="82"/>
+      <c r="BC29" s="82"/>
+      <c r="BD29" s="82"/>
+      <c r="BE29" s="88"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="99"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="101"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="80"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="69"/>
-      <c r="Q30" s="69"/>
-      <c r="R30" s="69"/>
-      <c r="S30" s="69"/>
-      <c r="T30" s="69"/>
-      <c r="U30" s="69"/>
-      <c r="V30" s="69"/>
-      <c r="W30" s="69"/>
-      <c r="X30" s="69"/>
-      <c r="Y30" s="69"/>
-      <c r="Z30" s="69"/>
-      <c r="AA30" s="69"/>
-      <c r="AB30" s="69"/>
-      <c r="AC30" s="69"/>
-      <c r="AD30" s="69"/>
-      <c r="AE30" s="69"/>
-      <c r="AF30" s="69"/>
-      <c r="AG30" s="69"/>
-      <c r="AH30" s="69"/>
-      <c r="AI30" s="69"/>
-      <c r="AJ30" s="69"/>
-      <c r="AK30" s="69"/>
-      <c r="AL30" s="69"/>
-      <c r="AM30" s="69"/>
-      <c r="AN30" s="69"/>
-      <c r="AO30" s="69"/>
-      <c r="AP30" s="81"/>
-      <c r="AQ30" s="68"/>
-      <c r="AR30" s="69"/>
-      <c r="AS30" s="69"/>
-      <c r="AT30" s="69"/>
-      <c r="AU30" s="69"/>
-      <c r="AV30" s="69"/>
-      <c r="AW30" s="69"/>
-      <c r="AX30" s="69"/>
-      <c r="AY30" s="69"/>
-      <c r="AZ30" s="69"/>
-      <c r="BA30" s="69"/>
-      <c r="BB30" s="69"/>
-      <c r="BC30" s="69"/>
-      <c r="BD30" s="69"/>
-      <c r="BE30" s="70"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
+      <c r="L30" s="89"/>
+      <c r="M30" s="89"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82"/>
+      <c r="R30" s="82"/>
+      <c r="S30" s="82"/>
+      <c r="T30" s="82"/>
+      <c r="U30" s="82"/>
+      <c r="V30" s="82"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="82"/>
+      <c r="Y30" s="82"/>
+      <c r="Z30" s="82"/>
+      <c r="AA30" s="82"/>
+      <c r="AB30" s="82"/>
+      <c r="AC30" s="82"/>
+      <c r="AD30" s="82"/>
+      <c r="AE30" s="82"/>
+      <c r="AF30" s="82"/>
+      <c r="AG30" s="82"/>
+      <c r="AH30" s="82"/>
+      <c r="AI30" s="82"/>
+      <c r="AJ30" s="82"/>
+      <c r="AK30" s="82"/>
+      <c r="AL30" s="82"/>
+      <c r="AM30" s="82"/>
+      <c r="AN30" s="82"/>
+      <c r="AO30" s="82"/>
+      <c r="AP30" s="83"/>
+      <c r="AQ30" s="87"/>
+      <c r="AR30" s="82"/>
+      <c r="AS30" s="82"/>
+      <c r="AT30" s="82"/>
+      <c r="AU30" s="82"/>
+      <c r="AV30" s="82"/>
+      <c r="AW30" s="82"/>
+      <c r="AX30" s="82"/>
+      <c r="AY30" s="82"/>
+      <c r="AZ30" s="82"/>
+      <c r="BA30" s="82"/>
+      <c r="BB30" s="82"/>
+      <c r="BC30" s="82"/>
+      <c r="BD30" s="82"/>
+      <c r="BE30" s="88"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
-      <c r="S31" s="69"/>
-      <c r="T31" s="69"/>
-      <c r="U31" s="69"/>
-      <c r="V31" s="69"/>
-      <c r="W31" s="69"/>
-      <c r="X31" s="69"/>
-      <c r="Y31" s="69"/>
-      <c r="Z31" s="69"/>
-      <c r="AA31" s="69"/>
-      <c r="AB31" s="69"/>
-      <c r="AC31" s="69"/>
-      <c r="AD31" s="69"/>
-      <c r="AE31" s="69"/>
-      <c r="AF31" s="69"/>
-      <c r="AG31" s="69"/>
-      <c r="AH31" s="69"/>
-      <c r="AI31" s="69"/>
-      <c r="AJ31" s="69"/>
-      <c r="AK31" s="69"/>
-      <c r="AL31" s="69"/>
-      <c r="AM31" s="69"/>
-      <c r="AN31" s="69"/>
-      <c r="AO31" s="69"/>
-      <c r="AP31" s="81"/>
-      <c r="AQ31" s="68"/>
-      <c r="AR31" s="69"/>
-      <c r="AS31" s="69"/>
-      <c r="AT31" s="69"/>
-      <c r="AU31" s="69"/>
-      <c r="AV31" s="69"/>
-      <c r="AW31" s="69"/>
-      <c r="AX31" s="69"/>
-      <c r="AY31" s="69"/>
-      <c r="AZ31" s="69"/>
-      <c r="BA31" s="69"/>
-      <c r="BB31" s="69"/>
-      <c r="BC31" s="69"/>
-      <c r="BD31" s="69"/>
-      <c r="BE31" s="70"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
+      <c r="M31" s="89"/>
+      <c r="N31" s="90"/>
+      <c r="O31" s="81"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82"/>
+      <c r="R31" s="82"/>
+      <c r="S31" s="82"/>
+      <c r="T31" s="82"/>
+      <c r="U31" s="82"/>
+      <c r="V31" s="82"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="82"/>
+      <c r="Y31" s="82"/>
+      <c r="Z31" s="82"/>
+      <c r="AA31" s="82"/>
+      <c r="AB31" s="82"/>
+      <c r="AC31" s="82"/>
+      <c r="AD31" s="82"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="82"/>
+      <c r="AI31" s="82"/>
+      <c r="AJ31" s="82"/>
+      <c r="AK31" s="82"/>
+      <c r="AL31" s="82"/>
+      <c r="AM31" s="82"/>
+      <c r="AN31" s="82"/>
+      <c r="AO31" s="82"/>
+      <c r="AP31" s="83"/>
+      <c r="AQ31" s="87"/>
+      <c r="AR31" s="82"/>
+      <c r="AS31" s="82"/>
+      <c r="AT31" s="82"/>
+      <c r="AU31" s="82"/>
+      <c r="AV31" s="82"/>
+      <c r="AW31" s="82"/>
+      <c r="AX31" s="82"/>
+      <c r="AY31" s="82"/>
+      <c r="AZ31" s="82"/>
+      <c r="BA31" s="82"/>
+      <c r="BB31" s="82"/>
+      <c r="BC31" s="82"/>
+      <c r="BD31" s="82"/>
+      <c r="BE31" s="88"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="99"/>
-      <c r="B32" s="100"/>
-      <c r="C32" s="100"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="100"/>
-      <c r="F32" s="100"/>
-      <c r="G32" s="101"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="69"/>
-      <c r="Q32" s="69"/>
-      <c r="R32" s="69"/>
-      <c r="S32" s="69"/>
-      <c r="T32" s="69"/>
-      <c r="U32" s="69"/>
-      <c r="V32" s="69"/>
-      <c r="W32" s="69"/>
-      <c r="X32" s="69"/>
-      <c r="Y32" s="69"/>
-      <c r="Z32" s="69"/>
-      <c r="AA32" s="69"/>
-      <c r="AB32" s="69"/>
-      <c r="AC32" s="69"/>
-      <c r="AD32" s="69"/>
-      <c r="AE32" s="69"/>
-      <c r="AF32" s="69"/>
-      <c r="AG32" s="69"/>
-      <c r="AH32" s="69"/>
-      <c r="AI32" s="69"/>
-      <c r="AJ32" s="69"/>
-      <c r="AK32" s="69"/>
-      <c r="AL32" s="69"/>
-      <c r="AM32" s="69"/>
-      <c r="AN32" s="69"/>
-      <c r="AO32" s="69"/>
-      <c r="AP32" s="81"/>
-      <c r="AQ32" s="68"/>
-      <c r="AR32" s="69"/>
-      <c r="AS32" s="69"/>
-      <c r="AT32" s="69"/>
-      <c r="AU32" s="69"/>
-      <c r="AV32" s="69"/>
-      <c r="AW32" s="69"/>
-      <c r="AX32" s="69"/>
-      <c r="AY32" s="69"/>
-      <c r="AZ32" s="69"/>
-      <c r="BA32" s="69"/>
-      <c r="BB32" s="69"/>
-      <c r="BC32" s="69"/>
-      <c r="BD32" s="69"/>
-      <c r="BE32" s="70"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
+      <c r="M32" s="89"/>
+      <c r="N32" s="90"/>
+      <c r="O32" s="81"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="82"/>
+      <c r="T32" s="82"/>
+      <c r="U32" s="82"/>
+      <c r="V32" s="82"/>
+      <c r="W32" s="82"/>
+      <c r="X32" s="82"/>
+      <c r="Y32" s="82"/>
+      <c r="Z32" s="82"/>
+      <c r="AA32" s="82"/>
+      <c r="AB32" s="82"/>
+      <c r="AC32" s="82"/>
+      <c r="AD32" s="82"/>
+      <c r="AE32" s="82"/>
+      <c r="AF32" s="82"/>
+      <c r="AG32" s="82"/>
+      <c r="AH32" s="82"/>
+      <c r="AI32" s="82"/>
+      <c r="AJ32" s="82"/>
+      <c r="AK32" s="82"/>
+      <c r="AL32" s="82"/>
+      <c r="AM32" s="82"/>
+      <c r="AN32" s="82"/>
+      <c r="AO32" s="82"/>
+      <c r="AP32" s="83"/>
+      <c r="AQ32" s="87"/>
+      <c r="AR32" s="82"/>
+      <c r="AS32" s="82"/>
+      <c r="AT32" s="82"/>
+      <c r="AU32" s="82"/>
+      <c r="AV32" s="82"/>
+      <c r="AW32" s="82"/>
+      <c r="AX32" s="82"/>
+      <c r="AY32" s="82"/>
+      <c r="AZ32" s="82"/>
+      <c r="BA32" s="82"/>
+      <c r="BB32" s="82"/>
+      <c r="BC32" s="82"/>
+      <c r="BD32" s="82"/>
+      <c r="BE32" s="88"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="99"/>
-      <c r="B33" s="100"/>
-      <c r="C33" s="100"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="80"/>
-      <c r="O33" s="78"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="69"/>
-      <c r="U33" s="69"/>
-      <c r="V33" s="69"/>
-      <c r="W33" s="69"/>
-      <c r="X33" s="69"/>
-      <c r="Y33" s="69"/>
-      <c r="Z33" s="69"/>
-      <c r="AA33" s="69"/>
-      <c r="AB33" s="69"/>
-      <c r="AC33" s="69"/>
-      <c r="AD33" s="69"/>
-      <c r="AE33" s="69"/>
-      <c r="AF33" s="69"/>
-      <c r="AG33" s="69"/>
-      <c r="AH33" s="69"/>
-      <c r="AI33" s="69"/>
-      <c r="AJ33" s="69"/>
-      <c r="AK33" s="69"/>
-      <c r="AL33" s="69"/>
-      <c r="AM33" s="69"/>
-      <c r="AN33" s="69"/>
-      <c r="AO33" s="69"/>
-      <c r="AP33" s="81"/>
-      <c r="AQ33" s="68"/>
-      <c r="AR33" s="69"/>
-      <c r="AS33" s="69"/>
-      <c r="AT33" s="69"/>
-      <c r="AU33" s="69"/>
-      <c r="AV33" s="69"/>
-      <c r="AW33" s="69"/>
-      <c r="AX33" s="69"/>
-      <c r="AY33" s="69"/>
-      <c r="AZ33" s="69"/>
-      <c r="BA33" s="69"/>
-      <c r="BB33" s="69"/>
-      <c r="BC33" s="69"/>
-      <c r="BD33" s="69"/>
-      <c r="BE33" s="70"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
+      <c r="M33" s="89"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="82"/>
+      <c r="T33" s="82"/>
+      <c r="U33" s="82"/>
+      <c r="V33" s="82"/>
+      <c r="W33" s="82"/>
+      <c r="X33" s="82"/>
+      <c r="Y33" s="82"/>
+      <c r="Z33" s="82"/>
+      <c r="AA33" s="82"/>
+      <c r="AB33" s="82"/>
+      <c r="AC33" s="82"/>
+      <c r="AD33" s="82"/>
+      <c r="AE33" s="82"/>
+      <c r="AF33" s="82"/>
+      <c r="AG33" s="82"/>
+      <c r="AH33" s="82"/>
+      <c r="AI33" s="82"/>
+      <c r="AJ33" s="82"/>
+      <c r="AK33" s="82"/>
+      <c r="AL33" s="82"/>
+      <c r="AM33" s="82"/>
+      <c r="AN33" s="82"/>
+      <c r="AO33" s="82"/>
+      <c r="AP33" s="83"/>
+      <c r="AQ33" s="87"/>
+      <c r="AR33" s="82"/>
+      <c r="AS33" s="82"/>
+      <c r="AT33" s="82"/>
+      <c r="AU33" s="82"/>
+      <c r="AV33" s="82"/>
+      <c r="AW33" s="82"/>
+      <c r="AX33" s="82"/>
+      <c r="AY33" s="82"/>
+      <c r="AZ33" s="82"/>
+      <c r="BA33" s="82"/>
+      <c r="BB33" s="82"/>
+      <c r="BC33" s="82"/>
+      <c r="BD33" s="82"/>
+      <c r="BE33" s="88"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="101"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="78"/>
-      <c r="P34" s="69"/>
-      <c r="Q34" s="69"/>
-      <c r="R34" s="69"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="69"/>
-      <c r="U34" s="69"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="69"/>
-      <c r="X34" s="69"/>
-      <c r="Y34" s="69"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="69"/>
-      <c r="AB34" s="69"/>
-      <c r="AC34" s="69"/>
-      <c r="AD34" s="69"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="69"/>
-      <c r="AG34" s="69"/>
-      <c r="AH34" s="69"/>
-      <c r="AI34" s="69"/>
-      <c r="AJ34" s="69"/>
-      <c r="AK34" s="69"/>
-      <c r="AL34" s="69"/>
-      <c r="AM34" s="69"/>
-      <c r="AN34" s="69"/>
-      <c r="AO34" s="69"/>
-      <c r="AP34" s="81"/>
-      <c r="AQ34" s="68"/>
-      <c r="AR34" s="69"/>
-      <c r="AS34" s="69"/>
-      <c r="AT34" s="69"/>
-      <c r="AU34" s="69"/>
-      <c r="AV34" s="69"/>
-      <c r="AW34" s="69"/>
-      <c r="AX34" s="69"/>
-      <c r="AY34" s="69"/>
-      <c r="AZ34" s="69"/>
-      <c r="BA34" s="69"/>
-      <c r="BB34" s="69"/>
-      <c r="BC34" s="69"/>
-      <c r="BD34" s="69"/>
-      <c r="BE34" s="70"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
+      <c r="M34" s="89"/>
+      <c r="N34" s="90"/>
+      <c r="O34" s="81"/>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82"/>
+      <c r="R34" s="82"/>
+      <c r="S34" s="82"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
+      <c r="V34" s="82"/>
+      <c r="W34" s="82"/>
+      <c r="X34" s="82"/>
+      <c r="Y34" s="82"/>
+      <c r="Z34" s="82"/>
+      <c r="AA34" s="82"/>
+      <c r="AB34" s="82"/>
+      <c r="AC34" s="82"/>
+      <c r="AD34" s="82"/>
+      <c r="AE34" s="82"/>
+      <c r="AF34" s="82"/>
+      <c r="AG34" s="82"/>
+      <c r="AH34" s="82"/>
+      <c r="AI34" s="82"/>
+      <c r="AJ34" s="82"/>
+      <c r="AK34" s="82"/>
+      <c r="AL34" s="82"/>
+      <c r="AM34" s="82"/>
+      <c r="AN34" s="82"/>
+      <c r="AO34" s="82"/>
+      <c r="AP34" s="83"/>
+      <c r="AQ34" s="87"/>
+      <c r="AR34" s="82"/>
+      <c r="AS34" s="82"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
+      <c r="AV34" s="82"/>
+      <c r="AW34" s="82"/>
+      <c r="AX34" s="82"/>
+      <c r="AY34" s="82"/>
+      <c r="AZ34" s="82"/>
+      <c r="BA34" s="82"/>
+      <c r="BB34" s="82"/>
+      <c r="BC34" s="82"/>
+      <c r="BD34" s="82"/>
+      <c r="BE34" s="88"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="112"/>
-      <c r="B35" s="113"/>
-      <c r="C35" s="113"/>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
-      <c r="F35" s="113"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="108"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="110"/>
-      <c r="O35" s="108"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
-      <c r="S35" s="103"/>
-      <c r="T35" s="103"/>
-      <c r="U35" s="103"/>
-      <c r="V35" s="103"/>
-      <c r="W35" s="103"/>
-      <c r="X35" s="103"/>
-      <c r="Y35" s="103"/>
-      <c r="Z35" s="103"/>
-      <c r="AA35" s="103"/>
-      <c r="AB35" s="103"/>
-      <c r="AC35" s="103"/>
-      <c r="AD35" s="103"/>
-      <c r="AE35" s="103"/>
-      <c r="AF35" s="103"/>
-      <c r="AG35" s="103"/>
-      <c r="AH35" s="103"/>
-      <c r="AI35" s="103"/>
-      <c r="AJ35" s="103"/>
-      <c r="AK35" s="103"/>
-      <c r="AL35" s="103"/>
-      <c r="AM35" s="103"/>
-      <c r="AN35" s="103"/>
-      <c r="AO35" s="103"/>
-      <c r="AP35" s="111"/>
-      <c r="AQ35" s="102"/>
-      <c r="AR35" s="103"/>
-      <c r="AS35" s="103"/>
-      <c r="AT35" s="103"/>
-      <c r="AU35" s="103"/>
-      <c r="AV35" s="103"/>
-      <c r="AW35" s="103"/>
-      <c r="AX35" s="103"/>
-      <c r="AY35" s="103"/>
-      <c r="AZ35" s="103"/>
-      <c r="BA35" s="103"/>
-      <c r="BB35" s="103"/>
-      <c r="BC35" s="103"/>
-      <c r="BD35" s="103"/>
-      <c r="BE35" s="104"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="78"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="78"/>
+      <c r="M35" s="78"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="77"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="69"/>
+      <c r="U35" s="69"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="69"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="69"/>
+      <c r="AB35" s="69"/>
+      <c r="AC35" s="69"/>
+      <c r="AD35" s="69"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="69"/>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="69"/>
+      <c r="AI35" s="69"/>
+      <c r="AJ35" s="69"/>
+      <c r="AK35" s="69"/>
+      <c r="AL35" s="69"/>
+      <c r="AM35" s="69"/>
+      <c r="AN35" s="69"/>
+      <c r="AO35" s="69"/>
+      <c r="AP35" s="80"/>
+      <c r="AQ35" s="68"/>
+      <c r="AR35" s="69"/>
+      <c r="AS35" s="69"/>
+      <c r="AT35" s="69"/>
+      <c r="AU35" s="69"/>
+      <c r="AV35" s="69"/>
+      <c r="AW35" s="69"/>
+      <c r="AX35" s="69"/>
+      <c r="AY35" s="69"/>
+      <c r="AZ35" s="69"/>
+      <c r="BA35" s="69"/>
+      <c r="BB35" s="69"/>
+      <c r="BC35" s="69"/>
+      <c r="BD35" s="69"/>
+      <c r="BE35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="O33:AP33"/>
     <mergeCell ref="AQ35:BE35"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
@@ -8909,115 +9158,6 @@
     <mergeCell ref="H23:N23"/>
     <mergeCell ref="H34:N34"/>
     <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0020_ShipItmCompSrch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8F69F3-731E-43E4-A044-BDAAAD0F6A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101A3417-7248-4D32-9C55-EED16AA3D614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3330" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBEP0050" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="278">
   <si>
     <t>*</t>
   </si>
@@ -2485,15 +2485,126 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2514,117 +2625,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="45">
@@ -5046,7 +5046,9 @@
         <v>65</v>
       </c>
       <c r="AC48" s="21"/>
-      <c r="AD48" s="21"/>
+      <c r="AD48" s="21" t="s">
+        <v>185</v>
+      </c>
       <c r="AF48" s="17"/>
     </row>
     <row r="49" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5095,7 +5097,9 @@
         <v>65</v>
       </c>
       <c r="AC49" s="21"/>
-      <c r="AD49" s="21"/>
+      <c r="AD49" s="21" t="s">
+        <v>189</v>
+      </c>
       <c r="AF49" s="17"/>
     </row>
     <row r="50" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5412,10 +5416,16 @@
       <c r="V56" s="31"/>
       <c r="W56" s="31"/>
       <c r="X56" s="31"/>
-      <c r="Z56" s="31"/>
-      <c r="AA56" s="31"/>
+      <c r="Z56" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA56" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="AC56" s="31"/>
-      <c r="AD56" s="31"/>
+      <c r="AD56" s="31" t="s">
+        <v>265</v>
+      </c>
       <c r="AF56" s="56"/>
     </row>
     <row r="57" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5433,7 +5443,9 @@
       <c r="F57" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="G57" s="31"/>
+      <c r="G57" s="31" t="s">
+        <v>1</v>
+      </c>
       <c r="H57" s="31"/>
       <c r="I57" s="31" t="s">
         <v>274</v>
@@ -5455,10 +5467,16 @@
       <c r="V57" s="31"/>
       <c r="W57" s="31"/>
       <c r="X57" s="31"/>
-      <c r="Z57" s="31"/>
-      <c r="AA57" s="31"/>
+      <c r="Z57" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA57" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
+      <c r="AD57" s="31" t="s">
+        <v>271</v>
+      </c>
       <c r="AF57" s="56"/>
     </row>
     <row r="58" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5507,7 +5525,9 @@
         <v>65</v>
       </c>
       <c r="AC58" s="21"/>
-      <c r="AD58" s="21"/>
+      <c r="AD58" s="21" t="s">
+        <v>210</v>
+      </c>
       <c r="AF58" s="18"/>
     </row>
     <row r="59" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5556,7 +5576,9 @@
         <v>65</v>
       </c>
       <c r="AC59" s="21"/>
-      <c r="AD59" s="21"/>
+      <c r="AD59" s="21" t="s">
+        <v>211</v>
+      </c>
       <c r="AF59" s="18"/>
     </row>
     <row r="60" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5598,10 +5620,16 @@
       <c r="V60" s="21"/>
       <c r="W60" s="21"/>
       <c r="X60" s="21"/>
-      <c r="Z60" s="21"/>
-      <c r="AA60" s="21"/>
+      <c r="Z60" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA60" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="AC60" s="21"/>
-      <c r="AD60" s="21"/>
+      <c r="AD60" s="21" t="s">
+        <v>212</v>
+      </c>
       <c r="AF60" s="18"/>
     </row>
     <row r="61" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5643,10 +5671,16 @@
       <c r="V61" s="21"/>
       <c r="W61" s="21"/>
       <c r="X61" s="21"/>
-      <c r="Z61" s="21"/>
-      <c r="AA61" s="21"/>
+      <c r="Z61" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA61" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="AC61" s="21"/>
-      <c r="AD61" s="21"/>
+      <c r="AD61" s="21" t="s">
+        <v>213</v>
+      </c>
       <c r="AF61" s="18"/>
     </row>
     <row r="62" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -5688,10 +5722,16 @@
       <c r="V62" s="21"/>
       <c r="W62" s="21"/>
       <c r="X62" s="21"/>
-      <c r="Z62" s="21"/>
-      <c r="AA62" s="21"/>
+      <c r="Z62" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA62" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="AC62" s="21"/>
-      <c r="AD62" s="21"/>
+      <c r="AD62" s="21" t="s">
+        <v>214</v>
+      </c>
       <c r="AF62" s="18"/>
     </row>
     <row r="63" spans="1:32" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -6181,1972 +6221,2081 @@
       <c r="AP2" s="14"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="85"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="97"/>
       <c r="H3" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="85"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="97"/>
       <c r="O3" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="96"/>
-      <c r="AD3" s="96"/>
-      <c r="AE3" s="96"/>
-      <c r="AF3" s="96"/>
-      <c r="AG3" s="96"/>
-      <c r="AH3" s="96"/>
-      <c r="AI3" s="96"/>
-      <c r="AJ3" s="96"/>
-      <c r="AK3" s="96"/>
-      <c r="AL3" s="96"/>
-      <c r="AM3" s="96"/>
-      <c r="AN3" s="96"/>
-      <c r="AO3" s="96"/>
-      <c r="AP3" s="97"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="Z3" s="98"/>
+      <c r="AA3" s="98"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="98"/>
+      <c r="AD3" s="98"/>
+      <c r="AE3" s="98"/>
+      <c r="AF3" s="98"/>
+      <c r="AG3" s="98"/>
+      <c r="AH3" s="98"/>
+      <c r="AI3" s="98"/>
+      <c r="AJ3" s="98"/>
+      <c r="AK3" s="98"/>
+      <c r="AL3" s="98"/>
+      <c r="AM3" s="98"/>
+      <c r="AN3" s="98"/>
+      <c r="AO3" s="98"/>
+      <c r="AP3" s="99"/>
       <c r="AQ3" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AR3" s="98"/>
-      <c r="AS3" s="98"/>
-      <c r="AT3" s="98"/>
-      <c r="AU3" s="98"/>
-      <c r="AV3" s="98"/>
-      <c r="AW3" s="98"/>
-      <c r="AX3" s="98"/>
-      <c r="AY3" s="98"/>
-      <c r="AZ3" s="98"/>
-      <c r="BA3" s="98"/>
-      <c r="BB3" s="98"/>
-      <c r="BC3" s="98"/>
-      <c r="BD3" s="98"/>
-      <c r="BE3" s="99"/>
+      <c r="AR3" s="100"/>
+      <c r="AS3" s="100"/>
+      <c r="AT3" s="100"/>
+      <c r="AU3" s="100"/>
+      <c r="AV3" s="100"/>
+      <c r="AW3" s="100"/>
+      <c r="AX3" s="100"/>
+      <c r="AY3" s="100"/>
+      <c r="AZ3" s="100"/>
+      <c r="BA3" s="100"/>
+      <c r="BB3" s="100"/>
+      <c r="BC3" s="100"/>
+      <c r="BD3" s="100"/>
+      <c r="BE3" s="101"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="106">
+      <c r="A4" s="72">
         <v>1</v>
       </c>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="72" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="75"/>
-      <c r="AA4" s="75"/>
-      <c r="AB4" s="75"/>
-      <c r="AC4" s="75"/>
-      <c r="AD4" s="75"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
-      <c r="AI4" s="75"/>
-      <c r="AJ4" s="75"/>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75"/>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="76"/>
-      <c r="AQ4" s="77"/>
-      <c r="AR4" s="75"/>
-      <c r="AS4" s="75"/>
-      <c r="AT4" s="75"/>
-      <c r="AU4" s="75"/>
-      <c r="AV4" s="75"/>
-      <c r="AW4" s="75"/>
-      <c r="AX4" s="75"/>
-      <c r="AY4" s="75"/>
-      <c r="AZ4" s="75"/>
-      <c r="BA4" s="75"/>
-      <c r="BB4" s="75"/>
-      <c r="BC4" s="75"/>
-      <c r="BD4" s="75"/>
-      <c r="BE4" s="78"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113"/>
+      <c r="AQ4" s="114"/>
+      <c r="AR4" s="112"/>
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="112"/>
+      <c r="AU4" s="112"/>
+      <c r="AV4" s="112"/>
+      <c r="AW4" s="112"/>
+      <c r="AX4" s="112"/>
+      <c r="AY4" s="112"/>
+      <c r="AZ4" s="112"/>
+      <c r="BA4" s="112"/>
+      <c r="BB4" s="112"/>
+      <c r="BC4" s="112"/>
+      <c r="BD4" s="112"/>
+      <c r="BE4" s="115"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="100">
+      <c r="A5" s="75">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="86" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="103" t="s">
         <v>160</v>
       </c>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="87"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="87"/>
-      <c r="U5" s="87"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="87"/>
-      <c r="X5" s="87"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="87"/>
-      <c r="AA5" s="87"/>
-      <c r="AB5" s="87"/>
-      <c r="AC5" s="87"/>
-      <c r="AD5" s="87"/>
-      <c r="AE5" s="87"/>
-      <c r="AF5" s="87"/>
-      <c r="AG5" s="87"/>
-      <c r="AH5" s="87"/>
-      <c r="AI5" s="87"/>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="87"/>
-      <c r="AL5" s="87"/>
-      <c r="AM5" s="87"/>
-      <c r="AN5" s="87"/>
-      <c r="AO5" s="87"/>
-      <c r="AP5" s="88"/>
-      <c r="AQ5" s="89" t="s">
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="104"/>
+      <c r="Y5" s="104"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
+      <c r="AB5" s="104"/>
+      <c r="AC5" s="104"/>
+      <c r="AD5" s="104"/>
+      <c r="AE5" s="104"/>
+      <c r="AF5" s="104"/>
+      <c r="AG5" s="104"/>
+      <c r="AH5" s="104"/>
+      <c r="AI5" s="104"/>
+      <c r="AJ5" s="104"/>
+      <c r="AK5" s="104"/>
+      <c r="AL5" s="104"/>
+      <c r="AM5" s="104"/>
+      <c r="AN5" s="104"/>
+      <c r="AO5" s="104"/>
+      <c r="AP5" s="105"/>
+      <c r="AQ5" s="106" t="s">
         <v>161</v>
       </c>
-      <c r="AR5" s="90"/>
-      <c r="AS5" s="90"/>
-      <c r="AT5" s="90"/>
-      <c r="AU5" s="90"/>
-      <c r="AV5" s="90"/>
-      <c r="AW5" s="90"/>
-      <c r="AX5" s="90"/>
-      <c r="AY5" s="90"/>
-      <c r="AZ5" s="90"/>
-      <c r="BA5" s="90"/>
-      <c r="BB5" s="90"/>
-      <c r="BC5" s="90"/>
-      <c r="BD5" s="90"/>
-      <c r="BE5" s="91"/>
+      <c r="AR5" s="107"/>
+      <c r="AS5" s="107"/>
+      <c r="AT5" s="107"/>
+      <c r="AU5" s="107"/>
+      <c r="AV5" s="107"/>
+      <c r="AW5" s="107"/>
+      <c r="AX5" s="107"/>
+      <c r="AY5" s="107"/>
+      <c r="AZ5" s="107"/>
+      <c r="BA5" s="107"/>
+      <c r="BB5" s="107"/>
+      <c r="BC5" s="107"/>
+      <c r="BD5" s="107"/>
+      <c r="BE5" s="108"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="70"/>
-      <c r="Y6" s="70"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="70"/>
-      <c r="AB6" s="70"/>
-      <c r="AC6" s="70"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="70"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="70"/>
-      <c r="AH6" s="70"/>
-      <c r="AI6" s="70"/>
-      <c r="AJ6" s="70"/>
-      <c r="AK6" s="70"/>
-      <c r="AL6" s="70"/>
-      <c r="AM6" s="70"/>
-      <c r="AN6" s="70"/>
-      <c r="AO6" s="70"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="69"/>
-      <c r="AR6" s="70"/>
-      <c r="AS6" s="70"/>
-      <c r="AT6" s="70"/>
-      <c r="AU6" s="70"/>
-      <c r="AV6" s="70"/>
-      <c r="AW6" s="70"/>
-      <c r="AX6" s="70"/>
-      <c r="AY6" s="70"/>
-      <c r="AZ6" s="70"/>
-      <c r="BA6" s="70"/>
-      <c r="BB6" s="70"/>
-      <c r="BC6" s="70"/>
-      <c r="BD6" s="70"/>
-      <c r="BE6" s="71"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
+      <c r="R6" s="83"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="83"/>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="83"/>
+      <c r="AB6" s="83"/>
+      <c r="AC6" s="83"/>
+      <c r="AD6" s="83"/>
+      <c r="AE6" s="83"/>
+      <c r="AF6" s="83"/>
+      <c r="AG6" s="83"/>
+      <c r="AH6" s="83"/>
+      <c r="AI6" s="83"/>
+      <c r="AJ6" s="83"/>
+      <c r="AK6" s="83"/>
+      <c r="AL6" s="83"/>
+      <c r="AM6" s="83"/>
+      <c r="AN6" s="83"/>
+      <c r="AO6" s="83"/>
+      <c r="AP6" s="84"/>
+      <c r="AQ6" s="88"/>
+      <c r="AR6" s="83"/>
+      <c r="AS6" s="83"/>
+      <c r="AT6" s="83"/>
+      <c r="AU6" s="83"/>
+      <c r="AV6" s="83"/>
+      <c r="AW6" s="83"/>
+      <c r="AX6" s="83"/>
+      <c r="AY6" s="83"/>
+      <c r="AZ6" s="83"/>
+      <c r="BA6" s="83"/>
+      <c r="BB6" s="83"/>
+      <c r="BC6" s="83"/>
+      <c r="BD6" s="83"/>
+      <c r="BE6" s="89"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="100"/>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="79"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="70"/>
-      <c r="U7" s="70"/>
-      <c r="V7" s="70"/>
-      <c r="W7" s="70"/>
-      <c r="X7" s="70"/>
-      <c r="Y7" s="70"/>
-      <c r="Z7" s="70"/>
-      <c r="AA7" s="70"/>
-      <c r="AB7" s="70"/>
-      <c r="AC7" s="70"/>
-      <c r="AD7" s="70"/>
-      <c r="AE7" s="70"/>
-      <c r="AF7" s="70"/>
-      <c r="AG7" s="70"/>
-      <c r="AH7" s="70"/>
-      <c r="AI7" s="70"/>
-      <c r="AJ7" s="70"/>
-      <c r="AK7" s="70"/>
-      <c r="AL7" s="70"/>
-      <c r="AM7" s="70"/>
-      <c r="AN7" s="70"/>
-      <c r="AO7" s="70"/>
-      <c r="AP7" s="82"/>
-      <c r="AQ7" s="69"/>
-      <c r="AR7" s="70"/>
-      <c r="AS7" s="70"/>
-      <c r="AT7" s="70"/>
-      <c r="AU7" s="70"/>
-      <c r="AV7" s="70"/>
-      <c r="AW7" s="70"/>
-      <c r="AX7" s="70"/>
-      <c r="AY7" s="70"/>
-      <c r="AZ7" s="70"/>
-      <c r="BA7" s="70"/>
-      <c r="BB7" s="70"/>
-      <c r="BC7" s="70"/>
-      <c r="BD7" s="70"/>
-      <c r="BE7" s="71"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="83"/>
+      <c r="X7" s="83"/>
+      <c r="Y7" s="83"/>
+      <c r="Z7" s="83"/>
+      <c r="AA7" s="83"/>
+      <c r="AB7" s="83"/>
+      <c r="AC7" s="83"/>
+      <c r="AD7" s="83"/>
+      <c r="AE7" s="83"/>
+      <c r="AF7" s="83"/>
+      <c r="AG7" s="83"/>
+      <c r="AH7" s="83"/>
+      <c r="AI7" s="83"/>
+      <c r="AJ7" s="83"/>
+      <c r="AK7" s="83"/>
+      <c r="AL7" s="83"/>
+      <c r="AM7" s="83"/>
+      <c r="AN7" s="83"/>
+      <c r="AO7" s="83"/>
+      <c r="AP7" s="84"/>
+      <c r="AQ7" s="88"/>
+      <c r="AR7" s="83"/>
+      <c r="AS7" s="83"/>
+      <c r="AT7" s="83"/>
+      <c r="AU7" s="83"/>
+      <c r="AV7" s="83"/>
+      <c r="AW7" s="83"/>
+      <c r="AX7" s="83"/>
+      <c r="AY7" s="83"/>
+      <c r="AZ7" s="83"/>
+      <c r="BA7" s="83"/>
+      <c r="BB7" s="83"/>
+      <c r="BC7" s="83"/>
+      <c r="BD7" s="83"/>
+      <c r="BE7" s="89"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="100"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
-      <c r="K8" s="80"/>
-      <c r="L8" s="80"/>
-      <c r="M8" s="80"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="70"/>
-      <c r="R8" s="70"/>
-      <c r="S8" s="70"/>
-      <c r="T8" s="70"/>
-      <c r="U8" s="70"/>
-      <c r="V8" s="70"/>
-      <c r="W8" s="70"/>
-      <c r="X8" s="70"/>
-      <c r="Y8" s="70"/>
-      <c r="Z8" s="70"/>
-      <c r="AA8" s="70"/>
-      <c r="AB8" s="70"/>
-      <c r="AC8" s="70"/>
-      <c r="AD8" s="70"/>
-      <c r="AE8" s="70"/>
-      <c r="AF8" s="70"/>
-      <c r="AG8" s="70"/>
-      <c r="AH8" s="70"/>
-      <c r="AI8" s="70"/>
-      <c r="AJ8" s="70"/>
-      <c r="AK8" s="70"/>
-      <c r="AL8" s="70"/>
-      <c r="AM8" s="70"/>
-      <c r="AN8" s="70"/>
-      <c r="AO8" s="70"/>
-      <c r="AP8" s="82"/>
-      <c r="AQ8" s="69"/>
-      <c r="AR8" s="70"/>
-      <c r="AS8" s="70"/>
-      <c r="AT8" s="70"/>
-      <c r="AU8" s="70"/>
-      <c r="AV8" s="70"/>
-      <c r="AW8" s="70"/>
-      <c r="AX8" s="70"/>
-      <c r="AY8" s="70"/>
-      <c r="AZ8" s="70"/>
-      <c r="BA8" s="70"/>
-      <c r="BB8" s="70"/>
-      <c r="BC8" s="70"/>
-      <c r="BD8" s="70"/>
-      <c r="BE8" s="71"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="83"/>
+      <c r="Q8" s="83"/>
+      <c r="R8" s="83"/>
+      <c r="S8" s="83"/>
+      <c r="T8" s="83"/>
+      <c r="U8" s="83"/>
+      <c r="V8" s="83"/>
+      <c r="W8" s="83"/>
+      <c r="X8" s="83"/>
+      <c r="Y8" s="83"/>
+      <c r="Z8" s="83"/>
+      <c r="AA8" s="83"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="83"/>
+      <c r="AD8" s="83"/>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="83"/>
+      <c r="AG8" s="83"/>
+      <c r="AH8" s="83"/>
+      <c r="AI8" s="83"/>
+      <c r="AJ8" s="83"/>
+      <c r="AK8" s="83"/>
+      <c r="AL8" s="83"/>
+      <c r="AM8" s="83"/>
+      <c r="AN8" s="83"/>
+      <c r="AO8" s="83"/>
+      <c r="AP8" s="84"/>
+      <c r="AQ8" s="88"/>
+      <c r="AR8" s="83"/>
+      <c r="AS8" s="83"/>
+      <c r="AT8" s="83"/>
+      <c r="AU8" s="83"/>
+      <c r="AV8" s="83"/>
+      <c r="AW8" s="83"/>
+      <c r="AX8" s="83"/>
+      <c r="AY8" s="83"/>
+      <c r="AZ8" s="83"/>
+      <c r="BA8" s="83"/>
+      <c r="BB8" s="83"/>
+      <c r="BC8" s="83"/>
+      <c r="BD8" s="83"/>
+      <c r="BE8" s="89"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="100"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="70"/>
-      <c r="Z9" s="70"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-      <c r="AG9" s="70"/>
-      <c r="AH9" s="70"/>
-      <c r="AI9" s="70"/>
-      <c r="AJ9" s="70"/>
-      <c r="AK9" s="70"/>
-      <c r="AL9" s="70"/>
-      <c r="AM9" s="70"/>
-      <c r="AN9" s="70"/>
-      <c r="AO9" s="70"/>
-      <c r="AP9" s="82"/>
-      <c r="AQ9" s="69"/>
-      <c r="AR9" s="70"/>
-      <c r="AS9" s="70"/>
-      <c r="AT9" s="70"/>
-      <c r="AU9" s="70"/>
-      <c r="AV9" s="70"/>
-      <c r="AW9" s="70"/>
-      <c r="AX9" s="70"/>
-      <c r="AY9" s="70"/>
-      <c r="AZ9" s="70"/>
-      <c r="BA9" s="70"/>
-      <c r="BB9" s="70"/>
-      <c r="BC9" s="70"/>
-      <c r="BD9" s="70"/>
-      <c r="BE9" s="71"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="91"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
+      <c r="Y9" s="83"/>
+      <c r="Z9" s="83"/>
+      <c r="AA9" s="83"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="83"/>
+      <c r="AD9" s="83"/>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
+      <c r="AH9" s="83"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="83"/>
+      <c r="AL9" s="83"/>
+      <c r="AM9" s="83"/>
+      <c r="AN9" s="83"/>
+      <c r="AO9" s="83"/>
+      <c r="AP9" s="84"/>
+      <c r="AQ9" s="88"/>
+      <c r="AR9" s="83"/>
+      <c r="AS9" s="83"/>
+      <c r="AT9" s="83"/>
+      <c r="AU9" s="83"/>
+      <c r="AV9" s="83"/>
+      <c r="AW9" s="83"/>
+      <c r="AX9" s="83"/>
+      <c r="AY9" s="83"/>
+      <c r="AZ9" s="83"/>
+      <c r="BA9" s="83"/>
+      <c r="BB9" s="83"/>
+      <c r="BC9" s="83"/>
+      <c r="BD9" s="83"/>
+      <c r="BE9" s="89"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="80"/>
-      <c r="M10" s="80"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="70"/>
-      <c r="Z10" s="70"/>
-      <c r="AA10" s="70"/>
-      <c r="AB10" s="70"/>
-      <c r="AC10" s="70"/>
-      <c r="AD10" s="70"/>
-      <c r="AE10" s="70"/>
-      <c r="AF10" s="70"/>
-      <c r="AG10" s="70"/>
-      <c r="AH10" s="70"/>
-      <c r="AI10" s="70"/>
-      <c r="AJ10" s="70"/>
-      <c r="AK10" s="70"/>
-      <c r="AL10" s="70"/>
-      <c r="AM10" s="70"/>
-      <c r="AN10" s="70"/>
-      <c r="AO10" s="70"/>
-      <c r="AP10" s="82"/>
-      <c r="AQ10" s="69"/>
-      <c r="AR10" s="70"/>
-      <c r="AS10" s="70"/>
-      <c r="AT10" s="70"/>
-      <c r="AU10" s="70"/>
-      <c r="AV10" s="70"/>
-      <c r="AW10" s="70"/>
-      <c r="AX10" s="70"/>
-      <c r="AY10" s="70"/>
-      <c r="AZ10" s="70"/>
-      <c r="BA10" s="70"/>
-      <c r="BB10" s="70"/>
-      <c r="BC10" s="70"/>
-      <c r="BD10" s="70"/>
-      <c r="BE10" s="71"/>
+      <c r="A10" s="75"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
+      <c r="R10" s="83"/>
+      <c r="S10" s="83"/>
+      <c r="T10" s="83"/>
+      <c r="U10" s="83"/>
+      <c r="V10" s="83"/>
+      <c r="W10" s="83"/>
+      <c r="X10" s="83"/>
+      <c r="Y10" s="83"/>
+      <c r="Z10" s="83"/>
+      <c r="AA10" s="83"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="83"/>
+      <c r="AE10" s="83"/>
+      <c r="AF10" s="83"/>
+      <c r="AG10" s="83"/>
+      <c r="AH10" s="83"/>
+      <c r="AI10" s="83"/>
+      <c r="AJ10" s="83"/>
+      <c r="AK10" s="83"/>
+      <c r="AL10" s="83"/>
+      <c r="AM10" s="83"/>
+      <c r="AN10" s="83"/>
+      <c r="AO10" s="83"/>
+      <c r="AP10" s="84"/>
+      <c r="AQ10" s="88"/>
+      <c r="AR10" s="83"/>
+      <c r="AS10" s="83"/>
+      <c r="AT10" s="83"/>
+      <c r="AU10" s="83"/>
+      <c r="AV10" s="83"/>
+      <c r="AW10" s="83"/>
+      <c r="AX10" s="83"/>
+      <c r="AY10" s="83"/>
+      <c r="AZ10" s="83"/>
+      <c r="BA10" s="83"/>
+      <c r="BB10" s="83"/>
+      <c r="BC10" s="83"/>
+      <c r="BD10" s="83"/>
+      <c r="BE10" s="89"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="100"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="80"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
-      <c r="W11" s="70"/>
-      <c r="X11" s="70"/>
-      <c r="Y11" s="70"/>
-      <c r="Z11" s="70"/>
-      <c r="AA11" s="70"/>
-      <c r="AB11" s="70"/>
-      <c r="AC11" s="70"/>
-      <c r="AD11" s="70"/>
-      <c r="AE11" s="70"/>
-      <c r="AF11" s="70"/>
-      <c r="AG11" s="70"/>
-      <c r="AH11" s="70"/>
-      <c r="AI11" s="70"/>
-      <c r="AJ11" s="70"/>
-      <c r="AK11" s="70"/>
-      <c r="AL11" s="70"/>
-      <c r="AM11" s="70"/>
-      <c r="AN11" s="70"/>
-      <c r="AO11" s="70"/>
-      <c r="AP11" s="82"/>
-      <c r="AQ11" s="69"/>
-      <c r="AR11" s="70"/>
-      <c r="AS11" s="70"/>
-      <c r="AT11" s="70"/>
-      <c r="AU11" s="70"/>
-      <c r="AV11" s="70"/>
-      <c r="AW11" s="70"/>
-      <c r="AX11" s="70"/>
-      <c r="AY11" s="70"/>
-      <c r="AZ11" s="70"/>
-      <c r="BA11" s="70"/>
-      <c r="BB11" s="70"/>
-      <c r="BC11" s="70"/>
-      <c r="BD11" s="70"/>
-      <c r="BE11" s="71"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
+      <c r="S11" s="83"/>
+      <c r="T11" s="83"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="83"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="83"/>
+      <c r="Z11" s="83"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="83"/>
+      <c r="AC11" s="83"/>
+      <c r="AD11" s="83"/>
+      <c r="AE11" s="83"/>
+      <c r="AF11" s="83"/>
+      <c r="AG11" s="83"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="83"/>
+      <c r="AL11" s="83"/>
+      <c r="AM11" s="83"/>
+      <c r="AN11" s="83"/>
+      <c r="AO11" s="83"/>
+      <c r="AP11" s="84"/>
+      <c r="AQ11" s="88"/>
+      <c r="AR11" s="83"/>
+      <c r="AS11" s="83"/>
+      <c r="AT11" s="83"/>
+      <c r="AU11" s="83"/>
+      <c r="AV11" s="83"/>
+      <c r="AW11" s="83"/>
+      <c r="AX11" s="83"/>
+      <c r="AY11" s="83"/>
+      <c r="AZ11" s="83"/>
+      <c r="BA11" s="83"/>
+      <c r="BB11" s="83"/>
+      <c r="BC11" s="83"/>
+      <c r="BD11" s="83"/>
+      <c r="BE11" s="89"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="100"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
-      <c r="L12" s="80"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="70"/>
-      <c r="R12" s="70"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="70"/>
-      <c r="U12" s="70"/>
-      <c r="V12" s="70"/>
-      <c r="W12" s="70"/>
-      <c r="X12" s="70"/>
-      <c r="Y12" s="70"/>
-      <c r="Z12" s="70"/>
-      <c r="AA12" s="70"/>
-      <c r="AB12" s="70"/>
-      <c r="AC12" s="70"/>
-      <c r="AD12" s="70"/>
-      <c r="AE12" s="70"/>
-      <c r="AF12" s="70"/>
-      <c r="AG12" s="70"/>
-      <c r="AH12" s="70"/>
-      <c r="AI12" s="70"/>
-      <c r="AJ12" s="70"/>
-      <c r="AK12" s="70"/>
-      <c r="AL12" s="70"/>
-      <c r="AM12" s="70"/>
-      <c r="AN12" s="70"/>
-      <c r="AO12" s="70"/>
-      <c r="AP12" s="82"/>
-      <c r="AQ12" s="69"/>
-      <c r="AR12" s="70"/>
-      <c r="AS12" s="70"/>
-      <c r="AT12" s="70"/>
-      <c r="AU12" s="70"/>
-      <c r="AV12" s="70"/>
-      <c r="AW12" s="70"/>
-      <c r="AX12" s="70"/>
-      <c r="AY12" s="70"/>
-      <c r="AZ12" s="70"/>
-      <c r="BA12" s="70"/>
-      <c r="BB12" s="70"/>
-      <c r="BC12" s="70"/>
-      <c r="BD12" s="70"/>
-      <c r="BE12" s="71"/>
+      <c r="A12" s="75"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="90"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="83"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="83"/>
+      <c r="W12" s="83"/>
+      <c r="X12" s="83"/>
+      <c r="Y12" s="83"/>
+      <c r="Z12" s="83"/>
+      <c r="AA12" s="83"/>
+      <c r="AB12" s="83"/>
+      <c r="AC12" s="83"/>
+      <c r="AD12" s="83"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="83"/>
+      <c r="AG12" s="83"/>
+      <c r="AH12" s="83"/>
+      <c r="AI12" s="83"/>
+      <c r="AJ12" s="83"/>
+      <c r="AK12" s="83"/>
+      <c r="AL12" s="83"/>
+      <c r="AM12" s="83"/>
+      <c r="AN12" s="83"/>
+      <c r="AO12" s="83"/>
+      <c r="AP12" s="84"/>
+      <c r="AQ12" s="88"/>
+      <c r="AR12" s="83"/>
+      <c r="AS12" s="83"/>
+      <c r="AT12" s="83"/>
+      <c r="AU12" s="83"/>
+      <c r="AV12" s="83"/>
+      <c r="AW12" s="83"/>
+      <c r="AX12" s="83"/>
+      <c r="AY12" s="83"/>
+      <c r="AZ12" s="83"/>
+      <c r="BA12" s="83"/>
+      <c r="BB12" s="83"/>
+      <c r="BC12" s="83"/>
+      <c r="BD12" s="83"/>
+      <c r="BE12" s="89"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="79"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="70"/>
-      <c r="R13" s="70"/>
-      <c r="S13" s="70"/>
-      <c r="T13" s="70"/>
-      <c r="U13" s="70"/>
-      <c r="V13" s="70"/>
-      <c r="W13" s="70"/>
-      <c r="X13" s="70"/>
-      <c r="Y13" s="70"/>
-      <c r="Z13" s="70"/>
-      <c r="AA13" s="70"/>
-      <c r="AB13" s="70"/>
-      <c r="AC13" s="70"/>
-      <c r="AD13" s="70"/>
-      <c r="AE13" s="70"/>
-      <c r="AF13" s="70"/>
-      <c r="AG13" s="70"/>
-      <c r="AH13" s="70"/>
-      <c r="AI13" s="70"/>
-      <c r="AJ13" s="70"/>
-      <c r="AK13" s="70"/>
-      <c r="AL13" s="70"/>
-      <c r="AM13" s="70"/>
-      <c r="AN13" s="70"/>
-      <c r="AO13" s="70"/>
-      <c r="AP13" s="82"/>
-      <c r="AQ13" s="69"/>
-      <c r="AR13" s="70"/>
-      <c r="AS13" s="70"/>
-      <c r="AT13" s="70"/>
-      <c r="AU13" s="70"/>
-      <c r="AV13" s="70"/>
-      <c r="AW13" s="70"/>
-      <c r="AX13" s="70"/>
-      <c r="AY13" s="70"/>
-      <c r="AZ13" s="70"/>
-      <c r="BA13" s="70"/>
-      <c r="BB13" s="70"/>
-      <c r="BC13" s="70"/>
-      <c r="BD13" s="70"/>
-      <c r="BE13" s="71"/>
+      <c r="A13" s="75"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
+      <c r="R13" s="83"/>
+      <c r="S13" s="83"/>
+      <c r="T13" s="83"/>
+      <c r="U13" s="83"/>
+      <c r="V13" s="83"/>
+      <c r="W13" s="83"/>
+      <c r="X13" s="83"/>
+      <c r="Y13" s="83"/>
+      <c r="Z13" s="83"/>
+      <c r="AA13" s="83"/>
+      <c r="AB13" s="83"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="83"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="83"/>
+      <c r="AH13" s="83"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="83"/>
+      <c r="AK13" s="83"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="83"/>
+      <c r="AN13" s="83"/>
+      <c r="AO13" s="83"/>
+      <c r="AP13" s="84"/>
+      <c r="AQ13" s="88"/>
+      <c r="AR13" s="83"/>
+      <c r="AS13" s="83"/>
+      <c r="AT13" s="83"/>
+      <c r="AU13" s="83"/>
+      <c r="AV13" s="83"/>
+      <c r="AW13" s="83"/>
+      <c r="AX13" s="83"/>
+      <c r="AY13" s="83"/>
+      <c r="AZ13" s="83"/>
+      <c r="BA13" s="83"/>
+      <c r="BB13" s="83"/>
+      <c r="BC13" s="83"/>
+      <c r="BD13" s="83"/>
+      <c r="BE13" s="89"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="100"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="79"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="70"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="70"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="70"/>
-      <c r="AC14" s="70"/>
-      <c r="AD14" s="70"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="70"/>
-      <c r="AG14" s="70"/>
-      <c r="AH14" s="70"/>
-      <c r="AI14" s="70"/>
-      <c r="AJ14" s="70"/>
-      <c r="AK14" s="70"/>
-      <c r="AL14" s="70"/>
-      <c r="AM14" s="70"/>
-      <c r="AN14" s="70"/>
-      <c r="AO14" s="70"/>
-      <c r="AP14" s="82"/>
-      <c r="AQ14" s="69"/>
-      <c r="AR14" s="70"/>
-      <c r="AS14" s="70"/>
-      <c r="AT14" s="70"/>
-      <c r="AU14" s="70"/>
-      <c r="AV14" s="70"/>
-      <c r="AW14" s="70"/>
-      <c r="AX14" s="70"/>
-      <c r="AY14" s="70"/>
-      <c r="AZ14" s="70"/>
-      <c r="BA14" s="70"/>
-      <c r="BB14" s="70"/>
-      <c r="BC14" s="70"/>
-      <c r="BD14" s="70"/>
-      <c r="BE14" s="71"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="83"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="83"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="83"/>
+      <c r="Z14" s="83"/>
+      <c r="AA14" s="83"/>
+      <c r="AB14" s="83"/>
+      <c r="AC14" s="83"/>
+      <c r="AD14" s="83"/>
+      <c r="AE14" s="83"/>
+      <c r="AF14" s="83"/>
+      <c r="AG14" s="83"/>
+      <c r="AH14" s="83"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="83"/>
+      <c r="AK14" s="83"/>
+      <c r="AL14" s="83"/>
+      <c r="AM14" s="83"/>
+      <c r="AN14" s="83"/>
+      <c r="AO14" s="83"/>
+      <c r="AP14" s="84"/>
+      <c r="AQ14" s="88"/>
+      <c r="AR14" s="83"/>
+      <c r="AS14" s="83"/>
+      <c r="AT14" s="83"/>
+      <c r="AU14" s="83"/>
+      <c r="AV14" s="83"/>
+      <c r="AW14" s="83"/>
+      <c r="AX14" s="83"/>
+      <c r="AY14" s="83"/>
+      <c r="AZ14" s="83"/>
+      <c r="BA14" s="83"/>
+      <c r="BB14" s="83"/>
+      <c r="BC14" s="83"/>
+      <c r="BD14" s="83"/>
+      <c r="BE14" s="89"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="100"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="79"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="70"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="70"/>
-      <c r="AC15" s="70"/>
-      <c r="AD15" s="70"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="70"/>
-      <c r="AL15" s="70"/>
-      <c r="AM15" s="70"/>
-      <c r="AN15" s="70"/>
-      <c r="AO15" s="70"/>
-      <c r="AP15" s="82"/>
-      <c r="AQ15" s="69"/>
-      <c r="AR15" s="70"/>
-      <c r="AS15" s="70"/>
-      <c r="AT15" s="70"/>
-      <c r="AU15" s="70"/>
-      <c r="AV15" s="70"/>
-      <c r="AW15" s="70"/>
-      <c r="AX15" s="70"/>
-      <c r="AY15" s="70"/>
-      <c r="AZ15" s="70"/>
-      <c r="BA15" s="70"/>
-      <c r="BB15" s="70"/>
-      <c r="BC15" s="70"/>
-      <c r="BD15" s="70"/>
-      <c r="BE15" s="71"/>
+      <c r="A15" s="75"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="90"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="83"/>
+      <c r="T15" s="83"/>
+      <c r="U15" s="83"/>
+      <c r="V15" s="83"/>
+      <c r="W15" s="83"/>
+      <c r="X15" s="83"/>
+      <c r="Y15" s="83"/>
+      <c r="Z15" s="83"/>
+      <c r="AA15" s="83"/>
+      <c r="AB15" s="83"/>
+      <c r="AC15" s="83"/>
+      <c r="AD15" s="83"/>
+      <c r="AE15" s="83"/>
+      <c r="AF15" s="83"/>
+      <c r="AG15" s="83"/>
+      <c r="AH15" s="83"/>
+      <c r="AI15" s="83"/>
+      <c r="AJ15" s="83"/>
+      <c r="AK15" s="83"/>
+      <c r="AL15" s="83"/>
+      <c r="AM15" s="83"/>
+      <c r="AN15" s="83"/>
+      <c r="AO15" s="83"/>
+      <c r="AP15" s="84"/>
+      <c r="AQ15" s="88"/>
+      <c r="AR15" s="83"/>
+      <c r="AS15" s="83"/>
+      <c r="AT15" s="83"/>
+      <c r="AU15" s="83"/>
+      <c r="AV15" s="83"/>
+      <c r="AW15" s="83"/>
+      <c r="AX15" s="83"/>
+      <c r="AY15" s="83"/>
+      <c r="AZ15" s="83"/>
+      <c r="BA15" s="83"/>
+      <c r="BB15" s="83"/>
+      <c r="BC15" s="83"/>
+      <c r="BD15" s="83"/>
+      <c r="BE15" s="89"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="100"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="70"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="70"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="70"/>
-      <c r="X16" s="70"/>
-      <c r="Y16" s="70"/>
-      <c r="Z16" s="70"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="70"/>
-      <c r="AC16" s="70"/>
-      <c r="AD16" s="70"/>
-      <c r="AE16" s="70"/>
-      <c r="AF16" s="70"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
-      <c r="AI16" s="70"/>
-      <c r="AJ16" s="70"/>
-      <c r="AK16" s="70"/>
-      <c r="AL16" s="70"/>
-      <c r="AM16" s="70"/>
-      <c r="AN16" s="70"/>
-      <c r="AO16" s="70"/>
-      <c r="AP16" s="82"/>
-      <c r="AQ16" s="69"/>
-      <c r="AR16" s="70"/>
-      <c r="AS16" s="70"/>
-      <c r="AT16" s="70"/>
-      <c r="AU16" s="70"/>
-      <c r="AV16" s="70"/>
-      <c r="AW16" s="70"/>
-      <c r="AX16" s="70"/>
-      <c r="AY16" s="70"/>
-      <c r="AZ16" s="70"/>
-      <c r="BA16" s="70"/>
-      <c r="BB16" s="70"/>
-      <c r="BC16" s="70"/>
-      <c r="BD16" s="70"/>
-      <c r="BE16" s="71"/>
+      <c r="A16" s="75"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="83"/>
+      <c r="X16" s="83"/>
+      <c r="Y16" s="83"/>
+      <c r="Z16" s="83"/>
+      <c r="AA16" s="83"/>
+      <c r="AB16" s="83"/>
+      <c r="AC16" s="83"/>
+      <c r="AD16" s="83"/>
+      <c r="AE16" s="83"/>
+      <c r="AF16" s="83"/>
+      <c r="AG16" s="83"/>
+      <c r="AH16" s="83"/>
+      <c r="AI16" s="83"/>
+      <c r="AJ16" s="83"/>
+      <c r="AK16" s="83"/>
+      <c r="AL16" s="83"/>
+      <c r="AM16" s="83"/>
+      <c r="AN16" s="83"/>
+      <c r="AO16" s="83"/>
+      <c r="AP16" s="84"/>
+      <c r="AQ16" s="88"/>
+      <c r="AR16" s="83"/>
+      <c r="AS16" s="83"/>
+      <c r="AT16" s="83"/>
+      <c r="AU16" s="83"/>
+      <c r="AV16" s="83"/>
+      <c r="AW16" s="83"/>
+      <c r="AX16" s="83"/>
+      <c r="AY16" s="83"/>
+      <c r="AZ16" s="83"/>
+      <c r="BA16" s="83"/>
+      <c r="BB16" s="83"/>
+      <c r="BC16" s="83"/>
+      <c r="BD16" s="83"/>
+      <c r="BE16" s="89"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="100"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="80"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="70"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="70"/>
-      <c r="AI17" s="70"/>
-      <c r="AJ17" s="70"/>
-      <c r="AK17" s="70"/>
-      <c r="AL17" s="70"/>
-      <c r="AM17" s="70"/>
-      <c r="AN17" s="70"/>
-      <c r="AO17" s="70"/>
-      <c r="AP17" s="82"/>
-      <c r="AQ17" s="69"/>
-      <c r="AR17" s="70"/>
-      <c r="AS17" s="70"/>
-      <c r="AT17" s="70"/>
-      <c r="AU17" s="70"/>
-      <c r="AV17" s="70"/>
-      <c r="AW17" s="70"/>
-      <c r="AX17" s="70"/>
-      <c r="AY17" s="70"/>
-      <c r="AZ17" s="70"/>
-      <c r="BA17" s="70"/>
-      <c r="BB17" s="70"/>
-      <c r="BC17" s="70"/>
-      <c r="BD17" s="70"/>
-      <c r="BE17" s="71"/>
+      <c r="A17" s="75"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="83"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="83"/>
+      <c r="S17" s="83"/>
+      <c r="T17" s="83"/>
+      <c r="U17" s="83"/>
+      <c r="V17" s="83"/>
+      <c r="W17" s="83"/>
+      <c r="X17" s="83"/>
+      <c r="Y17" s="83"/>
+      <c r="Z17" s="83"/>
+      <c r="AA17" s="83"/>
+      <c r="AB17" s="83"/>
+      <c r="AC17" s="83"/>
+      <c r="AD17" s="83"/>
+      <c r="AE17" s="83"/>
+      <c r="AF17" s="83"/>
+      <c r="AG17" s="83"/>
+      <c r="AH17" s="83"/>
+      <c r="AI17" s="83"/>
+      <c r="AJ17" s="83"/>
+      <c r="AK17" s="83"/>
+      <c r="AL17" s="83"/>
+      <c r="AM17" s="83"/>
+      <c r="AN17" s="83"/>
+      <c r="AO17" s="83"/>
+      <c r="AP17" s="84"/>
+      <c r="AQ17" s="88"/>
+      <c r="AR17" s="83"/>
+      <c r="AS17" s="83"/>
+      <c r="AT17" s="83"/>
+      <c r="AU17" s="83"/>
+      <c r="AV17" s="83"/>
+      <c r="AW17" s="83"/>
+      <c r="AX17" s="83"/>
+      <c r="AY17" s="83"/>
+      <c r="AZ17" s="83"/>
+      <c r="BA17" s="83"/>
+      <c r="BB17" s="83"/>
+      <c r="BC17" s="83"/>
+      <c r="BD17" s="83"/>
+      <c r="BE17" s="89"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="80"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="70"/>
-      <c r="T18" s="70"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="70"/>
-      <c r="X18" s="70"/>
-      <c r="Y18" s="70"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="70"/>
-      <c r="AC18" s="70"/>
-      <c r="AD18" s="70"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="70"/>
-      <c r="AI18" s="70"/>
-      <c r="AJ18" s="70"/>
-      <c r="AK18" s="70"/>
-      <c r="AL18" s="70"/>
-      <c r="AM18" s="70"/>
-      <c r="AN18" s="70"/>
-      <c r="AO18" s="70"/>
-      <c r="AP18" s="82"/>
-      <c r="AQ18" s="69"/>
-      <c r="AR18" s="70"/>
-      <c r="AS18" s="70"/>
-      <c r="AT18" s="70"/>
-      <c r="AU18" s="70"/>
-      <c r="AV18" s="70"/>
-      <c r="AW18" s="70"/>
-      <c r="AX18" s="70"/>
-      <c r="AY18" s="70"/>
-      <c r="AZ18" s="70"/>
-      <c r="BA18" s="70"/>
-      <c r="BB18" s="70"/>
-      <c r="BC18" s="70"/>
-      <c r="BD18" s="70"/>
-      <c r="BE18" s="71"/>
+      <c r="A18" s="75"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="83"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="83"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="83"/>
+      <c r="Y18" s="83"/>
+      <c r="Z18" s="83"/>
+      <c r="AA18" s="83"/>
+      <c r="AB18" s="83"/>
+      <c r="AC18" s="83"/>
+      <c r="AD18" s="83"/>
+      <c r="AE18" s="83"/>
+      <c r="AF18" s="83"/>
+      <c r="AG18" s="83"/>
+      <c r="AH18" s="83"/>
+      <c r="AI18" s="83"/>
+      <c r="AJ18" s="83"/>
+      <c r="AK18" s="83"/>
+      <c r="AL18" s="83"/>
+      <c r="AM18" s="83"/>
+      <c r="AN18" s="83"/>
+      <c r="AO18" s="83"/>
+      <c r="AP18" s="84"/>
+      <c r="AQ18" s="88"/>
+      <c r="AR18" s="83"/>
+      <c r="AS18" s="83"/>
+      <c r="AT18" s="83"/>
+      <c r="AU18" s="83"/>
+      <c r="AV18" s="83"/>
+      <c r="AW18" s="83"/>
+      <c r="AX18" s="83"/>
+      <c r="AY18" s="83"/>
+      <c r="AZ18" s="83"/>
+      <c r="BA18" s="83"/>
+      <c r="BB18" s="83"/>
+      <c r="BC18" s="83"/>
+      <c r="BD18" s="83"/>
+      <c r="BE18" s="89"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="100"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="70"/>
-      <c r="T19" s="70"/>
-      <c r="U19" s="70"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="70"/>
-      <c r="X19" s="70"/>
-      <c r="Y19" s="70"/>
-      <c r="Z19" s="70"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="70"/>
-      <c r="AC19" s="70"/>
-      <c r="AD19" s="70"/>
-      <c r="AE19" s="70"/>
-      <c r="AF19" s="70"/>
-      <c r="AG19" s="70"/>
-      <c r="AH19" s="70"/>
-      <c r="AI19" s="70"/>
-      <c r="AJ19" s="70"/>
-      <c r="AK19" s="70"/>
-      <c r="AL19" s="70"/>
-      <c r="AM19" s="70"/>
-      <c r="AN19" s="70"/>
-      <c r="AO19" s="70"/>
-      <c r="AP19" s="82"/>
-      <c r="AQ19" s="69"/>
-      <c r="AR19" s="70"/>
-      <c r="AS19" s="70"/>
-      <c r="AT19" s="70"/>
-      <c r="AU19" s="70"/>
-      <c r="AV19" s="70"/>
-      <c r="AW19" s="70"/>
-      <c r="AX19" s="70"/>
-      <c r="AY19" s="70"/>
-      <c r="AZ19" s="70"/>
-      <c r="BA19" s="70"/>
-      <c r="BB19" s="70"/>
-      <c r="BC19" s="70"/>
-      <c r="BD19" s="70"/>
-      <c r="BE19" s="71"/>
+      <c r="A19" s="75"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="83"/>
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="83"/>
+      <c r="W19" s="83"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="83"/>
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="83"/>
+      <c r="AB19" s="83"/>
+      <c r="AC19" s="83"/>
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="83"/>
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="83"/>
+      <c r="AH19" s="83"/>
+      <c r="AI19" s="83"/>
+      <c r="AJ19" s="83"/>
+      <c r="AK19" s="83"/>
+      <c r="AL19" s="83"/>
+      <c r="AM19" s="83"/>
+      <c r="AN19" s="83"/>
+      <c r="AO19" s="83"/>
+      <c r="AP19" s="84"/>
+      <c r="AQ19" s="88"/>
+      <c r="AR19" s="83"/>
+      <c r="AS19" s="83"/>
+      <c r="AT19" s="83"/>
+      <c r="AU19" s="83"/>
+      <c r="AV19" s="83"/>
+      <c r="AW19" s="83"/>
+      <c r="AX19" s="83"/>
+      <c r="AY19" s="83"/>
+      <c r="AZ19" s="83"/>
+      <c r="BA19" s="83"/>
+      <c r="BB19" s="83"/>
+      <c r="BC19" s="83"/>
+      <c r="BD19" s="83"/>
+      <c r="BE19" s="89"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="70"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="70"/>
-      <c r="T20" s="70"/>
-      <c r="U20" s="70"/>
-      <c r="V20" s="70"/>
-      <c r="W20" s="70"/>
-      <c r="X20" s="70"/>
-      <c r="Y20" s="70"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="70"/>
-      <c r="AC20" s="70"/>
-      <c r="AD20" s="70"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="70"/>
-      <c r="AH20" s="70"/>
-      <c r="AI20" s="70"/>
-      <c r="AJ20" s="70"/>
-      <c r="AK20" s="70"/>
-      <c r="AL20" s="70"/>
-      <c r="AM20" s="70"/>
-      <c r="AN20" s="70"/>
-      <c r="AO20" s="70"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="69"/>
-      <c r="AR20" s="70"/>
-      <c r="AS20" s="70"/>
-      <c r="AT20" s="70"/>
-      <c r="AU20" s="70"/>
-      <c r="AV20" s="70"/>
-      <c r="AW20" s="70"/>
-      <c r="AX20" s="70"/>
-      <c r="AY20" s="70"/>
-      <c r="AZ20" s="70"/>
-      <c r="BA20" s="70"/>
-      <c r="BB20" s="70"/>
-      <c r="BC20" s="70"/>
-      <c r="BD20" s="70"/>
-      <c r="BE20" s="71"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="84"/>
+      <c r="AQ20" s="88"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="89"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="100"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="101"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="70"/>
-      <c r="T21" s="70"/>
-      <c r="U21" s="70"/>
-      <c r="V21" s="70"/>
-      <c r="W21" s="70"/>
-      <c r="X21" s="70"/>
-      <c r="Y21" s="70"/>
-      <c r="Z21" s="70"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="70"/>
-      <c r="AC21" s="70"/>
-      <c r="AD21" s="70"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="70"/>
-      <c r="AI21" s="70"/>
-      <c r="AJ21" s="70"/>
-      <c r="AK21" s="70"/>
-      <c r="AL21" s="70"/>
-      <c r="AM21" s="70"/>
-      <c r="AN21" s="70"/>
-      <c r="AO21" s="70"/>
-      <c r="AP21" s="82"/>
-      <c r="AQ21" s="69"/>
-      <c r="AR21" s="70"/>
-      <c r="AS21" s="70"/>
-      <c r="AT21" s="70"/>
-      <c r="AU21" s="70"/>
-      <c r="AV21" s="70"/>
-      <c r="AW21" s="70"/>
-      <c r="AX21" s="70"/>
-      <c r="AY21" s="70"/>
-      <c r="AZ21" s="70"/>
-      <c r="BA21" s="70"/>
-      <c r="BB21" s="70"/>
-      <c r="BC21" s="70"/>
-      <c r="BD21" s="70"/>
-      <c r="BE21" s="71"/>
+      <c r="A21" s="75"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83"/>
+      <c r="S21" s="83"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="83"/>
+      <c r="Y21" s="83"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="83"/>
+      <c r="AB21" s="83"/>
+      <c r="AC21" s="83"/>
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="83"/>
+      <c r="AF21" s="83"/>
+      <c r="AG21" s="83"/>
+      <c r="AH21" s="83"/>
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="83"/>
+      <c r="AL21" s="83"/>
+      <c r="AM21" s="83"/>
+      <c r="AN21" s="83"/>
+      <c r="AO21" s="83"/>
+      <c r="AP21" s="84"/>
+      <c r="AQ21" s="88"/>
+      <c r="AR21" s="83"/>
+      <c r="AS21" s="83"/>
+      <c r="AT21" s="83"/>
+      <c r="AU21" s="83"/>
+      <c r="AV21" s="83"/>
+      <c r="AW21" s="83"/>
+      <c r="AX21" s="83"/>
+      <c r="AY21" s="83"/>
+      <c r="AZ21" s="83"/>
+      <c r="BA21" s="83"/>
+      <c r="BB21" s="83"/>
+      <c r="BC21" s="83"/>
+      <c r="BD21" s="83"/>
+      <c r="BE21" s="89"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="100"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="70"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="70"/>
-      <c r="AC22" s="70"/>
-      <c r="AD22" s="70"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="70"/>
-      <c r="AH22" s="70"/>
-      <c r="AI22" s="70"/>
-      <c r="AJ22" s="70"/>
-      <c r="AK22" s="70"/>
-      <c r="AL22" s="70"/>
-      <c r="AM22" s="70"/>
-      <c r="AN22" s="70"/>
-      <c r="AO22" s="70"/>
-      <c r="AP22" s="82"/>
-      <c r="AQ22" s="69"/>
-      <c r="AR22" s="70"/>
-      <c r="AS22" s="70"/>
-      <c r="AT22" s="70"/>
-      <c r="AU22" s="70"/>
-      <c r="AV22" s="70"/>
-      <c r="AW22" s="70"/>
-      <c r="AX22" s="70"/>
-      <c r="AY22" s="70"/>
-      <c r="AZ22" s="70"/>
-      <c r="BA22" s="70"/>
-      <c r="BB22" s="70"/>
-      <c r="BC22" s="70"/>
-      <c r="BD22" s="70"/>
-      <c r="BE22" s="71"/>
+      <c r="A22" s="75"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="90"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="82"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="83"/>
+      <c r="T22" s="83"/>
+      <c r="U22" s="83"/>
+      <c r="V22" s="83"/>
+      <c r="W22" s="83"/>
+      <c r="X22" s="83"/>
+      <c r="Y22" s="83"/>
+      <c r="Z22" s="83"/>
+      <c r="AA22" s="83"/>
+      <c r="AB22" s="83"/>
+      <c r="AC22" s="83"/>
+      <c r="AD22" s="83"/>
+      <c r="AE22" s="83"/>
+      <c r="AF22" s="83"/>
+      <c r="AG22" s="83"/>
+      <c r="AH22" s="83"/>
+      <c r="AI22" s="83"/>
+      <c r="AJ22" s="83"/>
+      <c r="AK22" s="83"/>
+      <c r="AL22" s="83"/>
+      <c r="AM22" s="83"/>
+      <c r="AN22" s="83"/>
+      <c r="AO22" s="83"/>
+      <c r="AP22" s="84"/>
+      <c r="AQ22" s="88"/>
+      <c r="AR22" s="83"/>
+      <c r="AS22" s="83"/>
+      <c r="AT22" s="83"/>
+      <c r="AU22" s="83"/>
+      <c r="AV22" s="83"/>
+      <c r="AW22" s="83"/>
+      <c r="AX22" s="83"/>
+      <c r="AY22" s="83"/>
+      <c r="AZ22" s="83"/>
+      <c r="BA22" s="83"/>
+      <c r="BB22" s="83"/>
+      <c r="BC22" s="83"/>
+      <c r="BD22" s="83"/>
+      <c r="BE22" s="89"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="100"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="70"/>
-      <c r="T23" s="70"/>
-      <c r="U23" s="70"/>
-      <c r="V23" s="70"/>
-      <c r="W23" s="70"/>
-      <c r="X23" s="70"/>
-      <c r="Y23" s="70"/>
-      <c r="Z23" s="70"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="70"/>
-      <c r="AC23" s="70"/>
-      <c r="AD23" s="70"/>
-      <c r="AE23" s="70"/>
-      <c r="AF23" s="70"/>
-      <c r="AG23" s="70"/>
-      <c r="AH23" s="70"/>
-      <c r="AI23" s="70"/>
-      <c r="AJ23" s="70"/>
-      <c r="AK23" s="70"/>
-      <c r="AL23" s="70"/>
-      <c r="AM23" s="70"/>
-      <c r="AN23" s="70"/>
-      <c r="AO23" s="70"/>
-      <c r="AP23" s="82"/>
-      <c r="AQ23" s="69"/>
-      <c r="AR23" s="70"/>
-      <c r="AS23" s="70"/>
-      <c r="AT23" s="70"/>
-      <c r="AU23" s="70"/>
-      <c r="AV23" s="70"/>
-      <c r="AW23" s="70"/>
-      <c r="AX23" s="70"/>
-      <c r="AY23" s="70"/>
-      <c r="AZ23" s="70"/>
-      <c r="BA23" s="70"/>
-      <c r="BB23" s="70"/>
-      <c r="BC23" s="70"/>
-      <c r="BD23" s="70"/>
-      <c r="BE23" s="71"/>
+      <c r="A23" s="75"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="83"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="83"/>
+      <c r="Y23" s="83"/>
+      <c r="Z23" s="83"/>
+      <c r="AA23" s="83"/>
+      <c r="AB23" s="83"/>
+      <c r="AC23" s="83"/>
+      <c r="AD23" s="83"/>
+      <c r="AE23" s="83"/>
+      <c r="AF23" s="83"/>
+      <c r="AG23" s="83"/>
+      <c r="AH23" s="83"/>
+      <c r="AI23" s="83"/>
+      <c r="AJ23" s="83"/>
+      <c r="AK23" s="83"/>
+      <c r="AL23" s="83"/>
+      <c r="AM23" s="83"/>
+      <c r="AN23" s="83"/>
+      <c r="AO23" s="83"/>
+      <c r="AP23" s="84"/>
+      <c r="AQ23" s="88"/>
+      <c r="AR23" s="83"/>
+      <c r="AS23" s="83"/>
+      <c r="AT23" s="83"/>
+      <c r="AU23" s="83"/>
+      <c r="AV23" s="83"/>
+      <c r="AW23" s="83"/>
+      <c r="AX23" s="83"/>
+      <c r="AY23" s="83"/>
+      <c r="AZ23" s="83"/>
+      <c r="BA23" s="83"/>
+      <c r="BB23" s="83"/>
+      <c r="BC23" s="83"/>
+      <c r="BD23" s="83"/>
+      <c r="BE23" s="89"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="100"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="70"/>
-      <c r="T24" s="70"/>
-      <c r="U24" s="70"/>
-      <c r="V24" s="70"/>
-      <c r="W24" s="70"/>
-      <c r="X24" s="70"/>
-      <c r="Y24" s="70"/>
-      <c r="Z24" s="70"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="70"/>
-      <c r="AC24" s="70"/>
-      <c r="AD24" s="70"/>
-      <c r="AE24" s="70"/>
-      <c r="AF24" s="70"/>
-      <c r="AG24" s="70"/>
-      <c r="AH24" s="70"/>
-      <c r="AI24" s="70"/>
-      <c r="AJ24" s="70"/>
-      <c r="AK24" s="70"/>
-      <c r="AL24" s="70"/>
-      <c r="AM24" s="70"/>
-      <c r="AN24" s="70"/>
-      <c r="AO24" s="70"/>
-      <c r="AP24" s="82"/>
-      <c r="AQ24" s="69"/>
-      <c r="AR24" s="70"/>
-      <c r="AS24" s="70"/>
-      <c r="AT24" s="70"/>
-      <c r="AU24" s="70"/>
-      <c r="AV24" s="70"/>
-      <c r="AW24" s="70"/>
-      <c r="AX24" s="70"/>
-      <c r="AY24" s="70"/>
-      <c r="AZ24" s="70"/>
-      <c r="BA24" s="70"/>
-      <c r="BB24" s="70"/>
-      <c r="BC24" s="70"/>
-      <c r="BD24" s="70"/>
-      <c r="BE24" s="71"/>
+      <c r="A24" s="75"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="83"/>
+      <c r="S24" s="83"/>
+      <c r="T24" s="83"/>
+      <c r="U24" s="83"/>
+      <c r="V24" s="83"/>
+      <c r="W24" s="83"/>
+      <c r="X24" s="83"/>
+      <c r="Y24" s="83"/>
+      <c r="Z24" s="83"/>
+      <c r="AA24" s="83"/>
+      <c r="AB24" s="83"/>
+      <c r="AC24" s="83"/>
+      <c r="AD24" s="83"/>
+      <c r="AE24" s="83"/>
+      <c r="AF24" s="83"/>
+      <c r="AG24" s="83"/>
+      <c r="AH24" s="83"/>
+      <c r="AI24" s="83"/>
+      <c r="AJ24" s="83"/>
+      <c r="AK24" s="83"/>
+      <c r="AL24" s="83"/>
+      <c r="AM24" s="83"/>
+      <c r="AN24" s="83"/>
+      <c r="AO24" s="83"/>
+      <c r="AP24" s="84"/>
+      <c r="AQ24" s="88"/>
+      <c r="AR24" s="83"/>
+      <c r="AS24" s="83"/>
+      <c r="AT24" s="83"/>
+      <c r="AU24" s="83"/>
+      <c r="AV24" s="83"/>
+      <c r="AW24" s="83"/>
+      <c r="AX24" s="83"/>
+      <c r="AY24" s="83"/>
+      <c r="AZ24" s="83"/>
+      <c r="BA24" s="83"/>
+      <c r="BB24" s="83"/>
+      <c r="BC24" s="83"/>
+      <c r="BD24" s="83"/>
+      <c r="BE24" s="89"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="100"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="70"/>
-      <c r="T25" s="70"/>
-      <c r="U25" s="70"/>
-      <c r="V25" s="70"/>
-      <c r="W25" s="70"/>
-      <c r="X25" s="70"/>
-      <c r="Y25" s="70"/>
-      <c r="Z25" s="70"/>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="70"/>
-      <c r="AC25" s="70"/>
-      <c r="AD25" s="70"/>
-      <c r="AE25" s="70"/>
-      <c r="AF25" s="70"/>
-      <c r="AG25" s="70"/>
-      <c r="AH25" s="70"/>
-      <c r="AI25" s="70"/>
-      <c r="AJ25" s="70"/>
-      <c r="AK25" s="70"/>
-      <c r="AL25" s="70"/>
-      <c r="AM25" s="70"/>
-      <c r="AN25" s="70"/>
-      <c r="AO25" s="70"/>
-      <c r="AP25" s="82"/>
-      <c r="AQ25" s="69"/>
-      <c r="AR25" s="70"/>
-      <c r="AS25" s="70"/>
-      <c r="AT25" s="70"/>
-      <c r="AU25" s="70"/>
-      <c r="AV25" s="70"/>
-      <c r="AW25" s="70"/>
-      <c r="AX25" s="70"/>
-      <c r="AY25" s="70"/>
-      <c r="AZ25" s="70"/>
-      <c r="BA25" s="70"/>
-      <c r="BB25" s="70"/>
-      <c r="BC25" s="70"/>
-      <c r="BD25" s="70"/>
-      <c r="BE25" s="71"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="83"/>
+      <c r="T25" s="83"/>
+      <c r="U25" s="83"/>
+      <c r="V25" s="83"/>
+      <c r="W25" s="83"/>
+      <c r="X25" s="83"/>
+      <c r="Y25" s="83"/>
+      <c r="Z25" s="83"/>
+      <c r="AA25" s="83"/>
+      <c r="AB25" s="83"/>
+      <c r="AC25" s="83"/>
+      <c r="AD25" s="83"/>
+      <c r="AE25" s="83"/>
+      <c r="AF25" s="83"/>
+      <c r="AG25" s="83"/>
+      <c r="AH25" s="83"/>
+      <c r="AI25" s="83"/>
+      <c r="AJ25" s="83"/>
+      <c r="AK25" s="83"/>
+      <c r="AL25" s="83"/>
+      <c r="AM25" s="83"/>
+      <c r="AN25" s="83"/>
+      <c r="AO25" s="83"/>
+      <c r="AP25" s="84"/>
+      <c r="AQ25" s="88"/>
+      <c r="AR25" s="83"/>
+      <c r="AS25" s="83"/>
+      <c r="AT25" s="83"/>
+      <c r="AU25" s="83"/>
+      <c r="AV25" s="83"/>
+      <c r="AW25" s="83"/>
+      <c r="AX25" s="83"/>
+      <c r="AY25" s="83"/>
+      <c r="AZ25" s="83"/>
+      <c r="BA25" s="83"/>
+      <c r="BB25" s="83"/>
+      <c r="BC25" s="83"/>
+      <c r="BD25" s="83"/>
+      <c r="BE25" s="89"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="100"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="79"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="70"/>
-      <c r="T26" s="70"/>
-      <c r="U26" s="70"/>
-      <c r="V26" s="70"/>
-      <c r="W26" s="70"/>
-      <c r="X26" s="70"/>
-      <c r="Y26" s="70"/>
-      <c r="Z26" s="70"/>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="70"/>
-      <c r="AC26" s="70"/>
-      <c r="AD26" s="70"/>
-      <c r="AE26" s="70"/>
-      <c r="AF26" s="70"/>
-      <c r="AG26" s="70"/>
-      <c r="AH26" s="70"/>
-      <c r="AI26" s="70"/>
-      <c r="AJ26" s="70"/>
-      <c r="AK26" s="70"/>
-      <c r="AL26" s="70"/>
-      <c r="AM26" s="70"/>
-      <c r="AN26" s="70"/>
-      <c r="AO26" s="70"/>
-      <c r="AP26" s="82"/>
-      <c r="AQ26" s="69"/>
-      <c r="AR26" s="70"/>
-      <c r="AS26" s="70"/>
-      <c r="AT26" s="70"/>
-      <c r="AU26" s="70"/>
-      <c r="AV26" s="70"/>
-      <c r="AW26" s="70"/>
-      <c r="AX26" s="70"/>
-      <c r="AY26" s="70"/>
-      <c r="AZ26" s="70"/>
-      <c r="BA26" s="70"/>
-      <c r="BB26" s="70"/>
-      <c r="BC26" s="70"/>
-      <c r="BD26" s="70"/>
-      <c r="BE26" s="71"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="83"/>
+      <c r="S26" s="83"/>
+      <c r="T26" s="83"/>
+      <c r="U26" s="83"/>
+      <c r="V26" s="83"/>
+      <c r="W26" s="83"/>
+      <c r="X26" s="83"/>
+      <c r="Y26" s="83"/>
+      <c r="Z26" s="83"/>
+      <c r="AA26" s="83"/>
+      <c r="AB26" s="83"/>
+      <c r="AC26" s="83"/>
+      <c r="AD26" s="83"/>
+      <c r="AE26" s="83"/>
+      <c r="AF26" s="83"/>
+      <c r="AG26" s="83"/>
+      <c r="AH26" s="83"/>
+      <c r="AI26" s="83"/>
+      <c r="AJ26" s="83"/>
+      <c r="AK26" s="83"/>
+      <c r="AL26" s="83"/>
+      <c r="AM26" s="83"/>
+      <c r="AN26" s="83"/>
+      <c r="AO26" s="83"/>
+      <c r="AP26" s="84"/>
+      <c r="AQ26" s="88"/>
+      <c r="AR26" s="83"/>
+      <c r="AS26" s="83"/>
+      <c r="AT26" s="83"/>
+      <c r="AU26" s="83"/>
+      <c r="AV26" s="83"/>
+      <c r="AW26" s="83"/>
+      <c r="AX26" s="83"/>
+      <c r="AY26" s="83"/>
+      <c r="AZ26" s="83"/>
+      <c r="BA26" s="83"/>
+      <c r="BB26" s="83"/>
+      <c r="BC26" s="83"/>
+      <c r="BD26" s="83"/>
+      <c r="BE26" s="89"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="80"/>
-      <c r="J27" s="80"/>
-      <c r="K27" s="80"/>
-      <c r="L27" s="80"/>
-      <c r="M27" s="80"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="70"/>
-      <c r="T27" s="70"/>
-      <c r="U27" s="70"/>
-      <c r="V27" s="70"/>
-      <c r="W27" s="70"/>
-      <c r="X27" s="70"/>
-      <c r="Y27" s="70"/>
-      <c r="Z27" s="70"/>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
-      <c r="AC27" s="70"/>
-      <c r="AD27" s="70"/>
-      <c r="AE27" s="70"/>
-      <c r="AF27" s="70"/>
-      <c r="AG27" s="70"/>
-      <c r="AH27" s="70"/>
-      <c r="AI27" s="70"/>
-      <c r="AJ27" s="70"/>
-      <c r="AK27" s="70"/>
-      <c r="AL27" s="70"/>
-      <c r="AM27" s="70"/>
-      <c r="AN27" s="70"/>
-      <c r="AO27" s="70"/>
-      <c r="AP27" s="82"/>
-      <c r="AQ27" s="69"/>
-      <c r="AR27" s="70"/>
-      <c r="AS27" s="70"/>
-      <c r="AT27" s="70"/>
-      <c r="AU27" s="70"/>
-      <c r="AV27" s="70"/>
-      <c r="AW27" s="70"/>
-      <c r="AX27" s="70"/>
-      <c r="AY27" s="70"/>
-      <c r="AZ27" s="70"/>
-      <c r="BA27" s="70"/>
-      <c r="BB27" s="70"/>
-      <c r="BC27" s="70"/>
-      <c r="BD27" s="70"/>
-      <c r="BE27" s="71"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="83"/>
+      <c r="S27" s="83"/>
+      <c r="T27" s="83"/>
+      <c r="U27" s="83"/>
+      <c r="V27" s="83"/>
+      <c r="W27" s="83"/>
+      <c r="X27" s="83"/>
+      <c r="Y27" s="83"/>
+      <c r="Z27" s="83"/>
+      <c r="AA27" s="83"/>
+      <c r="AB27" s="83"/>
+      <c r="AC27" s="83"/>
+      <c r="AD27" s="83"/>
+      <c r="AE27" s="83"/>
+      <c r="AF27" s="83"/>
+      <c r="AG27" s="83"/>
+      <c r="AH27" s="83"/>
+      <c r="AI27" s="83"/>
+      <c r="AJ27" s="83"/>
+      <c r="AK27" s="83"/>
+      <c r="AL27" s="83"/>
+      <c r="AM27" s="83"/>
+      <c r="AN27" s="83"/>
+      <c r="AO27" s="83"/>
+      <c r="AP27" s="84"/>
+      <c r="AQ27" s="88"/>
+      <c r="AR27" s="83"/>
+      <c r="AS27" s="83"/>
+      <c r="AT27" s="83"/>
+      <c r="AU27" s="83"/>
+      <c r="AV27" s="83"/>
+      <c r="AW27" s="83"/>
+      <c r="AX27" s="83"/>
+      <c r="AY27" s="83"/>
+      <c r="AZ27" s="83"/>
+      <c r="BA27" s="83"/>
+      <c r="BB27" s="83"/>
+      <c r="BC27" s="83"/>
+      <c r="BD27" s="83"/>
+      <c r="BE27" s="89"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="100"/>
-      <c r="B28" s="101"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="80"/>
-      <c r="J28" s="80"/>
-      <c r="K28" s="80"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="80"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="70"/>
-      <c r="T28" s="70"/>
-      <c r="U28" s="70"/>
-      <c r="V28" s="70"/>
-      <c r="W28" s="70"/>
-      <c r="X28" s="70"/>
-      <c r="Y28" s="70"/>
-      <c r="Z28" s="70"/>
-      <c r="AA28" s="70"/>
-      <c r="AB28" s="70"/>
-      <c r="AC28" s="70"/>
-      <c r="AD28" s="70"/>
-      <c r="AE28" s="70"/>
-      <c r="AF28" s="70"/>
-      <c r="AG28" s="70"/>
-      <c r="AH28" s="70"/>
-      <c r="AI28" s="70"/>
-      <c r="AJ28" s="70"/>
-      <c r="AK28" s="70"/>
-      <c r="AL28" s="70"/>
-      <c r="AM28" s="70"/>
-      <c r="AN28" s="70"/>
-      <c r="AO28" s="70"/>
-      <c r="AP28" s="82"/>
-      <c r="AQ28" s="69"/>
-      <c r="AR28" s="70"/>
-      <c r="AS28" s="70"/>
-      <c r="AT28" s="70"/>
-      <c r="AU28" s="70"/>
-      <c r="AV28" s="70"/>
-      <c r="AW28" s="70"/>
-      <c r="AX28" s="70"/>
-      <c r="AY28" s="70"/>
-      <c r="AZ28" s="70"/>
-      <c r="BA28" s="70"/>
-      <c r="BB28" s="70"/>
-      <c r="BC28" s="70"/>
-      <c r="BD28" s="70"/>
-      <c r="BE28" s="71"/>
+      <c r="A28" s="75"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="83"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="83"/>
+      <c r="AB28" s="83"/>
+      <c r="AC28" s="83"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="83"/>
+      <c r="AG28" s="83"/>
+      <c r="AH28" s="83"/>
+      <c r="AI28" s="83"/>
+      <c r="AJ28" s="83"/>
+      <c r="AK28" s="83"/>
+      <c r="AL28" s="83"/>
+      <c r="AM28" s="83"/>
+      <c r="AN28" s="83"/>
+      <c r="AO28" s="83"/>
+      <c r="AP28" s="84"/>
+      <c r="AQ28" s="88"/>
+      <c r="AR28" s="83"/>
+      <c r="AS28" s="83"/>
+      <c r="AT28" s="83"/>
+      <c r="AU28" s="83"/>
+      <c r="AV28" s="83"/>
+      <c r="AW28" s="83"/>
+      <c r="AX28" s="83"/>
+      <c r="AY28" s="83"/>
+      <c r="AZ28" s="83"/>
+      <c r="BA28" s="83"/>
+      <c r="BB28" s="83"/>
+      <c r="BC28" s="83"/>
+      <c r="BD28" s="83"/>
+      <c r="BE28" s="89"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="100"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
-      <c r="M29" s="80"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="70"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
-      <c r="Z29" s="70"/>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="70"/>
-      <c r="AC29" s="70"/>
-      <c r="AD29" s="70"/>
-      <c r="AE29" s="70"/>
-      <c r="AF29" s="70"/>
-      <c r="AG29" s="70"/>
-      <c r="AH29" s="70"/>
-      <c r="AI29" s="70"/>
-      <c r="AJ29" s="70"/>
-      <c r="AK29" s="70"/>
-      <c r="AL29" s="70"/>
-      <c r="AM29" s="70"/>
-      <c r="AN29" s="70"/>
-      <c r="AO29" s="70"/>
-      <c r="AP29" s="82"/>
-      <c r="AQ29" s="69"/>
-      <c r="AR29" s="70"/>
-      <c r="AS29" s="70"/>
-      <c r="AT29" s="70"/>
-      <c r="AU29" s="70"/>
-      <c r="AV29" s="70"/>
-      <c r="AW29" s="70"/>
-      <c r="AX29" s="70"/>
-      <c r="AY29" s="70"/>
-      <c r="AZ29" s="70"/>
-      <c r="BA29" s="70"/>
-      <c r="BB29" s="70"/>
-      <c r="BC29" s="70"/>
-      <c r="BD29" s="70"/>
-      <c r="BE29" s="71"/>
+      <c r="A29" s="75"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="82"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="82"/>
+      <c r="P29" s="83"/>
+      <c r="Q29" s="83"/>
+      <c r="R29" s="83"/>
+      <c r="S29" s="83"/>
+      <c r="T29" s="83"/>
+      <c r="U29" s="83"/>
+      <c r="V29" s="83"/>
+      <c r="W29" s="83"/>
+      <c r="X29" s="83"/>
+      <c r="Y29" s="83"/>
+      <c r="Z29" s="83"/>
+      <c r="AA29" s="83"/>
+      <c r="AB29" s="83"/>
+      <c r="AC29" s="83"/>
+      <c r="AD29" s="83"/>
+      <c r="AE29" s="83"/>
+      <c r="AF29" s="83"/>
+      <c r="AG29" s="83"/>
+      <c r="AH29" s="83"/>
+      <c r="AI29" s="83"/>
+      <c r="AJ29" s="83"/>
+      <c r="AK29" s="83"/>
+      <c r="AL29" s="83"/>
+      <c r="AM29" s="83"/>
+      <c r="AN29" s="83"/>
+      <c r="AO29" s="83"/>
+      <c r="AP29" s="84"/>
+      <c r="AQ29" s="88"/>
+      <c r="AR29" s="83"/>
+      <c r="AS29" s="83"/>
+      <c r="AT29" s="83"/>
+      <c r="AU29" s="83"/>
+      <c r="AV29" s="83"/>
+      <c r="AW29" s="83"/>
+      <c r="AX29" s="83"/>
+      <c r="AY29" s="83"/>
+      <c r="AZ29" s="83"/>
+      <c r="BA29" s="83"/>
+      <c r="BB29" s="83"/>
+      <c r="BC29" s="83"/>
+      <c r="BD29" s="83"/>
+      <c r="BE29" s="89"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="100"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="80"/>
-      <c r="M30" s="80"/>
-      <c r="N30" s="81"/>
-      <c r="O30" s="79"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="70"/>
-      <c r="S30" s="70"/>
-      <c r="T30" s="70"/>
-      <c r="U30" s="70"/>
-      <c r="V30" s="70"/>
-      <c r="W30" s="70"/>
-      <c r="X30" s="70"/>
-      <c r="Y30" s="70"/>
-      <c r="Z30" s="70"/>
-      <c r="AA30" s="70"/>
-      <c r="AB30" s="70"/>
-      <c r="AC30" s="70"/>
-      <c r="AD30" s="70"/>
-      <c r="AE30" s="70"/>
-      <c r="AF30" s="70"/>
-      <c r="AG30" s="70"/>
-      <c r="AH30" s="70"/>
-      <c r="AI30" s="70"/>
-      <c r="AJ30" s="70"/>
-      <c r="AK30" s="70"/>
-      <c r="AL30" s="70"/>
-      <c r="AM30" s="70"/>
-      <c r="AN30" s="70"/>
-      <c r="AO30" s="70"/>
-      <c r="AP30" s="82"/>
-      <c r="AQ30" s="69"/>
-      <c r="AR30" s="70"/>
-      <c r="AS30" s="70"/>
-      <c r="AT30" s="70"/>
-      <c r="AU30" s="70"/>
-      <c r="AV30" s="70"/>
-      <c r="AW30" s="70"/>
-      <c r="AX30" s="70"/>
-      <c r="AY30" s="70"/>
-      <c r="AZ30" s="70"/>
-      <c r="BA30" s="70"/>
-      <c r="BB30" s="70"/>
-      <c r="BC30" s="70"/>
-      <c r="BD30" s="70"/>
-      <c r="BE30" s="71"/>
+      <c r="A30" s="75"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="82"/>
+      <c r="P30" s="83"/>
+      <c r="Q30" s="83"/>
+      <c r="R30" s="83"/>
+      <c r="S30" s="83"/>
+      <c r="T30" s="83"/>
+      <c r="U30" s="83"/>
+      <c r="V30" s="83"/>
+      <c r="W30" s="83"/>
+      <c r="X30" s="83"/>
+      <c r="Y30" s="83"/>
+      <c r="Z30" s="83"/>
+      <c r="AA30" s="83"/>
+      <c r="AB30" s="83"/>
+      <c r="AC30" s="83"/>
+      <c r="AD30" s="83"/>
+      <c r="AE30" s="83"/>
+      <c r="AF30" s="83"/>
+      <c r="AG30" s="83"/>
+      <c r="AH30" s="83"/>
+      <c r="AI30" s="83"/>
+      <c r="AJ30" s="83"/>
+      <c r="AK30" s="83"/>
+      <c r="AL30" s="83"/>
+      <c r="AM30" s="83"/>
+      <c r="AN30" s="83"/>
+      <c r="AO30" s="83"/>
+      <c r="AP30" s="84"/>
+      <c r="AQ30" s="88"/>
+      <c r="AR30" s="83"/>
+      <c r="AS30" s="83"/>
+      <c r="AT30" s="83"/>
+      <c r="AU30" s="83"/>
+      <c r="AV30" s="83"/>
+      <c r="AW30" s="83"/>
+      <c r="AX30" s="83"/>
+      <c r="AY30" s="83"/>
+      <c r="AZ30" s="83"/>
+      <c r="BA30" s="83"/>
+      <c r="BB30" s="83"/>
+      <c r="BC30" s="83"/>
+      <c r="BD30" s="83"/>
+      <c r="BE30" s="89"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="100"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="79"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="70"/>
-      <c r="R31" s="70"/>
-      <c r="S31" s="70"/>
-      <c r="T31" s="70"/>
-      <c r="U31" s="70"/>
-      <c r="V31" s="70"/>
-      <c r="W31" s="70"/>
-      <c r="X31" s="70"/>
-      <c r="Y31" s="70"/>
-      <c r="Z31" s="70"/>
-      <c r="AA31" s="70"/>
-      <c r="AB31" s="70"/>
-      <c r="AC31" s="70"/>
-      <c r="AD31" s="70"/>
-      <c r="AE31" s="70"/>
-      <c r="AF31" s="70"/>
-      <c r="AG31" s="70"/>
-      <c r="AH31" s="70"/>
-      <c r="AI31" s="70"/>
-      <c r="AJ31" s="70"/>
-      <c r="AK31" s="70"/>
-      <c r="AL31" s="70"/>
-      <c r="AM31" s="70"/>
-      <c r="AN31" s="70"/>
-      <c r="AO31" s="70"/>
-      <c r="AP31" s="82"/>
-      <c r="AQ31" s="69"/>
-      <c r="AR31" s="70"/>
-      <c r="AS31" s="70"/>
-      <c r="AT31" s="70"/>
-      <c r="AU31" s="70"/>
-      <c r="AV31" s="70"/>
-      <c r="AW31" s="70"/>
-      <c r="AX31" s="70"/>
-      <c r="AY31" s="70"/>
-      <c r="AZ31" s="70"/>
-      <c r="BA31" s="70"/>
-      <c r="BB31" s="70"/>
-      <c r="BC31" s="70"/>
-      <c r="BD31" s="70"/>
-      <c r="BE31" s="71"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="82"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="83"/>
+      <c r="Q31" s="83"/>
+      <c r="R31" s="83"/>
+      <c r="S31" s="83"/>
+      <c r="T31" s="83"/>
+      <c r="U31" s="83"/>
+      <c r="V31" s="83"/>
+      <c r="W31" s="83"/>
+      <c r="X31" s="83"/>
+      <c r="Y31" s="83"/>
+      <c r="Z31" s="83"/>
+      <c r="AA31" s="83"/>
+      <c r="AB31" s="83"/>
+      <c r="AC31" s="83"/>
+      <c r="AD31" s="83"/>
+      <c r="AE31" s="83"/>
+      <c r="AF31" s="83"/>
+      <c r="AG31" s="83"/>
+      <c r="AH31" s="83"/>
+      <c r="AI31" s="83"/>
+      <c r="AJ31" s="83"/>
+      <c r="AK31" s="83"/>
+      <c r="AL31" s="83"/>
+      <c r="AM31" s="83"/>
+      <c r="AN31" s="83"/>
+      <c r="AO31" s="83"/>
+      <c r="AP31" s="84"/>
+      <c r="AQ31" s="88"/>
+      <c r="AR31" s="83"/>
+      <c r="AS31" s="83"/>
+      <c r="AT31" s="83"/>
+      <c r="AU31" s="83"/>
+      <c r="AV31" s="83"/>
+      <c r="AW31" s="83"/>
+      <c r="AX31" s="83"/>
+      <c r="AY31" s="83"/>
+      <c r="AZ31" s="83"/>
+      <c r="BA31" s="83"/>
+      <c r="BB31" s="83"/>
+      <c r="BC31" s="83"/>
+      <c r="BD31" s="83"/>
+      <c r="BE31" s="89"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="100"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="101"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
-      <c r="N32" s="81"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="70"/>
-      <c r="R32" s="70"/>
-      <c r="S32" s="70"/>
-      <c r="T32" s="70"/>
-      <c r="U32" s="70"/>
-      <c r="V32" s="70"/>
-      <c r="W32" s="70"/>
-      <c r="X32" s="70"/>
-      <c r="Y32" s="70"/>
-      <c r="Z32" s="70"/>
-      <c r="AA32" s="70"/>
-      <c r="AB32" s="70"/>
-      <c r="AC32" s="70"/>
-      <c r="AD32" s="70"/>
-      <c r="AE32" s="70"/>
-      <c r="AF32" s="70"/>
-      <c r="AG32" s="70"/>
-      <c r="AH32" s="70"/>
-      <c r="AI32" s="70"/>
-      <c r="AJ32" s="70"/>
-      <c r="AK32" s="70"/>
-      <c r="AL32" s="70"/>
-      <c r="AM32" s="70"/>
-      <c r="AN32" s="70"/>
-      <c r="AO32" s="70"/>
-      <c r="AP32" s="82"/>
-      <c r="AQ32" s="69"/>
-      <c r="AR32" s="70"/>
-      <c r="AS32" s="70"/>
-      <c r="AT32" s="70"/>
-      <c r="AU32" s="70"/>
-      <c r="AV32" s="70"/>
-      <c r="AW32" s="70"/>
-      <c r="AX32" s="70"/>
-      <c r="AY32" s="70"/>
-      <c r="AZ32" s="70"/>
-      <c r="BA32" s="70"/>
-      <c r="BB32" s="70"/>
-      <c r="BC32" s="70"/>
-      <c r="BD32" s="70"/>
-      <c r="BE32" s="71"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="82"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="83"/>
+      <c r="Q32" s="83"/>
+      <c r="R32" s="83"/>
+      <c r="S32" s="83"/>
+      <c r="T32" s="83"/>
+      <c r="U32" s="83"/>
+      <c r="V32" s="83"/>
+      <c r="W32" s="83"/>
+      <c r="X32" s="83"/>
+      <c r="Y32" s="83"/>
+      <c r="Z32" s="83"/>
+      <c r="AA32" s="83"/>
+      <c r="AB32" s="83"/>
+      <c r="AC32" s="83"/>
+      <c r="AD32" s="83"/>
+      <c r="AE32" s="83"/>
+      <c r="AF32" s="83"/>
+      <c r="AG32" s="83"/>
+      <c r="AH32" s="83"/>
+      <c r="AI32" s="83"/>
+      <c r="AJ32" s="83"/>
+      <c r="AK32" s="83"/>
+      <c r="AL32" s="83"/>
+      <c r="AM32" s="83"/>
+      <c r="AN32" s="83"/>
+      <c r="AO32" s="83"/>
+      <c r="AP32" s="84"/>
+      <c r="AQ32" s="88"/>
+      <c r="AR32" s="83"/>
+      <c r="AS32" s="83"/>
+      <c r="AT32" s="83"/>
+      <c r="AU32" s="83"/>
+      <c r="AV32" s="83"/>
+      <c r="AW32" s="83"/>
+      <c r="AX32" s="83"/>
+      <c r="AY32" s="83"/>
+      <c r="AZ32" s="83"/>
+      <c r="BA32" s="83"/>
+      <c r="BB32" s="83"/>
+      <c r="BC32" s="83"/>
+      <c r="BD32" s="83"/>
+      <c r="BE32" s="89"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="100"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="102"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="80"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="81"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
-      <c r="S33" s="70"/>
-      <c r="T33" s="70"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="70"/>
-      <c r="Y33" s="70"/>
-      <c r="Z33" s="70"/>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="70"/>
-      <c r="AC33" s="70"/>
-      <c r="AD33" s="70"/>
-      <c r="AE33" s="70"/>
-      <c r="AF33" s="70"/>
-      <c r="AG33" s="70"/>
-      <c r="AH33" s="70"/>
-      <c r="AI33" s="70"/>
-      <c r="AJ33" s="70"/>
-      <c r="AK33" s="70"/>
-      <c r="AL33" s="70"/>
-      <c r="AM33" s="70"/>
-      <c r="AN33" s="70"/>
-      <c r="AO33" s="70"/>
-      <c r="AP33" s="82"/>
-      <c r="AQ33" s="69"/>
-      <c r="AR33" s="70"/>
-      <c r="AS33" s="70"/>
-      <c r="AT33" s="70"/>
-      <c r="AU33" s="70"/>
-      <c r="AV33" s="70"/>
-      <c r="AW33" s="70"/>
-      <c r="AX33" s="70"/>
-      <c r="AY33" s="70"/>
-      <c r="AZ33" s="70"/>
-      <c r="BA33" s="70"/>
-      <c r="BB33" s="70"/>
-      <c r="BC33" s="70"/>
-      <c r="BD33" s="70"/>
-      <c r="BE33" s="71"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="82"/>
+      <c r="P33" s="83"/>
+      <c r="Q33" s="83"/>
+      <c r="R33" s="83"/>
+      <c r="S33" s="83"/>
+      <c r="T33" s="83"/>
+      <c r="U33" s="83"/>
+      <c r="V33" s="83"/>
+      <c r="W33" s="83"/>
+      <c r="X33" s="83"/>
+      <c r="Y33" s="83"/>
+      <c r="Z33" s="83"/>
+      <c r="AA33" s="83"/>
+      <c r="AB33" s="83"/>
+      <c r="AC33" s="83"/>
+      <c r="AD33" s="83"/>
+      <c r="AE33" s="83"/>
+      <c r="AF33" s="83"/>
+      <c r="AG33" s="83"/>
+      <c r="AH33" s="83"/>
+      <c r="AI33" s="83"/>
+      <c r="AJ33" s="83"/>
+      <c r="AK33" s="83"/>
+      <c r="AL33" s="83"/>
+      <c r="AM33" s="83"/>
+      <c r="AN33" s="83"/>
+      <c r="AO33" s="83"/>
+      <c r="AP33" s="84"/>
+      <c r="AQ33" s="88"/>
+      <c r="AR33" s="83"/>
+      <c r="AS33" s="83"/>
+      <c r="AT33" s="83"/>
+      <c r="AU33" s="83"/>
+      <c r="AV33" s="83"/>
+      <c r="AW33" s="83"/>
+      <c r="AX33" s="83"/>
+      <c r="AY33" s="83"/>
+      <c r="AZ33" s="83"/>
+      <c r="BA33" s="83"/>
+      <c r="BB33" s="83"/>
+      <c r="BC33" s="83"/>
+      <c r="BD33" s="83"/>
+      <c r="BE33" s="89"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="100"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="81"/>
-      <c r="O34" s="79"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="70"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="70"/>
-      <c r="AC34" s="70"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="70"/>
-      <c r="AH34" s="70"/>
-      <c r="AI34" s="70"/>
-      <c r="AJ34" s="70"/>
-      <c r="AK34" s="70"/>
-      <c r="AL34" s="70"/>
-      <c r="AM34" s="70"/>
-      <c r="AN34" s="70"/>
-      <c r="AO34" s="70"/>
-      <c r="AP34" s="82"/>
-      <c r="AQ34" s="69"/>
-      <c r="AR34" s="70"/>
-      <c r="AS34" s="70"/>
-      <c r="AT34" s="70"/>
-      <c r="AU34" s="70"/>
-      <c r="AV34" s="70"/>
-      <c r="AW34" s="70"/>
-      <c r="AX34" s="70"/>
-      <c r="AY34" s="70"/>
-      <c r="AZ34" s="70"/>
-      <c r="BA34" s="70"/>
-      <c r="BB34" s="70"/>
-      <c r="BC34" s="70"/>
-      <c r="BD34" s="70"/>
-      <c r="BE34" s="71"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="82"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="90"/>
+      <c r="M34" s="90"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="82"/>
+      <c r="P34" s="83"/>
+      <c r="Q34" s="83"/>
+      <c r="R34" s="83"/>
+      <c r="S34" s="83"/>
+      <c r="T34" s="83"/>
+      <c r="U34" s="83"/>
+      <c r="V34" s="83"/>
+      <c r="W34" s="83"/>
+      <c r="X34" s="83"/>
+      <c r="Y34" s="83"/>
+      <c r="Z34" s="83"/>
+      <c r="AA34" s="83"/>
+      <c r="AB34" s="83"/>
+      <c r="AC34" s="83"/>
+      <c r="AD34" s="83"/>
+      <c r="AE34" s="83"/>
+      <c r="AF34" s="83"/>
+      <c r="AG34" s="83"/>
+      <c r="AH34" s="83"/>
+      <c r="AI34" s="83"/>
+      <c r="AJ34" s="83"/>
+      <c r="AK34" s="83"/>
+      <c r="AL34" s="83"/>
+      <c r="AM34" s="83"/>
+      <c r="AN34" s="83"/>
+      <c r="AO34" s="83"/>
+      <c r="AP34" s="84"/>
+      <c r="AQ34" s="88"/>
+      <c r="AR34" s="83"/>
+      <c r="AS34" s="83"/>
+      <c r="AT34" s="83"/>
+      <c r="AU34" s="83"/>
+      <c r="AV34" s="83"/>
+      <c r="AW34" s="83"/>
+      <c r="AX34" s="83"/>
+      <c r="AY34" s="83"/>
+      <c r="AZ34" s="83"/>
+      <c r="BA34" s="83"/>
+      <c r="BB34" s="83"/>
+      <c r="BC34" s="83"/>
+      <c r="BD34" s="83"/>
+      <c r="BE34" s="89"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="113"/>
-      <c r="B35" s="114"/>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="110"/>
-      <c r="J35" s="110"/>
-      <c r="K35" s="110"/>
-      <c r="L35" s="110"/>
-      <c r="M35" s="110"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="109"/>
-      <c r="P35" s="104"/>
-      <c r="Q35" s="104"/>
-      <c r="R35" s="104"/>
-      <c r="S35" s="104"/>
-      <c r="T35" s="104"/>
-      <c r="U35" s="104"/>
-      <c r="V35" s="104"/>
-      <c r="W35" s="104"/>
-      <c r="X35" s="104"/>
-      <c r="Y35" s="104"/>
-      <c r="Z35" s="104"/>
-      <c r="AA35" s="104"/>
-      <c r="AB35" s="104"/>
-      <c r="AC35" s="104"/>
-      <c r="AD35" s="104"/>
-      <c r="AE35" s="104"/>
-      <c r="AF35" s="104"/>
-      <c r="AG35" s="104"/>
-      <c r="AH35" s="104"/>
-      <c r="AI35" s="104"/>
-      <c r="AJ35" s="104"/>
-      <c r="AK35" s="104"/>
-      <c r="AL35" s="104"/>
-      <c r="AM35" s="104"/>
-      <c r="AN35" s="104"/>
-      <c r="AO35" s="104"/>
-      <c r="AP35" s="112"/>
-      <c r="AQ35" s="103"/>
-      <c r="AR35" s="104"/>
-      <c r="AS35" s="104"/>
-      <c r="AT35" s="104"/>
-      <c r="AU35" s="104"/>
-      <c r="AV35" s="104"/>
-      <c r="AW35" s="104"/>
-      <c r="AX35" s="104"/>
-      <c r="AY35" s="104"/>
-      <c r="AZ35" s="104"/>
-      <c r="BA35" s="104"/>
-      <c r="BB35" s="104"/>
-      <c r="BC35" s="104"/>
-      <c r="BD35" s="104"/>
-      <c r="BE35" s="105"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="80"/>
+      <c r="O35" s="78"/>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="70"/>
+      <c r="S35" s="70"/>
+      <c r="T35" s="70"/>
+      <c r="U35" s="70"/>
+      <c r="V35" s="70"/>
+      <c r="W35" s="70"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="70"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="70"/>
+      <c r="AD35" s="70"/>
+      <c r="AE35" s="70"/>
+      <c r="AF35" s="70"/>
+      <c r="AG35" s="70"/>
+      <c r="AH35" s="70"/>
+      <c r="AI35" s="70"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="70"/>
+      <c r="AL35" s="70"/>
+      <c r="AM35" s="70"/>
+      <c r="AN35" s="70"/>
+      <c r="AO35" s="70"/>
+      <c r="AP35" s="81"/>
+      <c r="AQ35" s="69"/>
+      <c r="AR35" s="70"/>
+      <c r="AS35" s="70"/>
+      <c r="AT35" s="70"/>
+      <c r="AU35" s="70"/>
+      <c r="AV35" s="70"/>
+      <c r="AW35" s="70"/>
+      <c r="AX35" s="70"/>
+      <c r="AY35" s="70"/>
+      <c r="AZ35" s="70"/>
+      <c r="BA35" s="70"/>
+      <c r="BB35" s="70"/>
+      <c r="BC35" s="70"/>
+      <c r="BD35" s="70"/>
+      <c r="BE35" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="O33:AP33"/>
     <mergeCell ref="AQ35:BE35"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
@@ -8171,115 +8320,6 @@
     <mergeCell ref="H23:N23"/>
     <mergeCell ref="H34:N34"/>
     <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
